--- a/data/veg_final.xlsx
+++ b/data/veg_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailsfsu-my.sharepoint.com/personal/924318106_sfsu_edu/Documents/ProjectData/GitHub/DepositionSFB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="890" documentId="8_{59CBD094-BD12-4802-82EC-BFBFD8F2B4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B9947F3-472C-47F9-91EC-9B9A8CC9E753}"/>
+  <xr:revisionPtr revIDLastSave="909" documentId="8_{59CBD094-BD12-4802-82EC-BFBFD8F2B4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21FBB276-CC88-4175-937F-9288CFC7A9B4}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4080" windowWidth="29040" windowHeight="16440" xr2:uid="{09619B10-7E90-4FB8-AF45-F23757B21A39}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{09619B10-7E90-4FB8-AF45-F23757B21A39}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <author>Savannah Miller</author>
   </authors>
   <commentList>
-    <comment ref="F43" authorId="0" shapeId="0" xr:uid="{389FEA95-7DDE-4177-A949-5F8D55991682}">
+    <comment ref="G43" authorId="0" shapeId="0" xr:uid="{389FEA95-7DDE-4177-A949-5F8D55991682}">
       <text>
         <r>
           <rPr>
@@ -69,7 +69,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F73" authorId="0" shapeId="0" xr:uid="{318148E9-2D79-44B9-82CD-E08367CB215B}">
+    <comment ref="G73" authorId="0" shapeId="0" xr:uid="{318148E9-2D79-44B9-82CD-E08367CB215B}">
       <text>
         <r>
           <rPr>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="39">
   <si>
     <t>Site</t>
   </si>
@@ -214,7 +214,7 @@
     <t>NA</t>
   </si>
   <si>
-    <t>NA?</t>
+    <t>Date</t>
   </si>
 </sst>
 </file>
@@ -308,7 +308,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -647,13 +647,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C24C2CBB-D018-4603-A1EC-5007D4D3E68F}">
-  <dimension ref="A1:I166"/>
+  <dimension ref="A1:J166"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="14.44140625" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -661,3177 +662,3504 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>29</v>
+      <c r="C2" s="4">
+        <v>46074</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2">
-        <v>2026</v>
-      </c>
-      <c r="F2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2">
+        <v>2026</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2">
         <v>50</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>48</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>53.5</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
-        <v>29</v>
+      <c r="C3" s="4">
+        <v>46074</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3">
-        <v>2026</v>
-      </c>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3">
+        <v>2026</v>
+      </c>
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3">
         <v>55</v>
       </c>
-      <c r="H3" s="4">
+      <c r="I3">
         <v>34</v>
       </c>
-      <c r="I3" s="4">
+      <c r="J3">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
-        <v>29</v>
+      <c r="C4" s="4">
+        <v>46074</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4">
-        <v>2026</v>
-      </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4">
+        <v>2026</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4">
         <v>80</v>
       </c>
-      <c r="H4">
-        <v>31</v>
-      </c>
       <c r="I4">
+        <v>31</v>
+      </c>
+      <c r="J4">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
-        <v>29</v>
+      <c r="C5" s="4">
+        <v>46074</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5">
-        <v>2026</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5">
+        <v>2026</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5">
         <v>90</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>34</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>41.5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" t="s">
-        <v>29</v>
+      <c r="C6" s="4">
+        <v>46074</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6">
-        <v>2026</v>
-      </c>
-      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6">
+        <v>2026</v>
+      </c>
+      <c r="G6" t="s">
         <v>32</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>50</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>15</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>18.5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
-        <v>29</v>
+      <c r="C7" s="4">
+        <v>46074</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7">
-        <v>2026</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7">
+        <v>2026</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7">
         <v>20</v>
       </c>
-      <c r="H7">
-        <v>25</v>
-      </c>
       <c r="I7">
+        <v>25</v>
+      </c>
+      <c r="J7">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" t="s">
-        <v>29</v>
+      <c r="C8" s="4">
+        <v>46074</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>2026</v>
-      </c>
-      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8">
+        <v>2026</v>
+      </c>
+      <c r="G8" t="s">
         <v>32</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>55</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>13</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>18.5</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" t="s">
-        <v>29</v>
+      <c r="C9" s="4">
+        <v>46074</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9">
-        <v>2026</v>
-      </c>
-      <c r="F9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9">
+        <v>2026</v>
+      </c>
+      <c r="G9" t="s">
+        <v>31</v>
       </c>
       <c r="H9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I9">
+        <v>29</v>
+      </c>
+      <c r="J9">
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" t="s">
-        <v>29</v>
+      <c r="C10" s="4">
+        <v>46074</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10">
-        <v>2026</v>
-      </c>
-      <c r="F10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10">
+        <v>2026</v>
+      </c>
+      <c r="G10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10">
         <v>70</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>36</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="C11" t="s">
-        <v>29</v>
+      <c r="C11" s="4">
+        <v>46074</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11">
-        <v>2026</v>
-      </c>
-      <c r="F11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11">
+        <v>2026</v>
+      </c>
+      <c r="G11" t="s">
         <v>33</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>60</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>26</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="C12" t="s">
-        <v>29</v>
+      <c r="C12" s="4">
+        <v>46074</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12">
-        <v>2026</v>
-      </c>
-      <c r="F12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12">
+        <v>2026</v>
+      </c>
+      <c r="G12" t="s">
         <v>35</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>10</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>66</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
-      <c r="C13" t="s">
-        <v>29</v>
+      <c r="C13" s="4">
+        <v>46074</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13">
-        <v>2026</v>
-      </c>
-      <c r="F13" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13">
-        <v>40</v>
+        <v>29</v>
+      </c>
+      <c r="E13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13">
+        <v>2026</v>
+      </c>
+      <c r="G13" t="s">
+        <v>31</v>
       </c>
       <c r="H13">
         <v>40</v>
       </c>
       <c r="I13">
+        <v>40</v>
+      </c>
+      <c r="J13">
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>9</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" t="s">
-        <v>29</v>
+      <c r="C14" s="4">
+        <v>46074</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14">
-        <v>2026</v>
-      </c>
-      <c r="F14" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14">
+        <v>29</v>
+      </c>
+      <c r="E14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14">
+        <v>2026</v>
+      </c>
+      <c r="G14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14">
         <v>80</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>35</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>9</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
       </c>
-      <c r="C15" t="s">
-        <v>29</v>
+      <c r="C15" s="4">
+        <v>46074</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15">
-        <v>2026</v>
-      </c>
-      <c r="F15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15">
+        <v>29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15">
+        <v>2026</v>
+      </c>
+      <c r="G15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15">
         <v>80</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>37</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
       <c r="B16" t="s">
         <v>20</v>
       </c>
-      <c r="C16" t="s">
-        <v>29</v>
+      <c r="C16" s="4">
+        <v>46074</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16">
-        <v>2026</v>
-      </c>
-      <c r="F16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16">
+        <v>29</v>
+      </c>
+      <c r="E16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16">
+        <v>2026</v>
+      </c>
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16">
         <v>75</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>32</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
       <c r="B17" t="s">
         <v>19</v>
       </c>
-      <c r="C17" t="s">
-        <v>29</v>
+      <c r="C17" s="4">
+        <v>46074</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17">
-        <v>2026</v>
-      </c>
-      <c r="F17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17">
+        <v>2026</v>
+      </c>
+      <c r="G17" t="s">
         <v>32</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>40</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>16</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>9</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
       </c>
-      <c r="C18" t="s">
-        <v>29</v>
+      <c r="C18" s="4">
+        <v>46074</v>
       </c>
       <c r="D18" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18">
-        <v>2026</v>
-      </c>
-      <c r="F18" t="s">
-        <v>31</v>
-      </c>
-      <c r="G18">
+        <v>29</v>
+      </c>
+      <c r="E18" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18">
+        <v>2026</v>
+      </c>
+      <c r="G18" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18">
         <v>20</v>
       </c>
-      <c r="H18">
-        <v>25</v>
-      </c>
       <c r="I18">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="J18">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>9</v>
       </c>
       <c r="B19" t="s">
         <v>21</v>
       </c>
-      <c r="C19" t="s">
-        <v>29</v>
+      <c r="C19" s="4">
+        <v>46074</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19">
-        <v>2026</v>
-      </c>
-      <c r="F19" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19">
+        <v>29</v>
+      </c>
+      <c r="E19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19">
+        <v>2026</v>
+      </c>
+      <c r="G19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19">
         <v>65</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>42</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>9</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
       </c>
-      <c r="C20" t="s">
-        <v>29</v>
+      <c r="C20" s="4">
+        <v>46074</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20">
-        <v>2026</v>
-      </c>
-      <c r="F20" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20">
+        <v>29</v>
+      </c>
+      <c r="E20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20">
+        <v>2026</v>
+      </c>
+      <c r="G20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20">
         <v>70</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>38</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>24</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
       </c>
-      <c r="C21" t="s">
-        <v>29</v>
+      <c r="C21" s="4">
+        <v>46073</v>
       </c>
       <c r="D21" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21">
-        <v>2026</v>
-      </c>
-      <c r="F21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21">
+        <v>2026</v>
+      </c>
+      <c r="G21" t="s">
         <v>34</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>60</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>15</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>20.5</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>24</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
       </c>
-      <c r="C22" t="s">
-        <v>29</v>
+      <c r="C22" s="4">
+        <v>46073</v>
       </c>
       <c r="D22" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22">
-        <v>2026</v>
-      </c>
-      <c r="F22" t="s">
-        <v>31</v>
-      </c>
-      <c r="G22">
+        <v>29</v>
+      </c>
+      <c r="E22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22">
+        <v>2026</v>
+      </c>
+      <c r="G22" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22">
         <v>40</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>26</v>
       </c>
-      <c r="I22">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J22">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
       </c>
-      <c r="C23" t="s">
-        <v>29</v>
+      <c r="C23" s="4">
+        <v>46073</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23">
-        <v>2026</v>
-      </c>
-      <c r="F23" t="s">
-        <v>31</v>
-      </c>
-      <c r="G23">
+        <v>29</v>
+      </c>
+      <c r="E23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23">
+        <v>2026</v>
+      </c>
+      <c r="G23" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23">
         <v>50</v>
       </c>
-      <c r="H23">
-        <v>29</v>
-      </c>
       <c r="I23">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="J23">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
       </c>
-      <c r="C24" t="s">
-        <v>29</v>
+      <c r="C24" s="4">
+        <v>46073</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24">
-        <v>2026</v>
-      </c>
-      <c r="F24" t="s">
-        <v>31</v>
-      </c>
-      <c r="G24">
+        <v>29</v>
+      </c>
+      <c r="E24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24">
+        <v>2026</v>
+      </c>
+      <c r="G24" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24">
         <v>80</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>39</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>42.5</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="B25" t="s">
         <v>23</v>
       </c>
-      <c r="C25" t="s">
-        <v>29</v>
+      <c r="C25" s="4">
+        <v>46073</v>
       </c>
       <c r="D25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25">
-        <v>2026</v>
-      </c>
-      <c r="F25" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25">
+        <v>29</v>
+      </c>
+      <c r="E25" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25">
+        <v>2026</v>
+      </c>
+      <c r="G25" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25">
         <v>60</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>51</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
       </c>
-      <c r="C26" t="s">
-        <v>29</v>
+      <c r="C26" s="4">
+        <v>46073</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26">
-        <v>2026</v>
-      </c>
-      <c r="F26" t="s">
-        <v>31</v>
-      </c>
-      <c r="G26">
-        <v>80</v>
+        <v>29</v>
+      </c>
+      <c r="E26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26">
+        <v>2026</v>
+      </c>
+      <c r="G26" t="s">
+        <v>31</v>
       </c>
       <c r="H26">
         <v>80</v>
       </c>
       <c r="I26">
+        <v>80</v>
+      </c>
+      <c r="J26">
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>24</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
       </c>
-      <c r="C27" t="s">
-        <v>29</v>
+      <c r="C27" s="4">
+        <v>46073</v>
       </c>
       <c r="D27" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27">
-        <v>2026</v>
-      </c>
-      <c r="F27" t="s">
-        <v>31</v>
-      </c>
-      <c r="G27">
+        <v>29</v>
+      </c>
+      <c r="E27" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27">
+        <v>2026</v>
+      </c>
+      <c r="G27" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27">
         <v>85</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>38</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>24</v>
       </c>
       <c r="B28" t="s">
         <v>15</v>
       </c>
-      <c r="C28" t="s">
-        <v>29</v>
+      <c r="C28" s="4">
+        <v>46073</v>
       </c>
       <c r="D28" t="s">
-        <v>27</v>
-      </c>
-      <c r="E28">
-        <v>2026</v>
-      </c>
-      <c r="F28" t="s">
-        <v>31</v>
-      </c>
-      <c r="G28">
+        <v>29</v>
+      </c>
+      <c r="E28" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28">
+        <v>2026</v>
+      </c>
+      <c r="G28" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28">
         <v>45</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>36</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>24</v>
       </c>
       <c r="B29" t="s">
         <v>16</v>
       </c>
-      <c r="C29" t="s">
-        <v>29</v>
+      <c r="C29" s="4">
+        <v>46073</v>
       </c>
       <c r="D29" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29">
-        <v>2026</v>
-      </c>
-      <c r="F29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G29">
+        <v>29</v>
+      </c>
+      <c r="E29" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29">
+        <v>2026</v>
+      </c>
+      <c r="G29" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29">
         <v>10</v>
       </c>
-      <c r="H29">
-        <v>28</v>
-      </c>
       <c r="I29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>24</v>
       </c>
       <c r="B30" t="s">
         <v>17</v>
       </c>
-      <c r="C30" t="s">
-        <v>29</v>
+      <c r="C30" s="4">
+        <v>46073</v>
       </c>
       <c r="D30" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30">
-        <v>2026</v>
-      </c>
-      <c r="F30" t="s">
-        <v>31</v>
-      </c>
-      <c r="G30">
+        <v>29</v>
+      </c>
+      <c r="E30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30">
+        <v>2026</v>
+      </c>
+      <c r="G30" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30">
         <v>50</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>23.5</v>
       </c>
-      <c r="I30">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>24</v>
       </c>
       <c r="B31" t="s">
         <v>18</v>
       </c>
-      <c r="C31" t="s">
-        <v>29</v>
+      <c r="C31" s="4">
+        <v>46073</v>
       </c>
       <c r="D31" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31">
-        <v>2026</v>
-      </c>
-      <c r="F31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G31">
+        <v>29</v>
+      </c>
+      <c r="E31" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31">
+        <v>2026</v>
+      </c>
+      <c r="G31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H31">
         <v>90</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>33</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>37.5</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>24</v>
       </c>
       <c r="B32" t="s">
         <v>20</v>
       </c>
-      <c r="C32" t="s">
-        <v>29</v>
+      <c r="C32" s="4">
+        <v>46073</v>
       </c>
       <c r="D32" t="s">
-        <v>27</v>
-      </c>
-      <c r="E32">
-        <v>2026</v>
-      </c>
-      <c r="F32" t="s">
-        <v>31</v>
-      </c>
-      <c r="G32">
+        <v>29</v>
+      </c>
+      <c r="E32" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32">
+        <v>2026</v>
+      </c>
+      <c r="G32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H32">
         <v>90</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>39</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>45.5</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>24</v>
       </c>
       <c r="B33" t="s">
         <v>19</v>
       </c>
-      <c r="C33" t="s">
-        <v>29</v>
+      <c r="C33" s="4">
+        <v>46073</v>
       </c>
       <c r="D33" t="s">
-        <v>27</v>
-      </c>
-      <c r="E33">
-        <v>2026</v>
-      </c>
-      <c r="F33" t="s">
-        <v>31</v>
-      </c>
-      <c r="G33">
+        <v>29</v>
+      </c>
+      <c r="E33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33">
+        <v>2026</v>
+      </c>
+      <c r="G33" t="s">
+        <v>31</v>
+      </c>
+      <c r="H33">
         <v>75</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>37</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>24</v>
       </c>
       <c r="B34" t="s">
         <v>21</v>
       </c>
-      <c r="C34" t="s">
-        <v>29</v>
+      <c r="C34" s="4">
+        <v>46073</v>
       </c>
       <c r="D34" t="s">
-        <v>27</v>
-      </c>
-      <c r="E34">
-        <v>2026</v>
-      </c>
-      <c r="F34" t="s">
-        <v>31</v>
-      </c>
-      <c r="G34">
+        <v>29</v>
+      </c>
+      <c r="E34" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34">
+        <v>2026</v>
+      </c>
+      <c r="G34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H34">
         <v>70</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>41</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>24</v>
       </c>
       <c r="B35" t="s">
         <v>22</v>
       </c>
-      <c r="C35" t="s">
-        <v>29</v>
+      <c r="C35" s="4">
+        <v>46073</v>
       </c>
       <c r="D35" t="s">
-        <v>27</v>
-      </c>
-      <c r="E35">
-        <v>2026</v>
-      </c>
-      <c r="F35" t="s">
-        <v>31</v>
-      </c>
-      <c r="G35">
+        <v>29</v>
+      </c>
+      <c r="E35" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35">
+        <v>2026</v>
+      </c>
+      <c r="G35" t="s">
+        <v>31</v>
+      </c>
+      <c r="H35">
         <v>90</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>37</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>25</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
       </c>
-      <c r="C36" t="s">
-        <v>29</v>
+      <c r="C36" s="4">
+        <v>46060</v>
       </c>
       <c r="D36" t="s">
-        <v>27</v>
-      </c>
-      <c r="E36">
-        <v>2026</v>
-      </c>
-      <c r="F36" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36">
+        <v>2026</v>
+      </c>
+      <c r="G36" t="s">
         <v>33</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>70</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>14</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>25</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
       </c>
-      <c r="C37" t="s">
-        <v>29</v>
+      <c r="C37" s="4">
+        <v>46060</v>
       </c>
       <c r="D37" t="s">
-        <v>27</v>
-      </c>
-      <c r="E37">
-        <v>2026</v>
-      </c>
-      <c r="F37" t="s">
-        <v>31</v>
-      </c>
-      <c r="G37">
+        <v>29</v>
+      </c>
+      <c r="E37" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37">
+        <v>2026</v>
+      </c>
+      <c r="G37" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37">
         <v>15</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>22</v>
       </c>
-      <c r="I37">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J37">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>25</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
       </c>
-      <c r="C38" t="s">
-        <v>29</v>
+      <c r="C38" s="4">
+        <v>46060</v>
       </c>
       <c r="D38" t="s">
-        <v>27</v>
-      </c>
-      <c r="E38">
-        <v>2026</v>
-      </c>
-      <c r="F38" t="s">
-        <v>31</v>
-      </c>
-      <c r="G38">
+        <v>29</v>
+      </c>
+      <c r="E38" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38">
+        <v>2026</v>
+      </c>
+      <c r="G38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H38">
         <v>10</v>
-      </c>
-      <c r="H38">
-        <v>35</v>
       </c>
       <c r="I38">
         <v>35</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J38">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>25</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
       </c>
-      <c r="C39" t="s">
-        <v>29</v>
+      <c r="C39" s="4">
+        <v>46060</v>
       </c>
       <c r="D39" t="s">
-        <v>27</v>
-      </c>
-      <c r="E39">
-        <v>2026</v>
-      </c>
-      <c r="F39" t="s">
+        <v>29</v>
+      </c>
+      <c r="E39" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39">
+        <v>2026</v>
+      </c>
+      <c r="G39" t="s">
         <v>33</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>70</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>15</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>17.5</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>25</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
       </c>
-      <c r="C40" t="s">
-        <v>29</v>
+      <c r="C40" s="4">
+        <v>46060</v>
       </c>
       <c r="D40" t="s">
-        <v>27</v>
-      </c>
-      <c r="E40">
-        <v>2026</v>
-      </c>
-      <c r="F40" t="s">
+        <v>29</v>
+      </c>
+      <c r="E40" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40">
+        <v>2026</v>
+      </c>
+      <c r="G40" t="s">
         <v>34</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>90</v>
       </c>
-      <c r="H40">
-        <v>25</v>
-      </c>
       <c r="I40">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="J40">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>25</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
       </c>
-      <c r="C41" t="s">
-        <v>29</v>
+      <c r="C41" s="4">
+        <v>46060</v>
       </c>
       <c r="D41" t="s">
-        <v>27</v>
-      </c>
-      <c r="E41">
-        <v>2026</v>
-      </c>
-      <c r="F41" t="s">
-        <v>31</v>
-      </c>
-      <c r="G41">
+        <v>29</v>
+      </c>
+      <c r="E41" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41">
+        <v>2026</v>
+      </c>
+      <c r="G41" t="s">
+        <v>31</v>
+      </c>
+      <c r="H41">
         <v>15</v>
       </c>
-      <c r="H41">
-        <v>31</v>
-      </c>
       <c r="I41">
+        <v>31</v>
+      </c>
+      <c r="J41">
         <v>30.5</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>25</v>
       </c>
       <c r="B42" t="s">
         <v>23</v>
       </c>
-      <c r="C42" t="s">
-        <v>29</v>
+      <c r="C42" s="4">
+        <v>46060</v>
       </c>
       <c r="D42" t="s">
-        <v>27</v>
-      </c>
-      <c r="E42">
-        <v>2026</v>
-      </c>
-      <c r="F42" t="s">
-        <v>31</v>
-      </c>
-      <c r="G42">
+        <v>29</v>
+      </c>
+      <c r="E42" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42">
+        <v>2026</v>
+      </c>
+      <c r="G42" t="s">
+        <v>31</v>
+      </c>
+      <c r="H42">
         <v>50</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>53</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>25</v>
       </c>
       <c r="B43" t="s">
         <v>23</v>
       </c>
-      <c r="C43" t="s">
-        <v>29</v>
+      <c r="C43" s="4">
+        <v>46060</v>
       </c>
       <c r="D43" t="s">
-        <v>27</v>
-      </c>
-      <c r="E43">
-        <v>2026</v>
-      </c>
-      <c r="F43" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E43" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43">
+        <v>2026</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>15</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>71</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>25</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
       </c>
-      <c r="C44" t="s">
-        <v>29</v>
+      <c r="C44" s="4">
+        <v>46060</v>
       </c>
       <c r="D44" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44">
-        <v>2026</v>
-      </c>
-      <c r="F44" t="s">
-        <v>31</v>
-      </c>
-      <c r="G44">
+        <v>29</v>
+      </c>
+      <c r="E44" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44">
+        <v>2026</v>
+      </c>
+      <c r="G44" t="s">
+        <v>31</v>
+      </c>
+      <c r="H44">
         <v>65</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>46</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>25</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
       </c>
-      <c r="C45" t="s">
-        <v>29</v>
+      <c r="C45" s="4">
+        <v>46060</v>
       </c>
       <c r="D45" t="s">
-        <v>27</v>
-      </c>
-      <c r="E45">
-        <v>2026</v>
-      </c>
-      <c r="F45" t="s">
+        <v>29</v>
+      </c>
+      <c r="E45" t="s">
+        <v>27</v>
+      </c>
+      <c r="F45">
+        <v>2026</v>
+      </c>
+      <c r="G45" t="s">
         <v>35</v>
       </c>
-      <c r="G45">
-        <v>30</v>
-      </c>
       <c r="H45">
+        <v>30</v>
+      </c>
+      <c r="I45">
         <v>73</v>
       </c>
-      <c r="I45">
+      <c r="J45">
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>25</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
       </c>
-      <c r="C46" t="s">
-        <v>29</v>
+      <c r="C46" s="4">
+        <v>46060</v>
       </c>
       <c r="D46" t="s">
-        <v>27</v>
-      </c>
-      <c r="E46">
-        <v>2026</v>
-      </c>
-      <c r="F46" t="s">
-        <v>31</v>
-      </c>
-      <c r="G46">
+        <v>29</v>
+      </c>
+      <c r="E46" t="s">
+        <v>27</v>
+      </c>
+      <c r="F46">
+        <v>2026</v>
+      </c>
+      <c r="G46" t="s">
+        <v>31</v>
+      </c>
+      <c r="H46">
         <v>70</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>46</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>25</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
       </c>
-      <c r="C47" t="s">
-        <v>29</v>
+      <c r="C47" s="4">
+        <v>46060</v>
       </c>
       <c r="D47" t="s">
-        <v>27</v>
-      </c>
-      <c r="E47">
-        <v>2026</v>
-      </c>
-      <c r="F47" t="s">
+        <v>29</v>
+      </c>
+      <c r="E47" t="s">
+        <v>27</v>
+      </c>
+      <c r="F47">
+        <v>2026</v>
+      </c>
+      <c r="G47" t="s">
         <v>35</v>
       </c>
-      <c r="G47">
-        <v>30</v>
-      </c>
       <c r="H47">
+        <v>30</v>
+      </c>
+      <c r="I47">
         <v>68</v>
       </c>
-      <c r="I47">
+      <c r="J47">
         <v>74</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>25</v>
       </c>
       <c r="B48" t="s">
         <v>15</v>
       </c>
-      <c r="C48" t="s">
-        <v>29</v>
+      <c r="C48" s="4">
+        <v>46060</v>
       </c>
       <c r="D48" t="s">
-        <v>27</v>
-      </c>
-      <c r="E48">
-        <v>2026</v>
-      </c>
-      <c r="F48" t="s">
+        <v>29</v>
+      </c>
+      <c r="E48" t="s">
+        <v>27</v>
+      </c>
+      <c r="F48">
+        <v>2026</v>
+      </c>
+      <c r="G48" t="s">
         <v>34</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>75</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>34</v>
       </c>
-      <c r="I48">
+      <c r="J48">
         <v>39</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>25</v>
       </c>
       <c r="B49" t="s">
         <v>15</v>
       </c>
-      <c r="C49" t="s">
-        <v>29</v>
+      <c r="C49" s="4">
+        <v>46060</v>
       </c>
       <c r="D49" t="s">
-        <v>27</v>
-      </c>
-      <c r="E49">
-        <v>2026</v>
-      </c>
-      <c r="F49" t="s">
-        <v>31</v>
-      </c>
-      <c r="G49">
+        <v>29</v>
+      </c>
+      <c r="E49" t="s">
+        <v>27</v>
+      </c>
+      <c r="F49">
+        <v>2026</v>
+      </c>
+      <c r="G49" t="s">
+        <v>31</v>
+      </c>
+      <c r="H49">
         <v>15</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J49" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>25</v>
       </c>
       <c r="B50" t="s">
         <v>16</v>
       </c>
-      <c r="C50" t="s">
-        <v>29</v>
+      <c r="C50" s="4">
+        <v>46060</v>
       </c>
       <c r="D50" t="s">
-        <v>27</v>
-      </c>
-      <c r="E50">
-        <v>2026</v>
-      </c>
-      <c r="F50" t="s">
-        <v>31</v>
-      </c>
-      <c r="G50">
+        <v>29</v>
+      </c>
+      <c r="E50" t="s">
+        <v>27</v>
+      </c>
+      <c r="F50">
+        <v>2026</v>
+      </c>
+      <c r="G50" t="s">
+        <v>31</v>
+      </c>
+      <c r="H50">
         <v>55</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>35</v>
       </c>
-      <c r="I50">
+      <c r="J50">
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>25</v>
       </c>
       <c r="B51" t="s">
         <v>16</v>
       </c>
-      <c r="C51" t="s">
-        <v>29</v>
+      <c r="C51" s="4">
+        <v>46060</v>
       </c>
       <c r="D51" t="s">
-        <v>27</v>
-      </c>
-      <c r="E51">
-        <v>2026</v>
-      </c>
-      <c r="F51" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" t="s">
+        <v>27</v>
+      </c>
+      <c r="F51">
+        <v>2026</v>
+      </c>
+      <c r="G51" t="s">
         <v>33</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>50</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J51" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>25</v>
       </c>
       <c r="B52" t="s">
         <v>17</v>
       </c>
-      <c r="C52" t="s">
-        <v>29</v>
+      <c r="C52" s="4">
+        <v>46060</v>
       </c>
       <c r="D52" t="s">
-        <v>27</v>
-      </c>
-      <c r="E52">
-        <v>2026</v>
-      </c>
-      <c r="F52" t="s">
-        <v>31</v>
-      </c>
-      <c r="G52">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="E52" t="s">
+        <v>27</v>
+      </c>
+      <c r="F52">
+        <v>2026</v>
+      </c>
+      <c r="G52" t="s">
+        <v>31</v>
       </c>
       <c r="H52">
+        <v>30</v>
+      </c>
+      <c r="I52">
         <v>32</v>
       </c>
-      <c r="I52">
+      <c r="J52">
         <v>31.5</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>25</v>
       </c>
       <c r="B53" t="s">
         <v>17</v>
       </c>
-      <c r="C53" t="s">
-        <v>29</v>
+      <c r="C53" s="4">
+        <v>46060</v>
       </c>
       <c r="D53" t="s">
-        <v>27</v>
-      </c>
-      <c r="E53">
-        <v>2026</v>
-      </c>
-      <c r="F53" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" t="s">
+        <v>27</v>
+      </c>
+      <c r="F53">
+        <v>2026</v>
+      </c>
+      <c r="G53" t="s">
         <v>33</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <v>60</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <v>13</v>
       </c>
-      <c r="I53">
+      <c r="J53">
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>25</v>
       </c>
       <c r="B54" t="s">
         <v>18</v>
       </c>
-      <c r="C54" t="s">
-        <v>29</v>
+      <c r="C54" s="4">
+        <v>46060</v>
       </c>
       <c r="D54" t="s">
-        <v>27</v>
-      </c>
-      <c r="E54">
-        <v>2026</v>
-      </c>
-      <c r="F54" t="s">
-        <v>31</v>
-      </c>
-      <c r="G54">
+        <v>29</v>
+      </c>
+      <c r="E54" t="s">
+        <v>27</v>
+      </c>
+      <c r="F54">
+        <v>2026</v>
+      </c>
+      <c r="G54" t="s">
+        <v>31</v>
+      </c>
+      <c r="H54">
         <v>45</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>48</v>
       </c>
-      <c r="I54">
+      <c r="J54">
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>25</v>
       </c>
       <c r="B55" t="s">
         <v>18</v>
       </c>
-      <c r="C55" t="s">
-        <v>29</v>
+      <c r="C55" s="4">
+        <v>46060</v>
       </c>
       <c r="D55" t="s">
-        <v>27</v>
-      </c>
-      <c r="E55">
-        <v>2026</v>
-      </c>
-      <c r="F55" t="s">
+        <v>29</v>
+      </c>
+      <c r="E55" t="s">
+        <v>27</v>
+      </c>
+      <c r="F55">
+        <v>2026</v>
+      </c>
+      <c r="G55" t="s">
         <v>35</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>20</v>
       </c>
-      <c r="H55">
+      <c r="I55">
         <v>70</v>
       </c>
-      <c r="I55">
+      <c r="J55">
         <v>81</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>25</v>
       </c>
       <c r="B56" t="s">
         <v>20</v>
       </c>
-      <c r="C56" t="s">
-        <v>29</v>
+      <c r="C56" s="4">
+        <v>46060</v>
       </c>
       <c r="D56" t="s">
-        <v>27</v>
-      </c>
-      <c r="E56">
-        <v>2026</v>
-      </c>
-      <c r="F56" t="s">
-        <v>31</v>
-      </c>
-      <c r="G56">
+        <v>29</v>
+      </c>
+      <c r="E56" t="s">
+        <v>27</v>
+      </c>
+      <c r="F56">
+        <v>2026</v>
+      </c>
+      <c r="G56" t="s">
+        <v>31</v>
+      </c>
+      <c r="H56">
         <v>50</v>
       </c>
-      <c r="H56">
+      <c r="I56">
         <v>45</v>
       </c>
-      <c r="I56">
+      <c r="J56">
         <v>57</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>25</v>
       </c>
       <c r="B57" t="s">
         <v>19</v>
       </c>
-      <c r="C57" t="s">
-        <v>29</v>
+      <c r="C57" s="4">
+        <v>46060</v>
       </c>
       <c r="D57" t="s">
-        <v>27</v>
-      </c>
-      <c r="E57">
-        <v>2026</v>
-      </c>
-      <c r="F57" t="s">
-        <v>31</v>
-      </c>
-      <c r="G57">
+        <v>29</v>
+      </c>
+      <c r="E57" t="s">
+        <v>27</v>
+      </c>
+      <c r="F57">
+        <v>2026</v>
+      </c>
+      <c r="G57" t="s">
+        <v>31</v>
+      </c>
+      <c r="H57">
         <v>45</v>
       </c>
-      <c r="H57">
+      <c r="I57">
         <v>48</v>
       </c>
-      <c r="I57">
+      <c r="J57">
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>25</v>
       </c>
       <c r="B58" t="s">
         <v>19</v>
       </c>
-      <c r="C58" t="s">
-        <v>29</v>
+      <c r="C58" s="4">
+        <v>46060</v>
       </c>
       <c r="D58" t="s">
-        <v>27</v>
-      </c>
-      <c r="E58">
-        <v>2026</v>
-      </c>
-      <c r="F58" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" t="s">
+        <v>27</v>
+      </c>
+      <c r="F58">
+        <v>2026</v>
+      </c>
+      <c r="G58" t="s">
         <v>35</v>
       </c>
-      <c r="G58">
+      <c r="H58">
         <v>40</v>
       </c>
-      <c r="H58">
+      <c r="I58">
         <v>66</v>
       </c>
-      <c r="I58">
+      <c r="J58">
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>25</v>
       </c>
       <c r="B59" t="s">
         <v>21</v>
       </c>
-      <c r="C59" t="s">
-        <v>29</v>
+      <c r="C59" s="4">
+        <v>46060</v>
       </c>
       <c r="D59" t="s">
-        <v>27</v>
-      </c>
-      <c r="E59">
-        <v>2026</v>
-      </c>
-      <c r="F59" t="s">
+        <v>29</v>
+      </c>
+      <c r="E59" t="s">
+        <v>27</v>
+      </c>
+      <c r="F59">
+        <v>2026</v>
+      </c>
+      <c r="G59" t="s">
         <v>35</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <v>15</v>
       </c>
-      <c r="H59">
+      <c r="I59">
         <v>60</v>
       </c>
-      <c r="I59">
+      <c r="J59">
         <v>65</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>25</v>
       </c>
       <c r="B60" t="s">
         <v>21</v>
       </c>
-      <c r="C60" t="s">
-        <v>29</v>
+      <c r="C60" s="4">
+        <v>46060</v>
       </c>
       <c r="D60" t="s">
-        <v>27</v>
-      </c>
-      <c r="E60">
-        <v>2026</v>
-      </c>
-      <c r="F60" t="s">
-        <v>31</v>
-      </c>
-      <c r="G60">
+        <v>29</v>
+      </c>
+      <c r="E60" t="s">
+        <v>27</v>
+      </c>
+      <c r="F60">
+        <v>2026</v>
+      </c>
+      <c r="G60" t="s">
+        <v>31</v>
+      </c>
+      <c r="H60">
         <v>45</v>
       </c>
-      <c r="H60">
+      <c r="I60">
         <v>42</v>
       </c>
-      <c r="I60">
+      <c r="J60">
         <v>52</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>25</v>
       </c>
       <c r="B61" t="s">
         <v>22</v>
       </c>
-      <c r="C61" t="s">
-        <v>29</v>
+      <c r="C61" s="4">
+        <v>46060</v>
       </c>
       <c r="D61" t="s">
-        <v>27</v>
-      </c>
-      <c r="E61">
-        <v>2026</v>
-      </c>
-      <c r="F61" t="s">
+        <v>29</v>
+      </c>
+      <c r="E61" t="s">
+        <v>27</v>
+      </c>
+      <c r="F61">
+        <v>2026</v>
+      </c>
+      <c r="G61" t="s">
         <v>34</v>
       </c>
-      <c r="G61">
+      <c r="H61">
         <v>95</v>
       </c>
-      <c r="H61">
+      <c r="I61">
         <v>34</v>
       </c>
-      <c r="I61">
+      <c r="J61">
         <v>44</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>25</v>
       </c>
       <c r="B62" t="s">
         <v>22</v>
       </c>
-      <c r="C62" t="s">
-        <v>29</v>
+      <c r="C62" s="4">
+        <v>46060</v>
       </c>
       <c r="D62" t="s">
-        <v>27</v>
-      </c>
-      <c r="E62">
-        <v>2026</v>
-      </c>
-      <c r="F62" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" t="s">
+        <v>27</v>
+      </c>
+      <c r="F62">
+        <v>2026</v>
+      </c>
+      <c r="G62" t="s">
         <v>35</v>
       </c>
-      <c r="G62">
+      <c r="H62">
         <v>5</v>
       </c>
-      <c r="H62">
+      <c r="I62">
         <v>58</v>
       </c>
-      <c r="I62">
+      <c r="J62">
         <v>57.5</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>26</v>
       </c>
       <c r="B63" t="s">
         <v>10</v>
       </c>
-      <c r="C63" t="s">
-        <v>29</v>
+      <c r="C63" s="4">
+        <v>46059</v>
       </c>
       <c r="D63" t="s">
-        <v>27</v>
-      </c>
-      <c r="E63">
-        <v>2026</v>
-      </c>
-      <c r="F63" t="s">
-        <v>31</v>
-      </c>
-      <c r="G63">
+        <v>29</v>
+      </c>
+      <c r="E63" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63">
+        <v>2026</v>
+      </c>
+      <c r="G63" t="s">
+        <v>31</v>
+      </c>
+      <c r="H63">
         <v>65</v>
       </c>
-      <c r="H63">
+      <c r="I63">
         <v>57</v>
       </c>
-      <c r="I63">
+      <c r="J63">
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>26</v>
       </c>
       <c r="B64" t="s">
         <v>10</v>
       </c>
-      <c r="C64" t="s">
-        <v>29</v>
+      <c r="C64" s="4">
+        <v>46059</v>
       </c>
       <c r="D64" t="s">
-        <v>27</v>
-      </c>
-      <c r="E64">
-        <v>2026</v>
-      </c>
-      <c r="F64" t="s">
+        <v>29</v>
+      </c>
+      <c r="E64" t="s">
+        <v>27</v>
+      </c>
+      <c r="F64">
+        <v>2026</v>
+      </c>
+      <c r="G64" t="s">
         <v>35</v>
       </c>
-      <c r="G64">
+      <c r="H64">
         <v>20</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J64" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>26</v>
       </c>
       <c r="B65" t="s">
         <v>11</v>
       </c>
-      <c r="C65" t="s">
-        <v>29</v>
+      <c r="C65" s="4">
+        <v>46059</v>
       </c>
       <c r="D65" t="s">
-        <v>27</v>
-      </c>
-      <c r="E65">
-        <v>2026</v>
-      </c>
-      <c r="F65" t="s">
-        <v>31</v>
-      </c>
-      <c r="G65">
+        <v>29</v>
+      </c>
+      <c r="E65" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65">
+        <v>2026</v>
+      </c>
+      <c r="G65" t="s">
+        <v>31</v>
+      </c>
+      <c r="H65">
         <v>70</v>
       </c>
-      <c r="H65">
+      <c r="I65">
         <v>53</v>
       </c>
-      <c r="I65">
+      <c r="J65">
         <v>62.5</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>26</v>
       </c>
       <c r="B66" t="s">
         <v>12</v>
       </c>
-      <c r="C66" t="s">
-        <v>29</v>
+      <c r="C66" s="4">
+        <v>46059</v>
       </c>
       <c r="D66" t="s">
-        <v>27</v>
-      </c>
-      <c r="E66">
-        <v>2026</v>
-      </c>
-      <c r="F66" t="s">
-        <v>31</v>
-      </c>
-      <c r="G66">
+        <v>29</v>
+      </c>
+      <c r="E66" t="s">
+        <v>27</v>
+      </c>
+      <c r="F66">
+        <v>2026</v>
+      </c>
+      <c r="G66" t="s">
+        <v>31</v>
+      </c>
+      <c r="H66">
         <v>50</v>
       </c>
-      <c r="H66">
+      <c r="I66">
         <v>60</v>
       </c>
-      <c r="I66">
+      <c r="J66">
         <v>63</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>26</v>
       </c>
       <c r="B67" t="s">
         <v>23</v>
       </c>
-      <c r="C67" t="s">
-        <v>29</v>
+      <c r="C67" s="4">
+        <v>46059</v>
       </c>
       <c r="D67" t="s">
-        <v>27</v>
-      </c>
-      <c r="E67">
-        <v>2026</v>
-      </c>
-      <c r="F67" t="s">
-        <v>31</v>
-      </c>
-      <c r="G67">
+        <v>29</v>
+      </c>
+      <c r="E67" t="s">
+        <v>27</v>
+      </c>
+      <c r="F67">
+        <v>2026</v>
+      </c>
+      <c r="G67" t="s">
+        <v>31</v>
+      </c>
+      <c r="H67">
         <v>65</v>
       </c>
-      <c r="H67">
+      <c r="I67">
         <v>50</v>
       </c>
-      <c r="I67">
+      <c r="J67">
         <v>51</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>26</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
       </c>
-      <c r="C68" t="s">
-        <v>29</v>
+      <c r="C68" s="4">
+        <v>46059</v>
       </c>
       <c r="D68" t="s">
-        <v>27</v>
-      </c>
-      <c r="E68">
-        <v>2026</v>
-      </c>
-      <c r="F68" t="s">
-        <v>31</v>
-      </c>
-      <c r="G68">
+        <v>29</v>
+      </c>
+      <c r="E68" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68">
+        <v>2026</v>
+      </c>
+      <c r="G68" t="s">
+        <v>31</v>
+      </c>
+      <c r="H68">
         <v>80</v>
       </c>
-      <c r="H68">
+      <c r="I68">
         <v>63</v>
       </c>
-      <c r="I68">
+      <c r="J68">
         <v>66.5</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>26</v>
       </c>
       <c r="B69" t="s">
         <v>14</v>
       </c>
-      <c r="C69" t="s">
-        <v>29</v>
+      <c r="C69" s="4">
+        <v>46059</v>
       </c>
       <c r="D69" t="s">
-        <v>27</v>
-      </c>
-      <c r="E69">
-        <v>2026</v>
-      </c>
-      <c r="F69" t="s">
-        <v>31</v>
-      </c>
-      <c r="G69">
+        <v>29</v>
+      </c>
+      <c r="E69" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69">
+        <v>2026</v>
+      </c>
+      <c r="G69" t="s">
+        <v>31</v>
+      </c>
+      <c r="H69">
         <v>85</v>
       </c>
-      <c r="H69">
+      <c r="I69">
         <v>57</v>
       </c>
-      <c r="I69">
+      <c r="J69">
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>26</v>
       </c>
       <c r="B70" t="s">
         <v>15</v>
       </c>
-      <c r="C70" t="s">
-        <v>29</v>
+      <c r="C70" s="4">
+        <v>46059</v>
       </c>
       <c r="D70" t="s">
-        <v>27</v>
-      </c>
-      <c r="E70">
-        <v>2026</v>
-      </c>
-      <c r="F70" t="s">
-        <v>31</v>
-      </c>
-      <c r="G70">
+        <v>29</v>
+      </c>
+      <c r="E70" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70">
+        <v>2026</v>
+      </c>
+      <c r="G70" t="s">
+        <v>31</v>
+      </c>
+      <c r="H70">
         <v>90</v>
       </c>
-      <c r="H70">
+      <c r="I70">
         <v>56</v>
       </c>
-      <c r="I70">
+      <c r="J70">
         <v>61.5</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>26</v>
       </c>
       <c r="B71" t="s">
         <v>16</v>
       </c>
-      <c r="C71" t="s">
-        <v>29</v>
+      <c r="C71" s="4">
+        <v>46059</v>
       </c>
       <c r="D71" t="s">
-        <v>27</v>
-      </c>
-      <c r="E71">
-        <v>2026</v>
-      </c>
-      <c r="F71" t="s">
+        <v>29</v>
+      </c>
+      <c r="E71" t="s">
+        <v>27</v>
+      </c>
+      <c r="F71">
+        <v>2026</v>
+      </c>
+      <c r="G71" t="s">
         <v>35</v>
       </c>
-      <c r="G71">
+      <c r="H71">
         <v>20</v>
       </c>
-      <c r="H71" s="4">
+      <c r="I71">
         <v>67</v>
       </c>
-      <c r="I71">
+      <c r="J71">
         <v>67.5</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>26</v>
       </c>
       <c r="B72" t="s">
         <v>16</v>
       </c>
-      <c r="C72" t="s">
-        <v>29</v>
+      <c r="C72" s="4">
+        <v>46059</v>
       </c>
       <c r="D72" t="s">
-        <v>27</v>
-      </c>
-      <c r="E72">
-        <v>2026</v>
-      </c>
-      <c r="F72" t="s">
-        <v>31</v>
-      </c>
-      <c r="G72">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="E72" t="s">
+        <v>27</v>
+      </c>
+      <c r="F72">
+        <v>2026</v>
+      </c>
+      <c r="G72" t="s">
+        <v>31</v>
       </c>
       <c r="H72">
+        <v>30</v>
+      </c>
+      <c r="I72">
         <v>52</v>
       </c>
-      <c r="I72">
+      <c r="J72">
         <v>57</v>
       </c>
     </row>
-    <row r="73" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>29</v>
+      <c r="C73" s="4">
+        <v>46059</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E73" s="1">
-        <v>2026</v>
-      </c>
-      <c r="F73" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F73" s="1">
+        <v>2026</v>
+      </c>
+      <c r="G73" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G73" s="1">
+      <c r="H73" s="1">
         <v>20</v>
       </c>
-      <c r="H73" s="1">
+      <c r="I73" s="1">
         <v>70</v>
       </c>
-      <c r="I73" s="1">
+      <c r="J73" s="1">
         <v>79</v>
       </c>
     </row>
-    <row r="74" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>29</v>
+      <c r="C74" s="4">
+        <v>46059</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E74" s="1">
-        <v>2026</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G74" s="1">
+        <v>29</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F74" s="1">
+        <v>2026</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H74" s="1">
         <v>35</v>
       </c>
-      <c r="H74" s="1">
+      <c r="I74" s="1">
         <v>55</v>
       </c>
-      <c r="I74" s="1">
+      <c r="J74" s="1">
         <v>65.5</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>26</v>
       </c>
       <c r="B75" t="s">
         <v>18</v>
       </c>
-      <c r="C75" t="s">
-        <v>29</v>
+      <c r="C75" s="4">
+        <v>46059</v>
       </c>
       <c r="D75" t="s">
-        <v>27</v>
-      </c>
-      <c r="E75">
-        <v>2026</v>
-      </c>
-      <c r="F75" t="s">
-        <v>31</v>
-      </c>
-      <c r="G75">
+        <v>29</v>
+      </c>
+      <c r="E75" t="s">
+        <v>27</v>
+      </c>
+      <c r="F75">
+        <v>2026</v>
+      </c>
+      <c r="G75" t="s">
+        <v>31</v>
+      </c>
+      <c r="H75">
         <v>65</v>
       </c>
-      <c r="H75">
+      <c r="I75">
         <v>52</v>
       </c>
-      <c r="I75">
+      <c r="J75">
         <v>62</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>26</v>
       </c>
       <c r="B76" t="s">
         <v>20</v>
       </c>
-      <c r="C76" t="s">
-        <v>29</v>
+      <c r="C76" s="4">
+        <v>46059</v>
       </c>
       <c r="D76" t="s">
-        <v>27</v>
-      </c>
-      <c r="E76">
-        <v>2026</v>
-      </c>
-      <c r="F76" t="s">
-        <v>31</v>
-      </c>
-      <c r="G76">
+        <v>29</v>
+      </c>
+      <c r="E76" t="s">
+        <v>27</v>
+      </c>
+      <c r="F76">
+        <v>2026</v>
+      </c>
+      <c r="G76" t="s">
+        <v>31</v>
+      </c>
+      <c r="H76">
         <v>75</v>
       </c>
-      <c r="H76">
+      <c r="I76">
         <v>54</v>
       </c>
-      <c r="I76">
+      <c r="J76">
         <v>57</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>26</v>
       </c>
       <c r="B77" t="s">
         <v>19</v>
       </c>
-      <c r="C77" t="s">
-        <v>29</v>
+      <c r="C77" s="4">
+        <v>46059</v>
       </c>
       <c r="D77" t="s">
-        <v>27</v>
-      </c>
-      <c r="E77">
-        <v>2026</v>
-      </c>
-      <c r="F77" t="s">
-        <v>31</v>
-      </c>
-      <c r="G77">
+        <v>29</v>
+      </c>
+      <c r="E77" t="s">
+        <v>27</v>
+      </c>
+      <c r="F77">
+        <v>2026</v>
+      </c>
+      <c r="G77" t="s">
+        <v>31</v>
+      </c>
+      <c r="H77">
         <v>90</v>
       </c>
-      <c r="H77">
+      <c r="I77">
         <v>65</v>
       </c>
-      <c r="I77">
+      <c r="J77">
         <v>68.5</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>26</v>
       </c>
       <c r="B78" t="s">
         <v>21</v>
       </c>
-      <c r="C78" t="s">
-        <v>29</v>
+      <c r="C78" s="4">
+        <v>46059</v>
       </c>
       <c r="D78" t="s">
-        <v>27</v>
-      </c>
-      <c r="E78">
-        <v>2026</v>
-      </c>
-      <c r="F78" t="s">
-        <v>31</v>
-      </c>
-      <c r="G78">
+        <v>29</v>
+      </c>
+      <c r="E78" t="s">
+        <v>27</v>
+      </c>
+      <c r="F78">
+        <v>2026</v>
+      </c>
+      <c r="G78" t="s">
+        <v>31</v>
+      </c>
+      <c r="H78">
         <v>70</v>
       </c>
-      <c r="H78">
+      <c r="I78">
         <v>57</v>
       </c>
-      <c r="I78">
+      <c r="J78">
         <v>62.5</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>26</v>
       </c>
       <c r="B79" t="s">
         <v>22</v>
       </c>
-      <c r="C79" t="s">
-        <v>29</v>
+      <c r="C79" s="4">
+        <v>46059</v>
       </c>
       <c r="D79" t="s">
-        <v>27</v>
-      </c>
-      <c r="E79">
-        <v>2026</v>
-      </c>
-      <c r="F79" t="s">
-        <v>31</v>
-      </c>
-      <c r="G79">
+        <v>29</v>
+      </c>
+      <c r="E79" t="s">
+        <v>27</v>
+      </c>
+      <c r="F79">
+        <v>2026</v>
+      </c>
+      <c r="G79" t="s">
+        <v>31</v>
+      </c>
+      <c r="H79">
         <v>75</v>
       </c>
-      <c r="H79">
+      <c r="I79">
         <v>47.25</v>
       </c>
-      <c r="I79">
+      <c r="J79">
         <v>50</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>9</v>
       </c>
       <c r="B80" t="s">
         <v>10</v>
       </c>
-      <c r="C80" t="s">
-        <v>30</v>
+      <c r="C80" s="4">
+        <v>46184</v>
       </c>
       <c r="D80" t="s">
-        <v>28</v>
-      </c>
-      <c r="E80">
-        <v>2026</v>
-      </c>
-      <c r="F80" t="s">
+        <v>30</v>
+      </c>
+      <c r="E80" t="s">
+        <v>28</v>
+      </c>
+      <c r="F80">
+        <v>2026</v>
+      </c>
+      <c r="G80" t="s">
         <v>35</v>
       </c>
-      <c r="G80">
-        <v>30</v>
-      </c>
       <c r="H80">
+        <v>30</v>
+      </c>
+      <c r="I80">
         <v>89.5</v>
       </c>
-      <c r="I80">
+      <c r="J80">
         <v>95.5</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>9</v>
       </c>
       <c r="B81" t="s">
         <v>10</v>
       </c>
-      <c r="C81" t="s">
-        <v>30</v>
+      <c r="C81" s="4">
+        <v>46184</v>
       </c>
       <c r="D81" t="s">
-        <v>28</v>
-      </c>
-      <c r="E81">
-        <v>2026</v>
-      </c>
-      <c r="F81" t="s">
-        <v>31</v>
-      </c>
-      <c r="G81">
+        <v>30</v>
+      </c>
+      <c r="E81" t="s">
+        <v>28</v>
+      </c>
+      <c r="F81">
+        <v>2026</v>
+      </c>
+      <c r="G81" t="s">
+        <v>31</v>
+      </c>
+      <c r="H81">
         <v>45</v>
       </c>
-      <c r="H81">
+      <c r="I81">
         <v>52.75</v>
       </c>
-      <c r="I81">
+      <c r="J81">
         <v>60</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>9</v>
       </c>
       <c r="B82" t="s">
         <v>11</v>
       </c>
-      <c r="C82" t="s">
-        <v>30</v>
+      <c r="C82" s="4">
+        <v>46184</v>
       </c>
       <c r="D82" t="s">
-        <v>28</v>
-      </c>
-      <c r="E82">
-        <v>2026</v>
-      </c>
-      <c r="F82" t="s">
-        <v>31</v>
-      </c>
-      <c r="G82">
+        <v>30</v>
+      </c>
+      <c r="E82" t="s">
+        <v>28</v>
+      </c>
+      <c r="F82">
+        <v>2026</v>
+      </c>
+      <c r="G82" t="s">
+        <v>31</v>
+      </c>
+      <c r="H82">
         <v>55</v>
       </c>
-      <c r="H82">
+      <c r="I82">
         <v>39</v>
       </c>
-      <c r="I82">
+      <c r="J82">
         <v>42</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>9</v>
       </c>
       <c r="B83" t="s">
         <v>12</v>
       </c>
-      <c r="C83" t="s">
-        <v>30</v>
+      <c r="C83" s="4">
+        <v>46184</v>
       </c>
       <c r="D83" t="s">
-        <v>28</v>
-      </c>
-      <c r="E83">
-        <v>2026</v>
-      </c>
-      <c r="F83" t="s">
-        <v>31</v>
-      </c>
-      <c r="G83">
+        <v>30</v>
+      </c>
+      <c r="E83" t="s">
+        <v>28</v>
+      </c>
+      <c r="F83">
+        <v>2026</v>
+      </c>
+      <c r="G83" t="s">
+        <v>31</v>
+      </c>
+      <c r="H83">
         <v>90</v>
       </c>
-      <c r="H83">
+      <c r="I83">
         <v>39</v>
       </c>
-      <c r="I83">
+      <c r="J83">
         <v>44</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>9</v>
       </c>
       <c r="B84" t="s">
         <v>23</v>
       </c>
-      <c r="C84" t="s">
-        <v>30</v>
+      <c r="C84" s="4">
+        <v>46184</v>
       </c>
       <c r="D84" t="s">
-        <v>28</v>
-      </c>
-      <c r="E84">
-        <v>2026</v>
-      </c>
-      <c r="F84" t="s">
-        <v>31</v>
-      </c>
-      <c r="G84">
+        <v>30</v>
+      </c>
+      <c r="E84" t="s">
+        <v>28</v>
+      </c>
+      <c r="F84">
+        <v>2026</v>
+      </c>
+      <c r="G84" t="s">
+        <v>31</v>
+      </c>
+      <c r="H84">
         <v>90</v>
       </c>
-      <c r="H84">
+      <c r="I84">
         <v>37</v>
       </c>
-      <c r="I84">
+      <c r="J84">
         <v>39</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>9</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
       </c>
-      <c r="C85" t="s">
-        <v>30</v>
+      <c r="C85" s="4">
+        <v>46184</v>
       </c>
       <c r="D85" t="s">
-        <v>28</v>
-      </c>
-      <c r="E85">
-        <v>2026</v>
-      </c>
-      <c r="F85" t="s">
+        <v>30</v>
+      </c>
+      <c r="E85" t="s">
+        <v>28</v>
+      </c>
+      <c r="F85">
+        <v>2026</v>
+      </c>
+      <c r="G85" t="s">
         <v>32</v>
       </c>
-      <c r="G85">
+      <c r="H85">
         <v>65</v>
       </c>
-      <c r="H85">
+      <c r="I85">
         <v>20.75</v>
       </c>
-      <c r="I85">
+      <c r="J85">
         <v>18.5</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>9</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
       </c>
-      <c r="C86" t="s">
-        <v>30</v>
+      <c r="C86" s="4">
+        <v>46184</v>
       </c>
       <c r="D86" t="s">
-        <v>28</v>
-      </c>
-      <c r="E86">
-        <v>2026</v>
-      </c>
-      <c r="F86" t="s">
-        <v>31</v>
-      </c>
-      <c r="G86">
+        <v>30</v>
+      </c>
+      <c r="E86" t="s">
+        <v>28</v>
+      </c>
+      <c r="F86">
+        <v>2026</v>
+      </c>
+      <c r="G86" t="s">
+        <v>31</v>
+      </c>
+      <c r="H86">
         <v>15</v>
       </c>
-      <c r="H86">
+      <c r="I86">
         <v>30.75</v>
       </c>
-      <c r="I86">
+      <c r="J86">
         <v>35</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>9</v>
       </c>
       <c r="B87" t="s">
         <v>14</v>
       </c>
-      <c r="C87" t="s">
-        <v>30</v>
+      <c r="C87" s="4">
+        <v>46184</v>
       </c>
       <c r="D87" t="s">
-        <v>28</v>
-      </c>
-      <c r="E87">
-        <v>2026</v>
-      </c>
-      <c r="F87" t="s">
-        <v>31</v>
-      </c>
-      <c r="G87">
+        <v>30</v>
+      </c>
+      <c r="E87" t="s">
+        <v>28</v>
+      </c>
+      <c r="F87">
+        <v>2026</v>
+      </c>
+      <c r="G87" t="s">
+        <v>31</v>
+      </c>
+      <c r="H87">
         <v>35</v>
       </c>
-      <c r="H87">
+      <c r="I87">
         <v>30.25</v>
       </c>
-      <c r="I87">
+      <c r="J87">
         <v>38.5</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>9</v>
       </c>
       <c r="B88" t="s">
         <v>14</v>
       </c>
-      <c r="C88" t="s">
-        <v>30</v>
+      <c r="C88" s="4">
+        <v>46184</v>
       </c>
       <c r="D88" t="s">
-        <v>28</v>
-      </c>
-      <c r="E88">
-        <v>2026</v>
-      </c>
-      <c r="F88" t="s">
+        <v>30</v>
+      </c>
+      <c r="E88" t="s">
+        <v>28</v>
+      </c>
+      <c r="F88">
+        <v>2026</v>
+      </c>
+      <c r="G88" t="s">
         <v>32</v>
       </c>
-      <c r="G88">
+      <c r="H88">
         <v>40</v>
       </c>
-      <c r="H88">
+      <c r="I88">
         <v>15.75</v>
       </c>
-      <c r="I88">
+      <c r="J88">
         <v>18.5</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>9</v>
       </c>
       <c r="B89" t="s">
         <v>15</v>
       </c>
-      <c r="C89" t="s">
-        <v>30</v>
+      <c r="C89" s="4">
+        <v>46184</v>
       </c>
       <c r="D89" t="s">
-        <v>28</v>
-      </c>
-      <c r="E89">
-        <v>2026</v>
-      </c>
-      <c r="F89" t="s">
-        <v>31</v>
-      </c>
-      <c r="G89">
+        <v>30</v>
+      </c>
+      <c r="E89" t="s">
+        <v>28</v>
+      </c>
+      <c r="F89">
+        <v>2026</v>
+      </c>
+      <c r="G89" t="s">
+        <v>31</v>
+      </c>
+      <c r="H89">
         <v>75</v>
       </c>
-      <c r="H89">
+      <c r="I89">
         <v>35</v>
       </c>
-      <c r="I89">
+      <c r="J89">
         <v>40.5</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>9</v>
       </c>
       <c r="B90" t="s">
         <v>16</v>
       </c>
-      <c r="C90" t="s">
-        <v>30</v>
+      <c r="C90" s="4">
+        <v>46184</v>
       </c>
       <c r="D90" t="s">
-        <v>28</v>
-      </c>
-      <c r="E90">
-        <v>2026</v>
-      </c>
-      <c r="F90" t="s">
+        <v>30</v>
+      </c>
+      <c r="E90" t="s">
+        <v>28</v>
+      </c>
+      <c r="F90">
+        <v>2026</v>
+      </c>
+      <c r="G90" t="s">
         <v>35</v>
       </c>
-      <c r="G90">
+      <c r="H90">
         <v>10</v>
       </c>
-      <c r="H90">
+      <c r="I90">
         <v>64.75</v>
       </c>
-      <c r="I90">
+      <c r="J90">
         <v>71.5</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>9</v>
       </c>
       <c r="B91" t="s">
         <v>16</v>
       </c>
-      <c r="C91" t="s">
-        <v>30</v>
+      <c r="C91" s="4">
+        <v>46184</v>
       </c>
       <c r="D91" t="s">
-        <v>28</v>
-      </c>
-      <c r="E91">
-        <v>2026</v>
-      </c>
-      <c r="F91" t="s">
-        <v>31</v>
-      </c>
-      <c r="G91">
+        <v>30</v>
+      </c>
+      <c r="E91" t="s">
+        <v>28</v>
+      </c>
+      <c r="F91">
+        <v>2026</v>
+      </c>
+      <c r="G91" t="s">
+        <v>31</v>
+      </c>
+      <c r="H91">
         <v>50</v>
       </c>
-      <c r="H91">
+      <c r="I91">
         <v>40.125</v>
       </c>
-      <c r="I91">
+      <c r="J91">
         <v>46</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>9</v>
       </c>
       <c r="B92" t="s">
         <v>17</v>
       </c>
-      <c r="C92" t="s">
-        <v>30</v>
+      <c r="C92" s="4">
+        <v>46184</v>
       </c>
       <c r="D92" t="s">
-        <v>28</v>
-      </c>
-      <c r="E92">
-        <v>2026</v>
-      </c>
-      <c r="F92" t="s">
-        <v>31</v>
-      </c>
-      <c r="G92">
+        <v>30</v>
+      </c>
+      <c r="E92" t="s">
+        <v>28</v>
+      </c>
+      <c r="F92">
+        <v>2026</v>
+      </c>
+      <c r="G92" t="s">
+        <v>31</v>
+      </c>
+      <c r="H92">
         <v>55</v>
       </c>
-      <c r="H92">
+      <c r="I92">
         <v>33.875</v>
       </c>
-      <c r="I92">
+      <c r="J92">
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>9</v>
       </c>
       <c r="B93" t="s">
         <v>18</v>
       </c>
-      <c r="C93" t="s">
-        <v>30</v>
+      <c r="C93" s="4">
+        <v>46184</v>
       </c>
       <c r="D93" t="s">
-        <v>28</v>
-      </c>
-      <c r="E93">
-        <v>2026</v>
-      </c>
-      <c r="F93" t="s">
-        <v>31</v>
-      </c>
-      <c r="G93">
+        <v>30</v>
+      </c>
+      <c r="E93" t="s">
+        <v>28</v>
+      </c>
+      <c r="F93">
+        <v>2026</v>
+      </c>
+      <c r="G93" t="s">
+        <v>31</v>
+      </c>
+      <c r="H93">
         <v>85</v>
       </c>
-      <c r="H93">
+      <c r="I93">
         <v>36.5</v>
       </c>
-      <c r="I93">
+      <c r="J93">
         <v>44</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>9</v>
       </c>
       <c r="B94" t="s">
         <v>20</v>
       </c>
-      <c r="C94" t="s">
-        <v>30</v>
+      <c r="C94" s="4">
+        <v>46184</v>
       </c>
       <c r="D94" t="s">
-        <v>28</v>
-      </c>
-      <c r="E94">
-        <v>2026</v>
-      </c>
-      <c r="F94" t="s">
-        <v>31</v>
-      </c>
-      <c r="G94">
+        <v>30</v>
+      </c>
+      <c r="E94" t="s">
+        <v>28</v>
+      </c>
+      <c r="F94">
+        <v>2026</v>
+      </c>
+      <c r="G94" t="s">
+        <v>31</v>
+      </c>
+      <c r="H94">
         <v>75</v>
       </c>
-      <c r="H94">
+      <c r="I94">
         <v>35.25</v>
       </c>
-      <c r="I94">
+      <c r="J94">
         <v>39</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>9</v>
       </c>
       <c r="B95" t="s">
         <v>19</v>
       </c>
-      <c r="C95" t="s">
-        <v>30</v>
+      <c r="C95" s="4">
+        <v>46184</v>
       </c>
       <c r="D95" t="s">
-        <v>28</v>
-      </c>
-      <c r="E95">
-        <v>2026</v>
-      </c>
-      <c r="F95" t="s">
+        <v>30</v>
+      </c>
+      <c r="E95" t="s">
+        <v>28</v>
+      </c>
+      <c r="F95">
+        <v>2026</v>
+      </c>
+      <c r="G95" t="s">
         <v>32</v>
       </c>
-      <c r="G95">
+      <c r="H95">
         <v>70</v>
       </c>
-      <c r="H95">
+      <c r="I95">
         <v>21.5</v>
       </c>
-      <c r="I95">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J95">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>9</v>
       </c>
       <c r="B96" t="s">
         <v>19</v>
       </c>
-      <c r="C96" t="s">
-        <v>30</v>
+      <c r="C96" s="4">
+        <v>46184</v>
       </c>
       <c r="D96" t="s">
-        <v>28</v>
-      </c>
-      <c r="E96">
-        <v>2026</v>
-      </c>
-      <c r="F96" t="s">
-        <v>31</v>
-      </c>
-      <c r="G96">
+        <v>30</v>
+      </c>
+      <c r="E96" t="s">
+        <v>28</v>
+      </c>
+      <c r="F96">
+        <v>2026</v>
+      </c>
+      <c r="G96" t="s">
+        <v>31</v>
+      </c>
+      <c r="H96">
         <v>15</v>
       </c>
-      <c r="H96">
-        <v>30</v>
-      </c>
       <c r="I96">
+        <v>30</v>
+      </c>
+      <c r="J96">
         <v>45</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>9</v>
       </c>
       <c r="B97" t="s">
         <v>21</v>
       </c>
-      <c r="C97" t="s">
-        <v>30</v>
+      <c r="C97" s="4">
+        <v>46184</v>
       </c>
       <c r="D97" t="s">
-        <v>28</v>
-      </c>
-      <c r="E97">
-        <v>2026</v>
-      </c>
-      <c r="F97" t="s">
-        <v>31</v>
-      </c>
-      <c r="G97">
+        <v>30</v>
+      </c>
+      <c r="E97" t="s">
+        <v>28</v>
+      </c>
+      <c r="F97">
+        <v>2026</v>
+      </c>
+      <c r="G97" t="s">
+        <v>31</v>
+      </c>
+      <c r="H97">
         <v>80</v>
       </c>
-      <c r="H97">
+      <c r="I97">
         <v>42.125</v>
       </c>
-      <c r="I97">
+      <c r="J97">
         <v>55.5</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>9</v>
       </c>
       <c r="B98" t="s">
         <v>22</v>
       </c>
-      <c r="C98" t="s">
-        <v>30</v>
+      <c r="C98" s="4">
+        <v>46184</v>
       </c>
       <c r="D98" t="s">
-        <v>28</v>
-      </c>
-      <c r="E98">
-        <v>2026</v>
-      </c>
-      <c r="F98" t="s">
-        <v>31</v>
-      </c>
-      <c r="G98">
+        <v>30</v>
+      </c>
+      <c r="E98" t="s">
+        <v>28</v>
+      </c>
+      <c r="F98">
+        <v>2026</v>
+      </c>
+      <c r="G98" t="s">
+        <v>31</v>
+      </c>
+      <c r="H98">
         <v>55</v>
       </c>
-      <c r="H98">
+      <c r="I98">
         <v>40.5</v>
       </c>
-      <c r="I98">
+      <c r="J98">
         <v>46</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>24</v>
       </c>
       <c r="B99" t="s">
         <v>10</v>
       </c>
-      <c r="C99" t="s">
-        <v>30</v>
+      <c r="C99" s="4">
+        <v>46182</v>
       </c>
       <c r="D99" t="s">
-        <v>28</v>
-      </c>
-      <c r="E99">
-        <v>2026</v>
-      </c>
-      <c r="F99" t="s">
+        <v>30</v>
+      </c>
+      <c r="E99" t="s">
+        <v>28</v>
+      </c>
+      <c r="F99">
+        <v>2026</v>
+      </c>
+      <c r="G99" t="s">
         <v>34</v>
       </c>
-      <c r="G99">
-        <v>30</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I99">
+      <c r="H99">
+        <v>30</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J99">
         <v>20.5</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>24</v>
       </c>
       <c r="B100" t="s">
         <v>10</v>
       </c>
-      <c r="C100" t="s">
-        <v>30</v>
+      <c r="C100" s="4">
+        <v>46182</v>
       </c>
       <c r="D100" t="s">
-        <v>28</v>
-      </c>
-      <c r="E100">
-        <v>2026</v>
-      </c>
-      <c r="F100" t="s">
-        <v>31</v>
-      </c>
-      <c r="G100">
+        <v>30</v>
+      </c>
+      <c r="E100" t="s">
+        <v>28</v>
+      </c>
+      <c r="F100">
+        <v>2026</v>
+      </c>
+      <c r="G100" t="s">
+        <v>31</v>
+      </c>
+      <c r="H100">
         <v>15</v>
       </c>
-      <c r="H100">
+      <c r="I100">
         <v>24.832999999999998</v>
       </c>
-      <c r="I100">
+      <c r="J100">
         <v>33</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>24</v>
       </c>
       <c r="B101" t="s">
         <v>10</v>
       </c>
-      <c r="C101" t="s">
-        <v>30</v>
+      <c r="C101" s="4">
+        <v>46182</v>
       </c>
       <c r="D101" t="s">
-        <v>28</v>
-      </c>
-      <c r="E101">
-        <v>2026</v>
-      </c>
-      <c r="F101" t="s">
+        <v>30</v>
+      </c>
+      <c r="E101" t="s">
+        <v>28</v>
+      </c>
+      <c r="F101">
+        <v>2026</v>
+      </c>
+      <c r="G101" t="s">
         <v>36</v>
       </c>
-      <c r="G101">
+      <c r="H101">
         <v>65</v>
       </c>
-      <c r="H101">
+      <c r="I101">
         <v>7.25</v>
       </c>
-      <c r="I101">
+      <c r="J101">
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>24</v>
       </c>
       <c r="B102" t="s">
         <v>11</v>
       </c>
-      <c r="C102" t="s">
-        <v>30</v>
+      <c r="C102" s="4">
+        <v>46182</v>
       </c>
       <c r="D102" t="s">
-        <v>28</v>
-      </c>
-      <c r="E102">
-        <v>2026</v>
-      </c>
-      <c r="F102" t="s">
+        <v>30</v>
+      </c>
+      <c r="E102" t="s">
+        <v>28</v>
+      </c>
+      <c r="F102">
+        <v>2026</v>
+      </c>
+      <c r="G102" t="s">
         <v>34</v>
       </c>
-      <c r="G102">
+      <c r="H102">
         <v>40</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J102" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>24</v>
       </c>
       <c r="B103" t="s">
         <v>11</v>
       </c>
-      <c r="C103" t="s">
-        <v>30</v>
+      <c r="C103" s="4">
+        <v>46182</v>
       </c>
       <c r="D103" t="s">
-        <v>28</v>
-      </c>
-      <c r="E103">
-        <v>2026</v>
-      </c>
-      <c r="F103" t="s">
-        <v>31</v>
-      </c>
-      <c r="G103">
+        <v>30</v>
+      </c>
+      <c r="E103" t="s">
+        <v>28</v>
+      </c>
+      <c r="F103">
+        <v>2026</v>
+      </c>
+      <c r="G103" t="s">
+        <v>31</v>
+      </c>
+      <c r="H103">
         <v>50</v>
       </c>
-      <c r="H103">
+      <c r="I103">
         <v>33.625</v>
       </c>
-      <c r="I103">
+      <c r="J103">
         <v>35.5</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>24</v>
       </c>
       <c r="B104" t="s">
         <v>12</v>
       </c>
-      <c r="C104" t="s">
-        <v>30</v>
+      <c r="C104" s="4">
+        <v>46182</v>
       </c>
       <c r="D104" t="s">
-        <v>28</v>
-      </c>
-      <c r="E104">
-        <v>2026</v>
-      </c>
-      <c r="F104" t="s">
-        <v>31</v>
-      </c>
-      <c r="G104">
+        <v>30</v>
+      </c>
+      <c r="E104" t="s">
+        <v>28</v>
+      </c>
+      <c r="F104">
+        <v>2026</v>
+      </c>
+      <c r="G104" t="s">
+        <v>31</v>
+      </c>
+      <c r="H104">
         <v>85</v>
       </c>
-      <c r="H104">
+      <c r="I104">
         <v>39.625</v>
       </c>
-      <c r="I104">
+      <c r="J104">
         <v>43</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>24</v>
       </c>
       <c r="B105" t="s">
         <v>23</v>
       </c>
-      <c r="C105" t="s">
-        <v>30</v>
+      <c r="C105" s="4">
+        <v>46182</v>
       </c>
       <c r="D105" t="s">
-        <v>28</v>
-      </c>
-      <c r="E105">
-        <v>2026</v>
-      </c>
-      <c r="F105" t="s">
-        <v>31</v>
-      </c>
-      <c r="G105">
+        <v>30</v>
+      </c>
+      <c r="E105" t="s">
+        <v>28</v>
+      </c>
+      <c r="F105">
+        <v>2026</v>
+      </c>
+      <c r="G105" t="s">
+        <v>31</v>
+      </c>
+      <c r="H105">
         <v>80</v>
       </c>
-      <c r="H105">
+      <c r="I105">
         <v>46.25</v>
       </c>
-      <c r="I105">
+      <c r="J105">
         <v>58</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>24</v>
       </c>
       <c r="B106" t="s">
         <v>13</v>
       </c>
-      <c r="C106" t="s">
-        <v>30</v>
+      <c r="C106" s="4">
+        <v>46182</v>
       </c>
       <c r="D106" t="s">
-        <v>28</v>
-      </c>
-      <c r="E106">
-        <v>2026</v>
-      </c>
-      <c r="F106" t="s">
-        <v>31</v>
-      </c>
-      <c r="G106">
+        <v>30</v>
+      </c>
+      <c r="E106" t="s">
+        <v>28</v>
+      </c>
+      <c r="F106">
+        <v>2026</v>
+      </c>
+      <c r="G106" t="s">
+        <v>31</v>
+      </c>
+      <c r="H106">
         <v>90</v>
       </c>
-      <c r="H106">
+      <c r="I106">
         <v>37.25</v>
       </c>
-      <c r="I106">
+      <c r="J106">
         <v>44</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>24</v>
       </c>
       <c r="B107" t="s">
         <v>14</v>
       </c>
-      <c r="C107" t="s">
-        <v>30</v>
+      <c r="C107" s="4">
+        <v>46182</v>
       </c>
       <c r="D107" t="s">
-        <v>28</v>
-      </c>
-      <c r="E107">
-        <v>2026</v>
-      </c>
-      <c r="F107" t="s">
-        <v>31</v>
-      </c>
-      <c r="G107">
+        <v>30</v>
+      </c>
+      <c r="E107" t="s">
+        <v>28</v>
+      </c>
+      <c r="F107">
+        <v>2026</v>
+      </c>
+      <c r="G107" t="s">
+        <v>31</v>
+      </c>
+      <c r="H107">
         <v>50</v>
       </c>
-      <c r="H107">
+      <c r="I107">
         <v>35.25</v>
       </c>
-      <c r="I107">
+      <c r="J107">
         <v>41.5</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>24</v>
       </c>
       <c r="B108" t="s">
         <v>14</v>
       </c>
-      <c r="C108" t="s">
-        <v>30</v>
+      <c r="C108" s="4">
+        <v>46182</v>
       </c>
       <c r="D108" t="s">
-        <v>28</v>
-      </c>
-      <c r="E108">
-        <v>2026</v>
-      </c>
-      <c r="F108" t="s">
+        <v>30</v>
+      </c>
+      <c r="E108" t="s">
+        <v>28</v>
+      </c>
+      <c r="F108">
+        <v>2026</v>
+      </c>
+      <c r="G108" t="s">
         <v>33</v>
       </c>
-      <c r="G108">
+      <c r="H108">
         <v>55</v>
       </c>
-      <c r="H108">
+      <c r="I108">
         <v>19.875</v>
       </c>
-      <c r="I108">
+      <c r="J108">
         <v>23</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>24</v>
       </c>
       <c r="B109" t="s">
         <v>15</v>
       </c>
-      <c r="C109" t="s">
-        <v>30</v>
+      <c r="C109" s="4">
+        <v>46182</v>
       </c>
       <c r="D109" t="s">
-        <v>28</v>
-      </c>
-      <c r="E109">
-        <v>2026</v>
-      </c>
-      <c r="F109" t="s">
+        <v>30</v>
+      </c>
+      <c r="E109" t="s">
+        <v>28</v>
+      </c>
+      <c r="F109">
+        <v>2026</v>
+      </c>
+      <c r="G109" t="s">
         <v>33</v>
       </c>
-      <c r="G109">
+      <c r="H109">
         <v>75</v>
       </c>
-      <c r="H109">
+      <c r="I109">
         <v>19.25</v>
       </c>
-      <c r="I109" s="4">
+      <c r="J109">
         <v>26</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>24</v>
       </c>
       <c r="B110" t="s">
         <v>16</v>
       </c>
-      <c r="C110" t="s">
-        <v>30</v>
+      <c r="C110" s="4">
+        <v>46182</v>
       </c>
       <c r="D110" t="s">
-        <v>28</v>
-      </c>
-      <c r="E110">
-        <v>2026</v>
-      </c>
-      <c r="F110" t="s">
-        <v>37</v>
+        <v>30</v>
+      </c>
+      <c r="E110" t="s">
+        <v>28</v>
+      </c>
+      <c r="F110">
+        <v>2026</v>
       </c>
       <c r="G110" t="s">
         <v>37</v>
@@ -3839,1631 +4167,1802 @@
       <c r="H110" t="s">
         <v>37</v>
       </c>
-      <c r="I110" s="4" t="s">
+      <c r="I110" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J110" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>24</v>
       </c>
       <c r="B111" t="s">
         <v>17</v>
       </c>
-      <c r="C111" t="s">
-        <v>30</v>
+      <c r="C111" s="4">
+        <v>46182</v>
       </c>
       <c r="D111" t="s">
-        <v>28</v>
-      </c>
-      <c r="E111">
-        <v>2026</v>
-      </c>
-      <c r="F111" t="s">
-        <v>31</v>
-      </c>
-      <c r="G111">
+        <v>30</v>
+      </c>
+      <c r="E111" t="s">
+        <v>28</v>
+      </c>
+      <c r="F111">
+        <v>2026</v>
+      </c>
+      <c r="G111" t="s">
+        <v>31</v>
+      </c>
+      <c r="H111">
         <v>20</v>
       </c>
-      <c r="H111">
+      <c r="I111">
         <v>20.25</v>
       </c>
-      <c r="I111" s="4">
+      <c r="J111">
         <v>26.5</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>24</v>
       </c>
       <c r="B112" t="s">
         <v>17</v>
       </c>
-      <c r="C112" t="s">
-        <v>30</v>
+      <c r="C112" s="4">
+        <v>46182</v>
       </c>
       <c r="D112" t="s">
-        <v>28</v>
-      </c>
-      <c r="E112">
-        <v>2026</v>
-      </c>
-      <c r="F112" t="s">
+        <v>30</v>
+      </c>
+      <c r="E112" t="s">
+        <v>28</v>
+      </c>
+      <c r="F112">
+        <v>2026</v>
+      </c>
+      <c r="G112" t="s">
         <v>36</v>
       </c>
-      <c r="G112">
+      <c r="H112">
         <v>80</v>
       </c>
-      <c r="H112">
+      <c r="I112">
         <v>12.125</v>
       </c>
-      <c r="I112" s="4">
+      <c r="J112">
         <v>13.5</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>24</v>
       </c>
       <c r="B113" t="s">
         <v>18</v>
       </c>
-      <c r="C113" t="s">
-        <v>30</v>
+      <c r="C113" s="4">
+        <v>46182</v>
       </c>
       <c r="D113" t="s">
-        <v>28</v>
-      </c>
-      <c r="E113">
-        <v>2026</v>
-      </c>
-      <c r="F113" t="s">
-        <v>31</v>
-      </c>
-      <c r="G113">
+        <v>30</v>
+      </c>
+      <c r="E113" t="s">
+        <v>28</v>
+      </c>
+      <c r="F113">
+        <v>2026</v>
+      </c>
+      <c r="G113" t="s">
+        <v>31</v>
+      </c>
+      <c r="H113">
         <v>85</v>
       </c>
-      <c r="H113">
+      <c r="I113">
         <v>33.375</v>
       </c>
-      <c r="I113" s="4">
+      <c r="J113">
         <v>39</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>24</v>
       </c>
       <c r="B114" t="s">
         <v>20</v>
       </c>
-      <c r="C114" t="s">
-        <v>30</v>
+      <c r="C114" s="4">
+        <v>46182</v>
       </c>
       <c r="D114" t="s">
-        <v>28</v>
-      </c>
-      <c r="E114">
-        <v>2026</v>
-      </c>
-      <c r="F114" t="s">
-        <v>31</v>
-      </c>
-      <c r="G114">
+        <v>30</v>
+      </c>
+      <c r="E114" t="s">
+        <v>28</v>
+      </c>
+      <c r="F114">
+        <v>2026</v>
+      </c>
+      <c r="G114" t="s">
+        <v>31</v>
+      </c>
+      <c r="H114">
         <v>95</v>
       </c>
-      <c r="H114">
+      <c r="I114">
         <v>36.375</v>
       </c>
-      <c r="I114">
+      <c r="J114">
         <v>43</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>24</v>
       </c>
       <c r="B115" t="s">
         <v>19</v>
       </c>
-      <c r="C115" t="s">
-        <v>30</v>
+      <c r="C115" s="4">
+        <v>46182</v>
       </c>
       <c r="D115" t="s">
-        <v>28</v>
-      </c>
-      <c r="E115">
-        <v>2026</v>
-      </c>
-      <c r="F115" t="s">
-        <v>31</v>
-      </c>
-      <c r="G115">
+        <v>30</v>
+      </c>
+      <c r="E115" t="s">
+        <v>28</v>
+      </c>
+      <c r="F115">
+        <v>2026</v>
+      </c>
+      <c r="G115" t="s">
+        <v>31</v>
+      </c>
+      <c r="H115">
         <v>90</v>
       </c>
-      <c r="H115">
+      <c r="I115">
         <v>43</v>
       </c>
-      <c r="I115">
+      <c r="J115">
         <v>47</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>24</v>
       </c>
       <c r="B116" t="s">
         <v>21</v>
       </c>
-      <c r="C116" t="s">
-        <v>30</v>
+      <c r="C116" s="4">
+        <v>46182</v>
       </c>
       <c r="D116" t="s">
-        <v>28</v>
-      </c>
-      <c r="E116">
-        <v>2026</v>
-      </c>
-      <c r="F116" t="s">
-        <v>31</v>
-      </c>
-      <c r="G116">
+        <v>30</v>
+      </c>
+      <c r="E116" t="s">
+        <v>28</v>
+      </c>
+      <c r="F116">
+        <v>2026</v>
+      </c>
+      <c r="G116" t="s">
+        <v>31</v>
+      </c>
+      <c r="H116">
         <v>95</v>
       </c>
-      <c r="H116">
+      <c r="I116">
         <v>42.25</v>
       </c>
-      <c r="I116">
+      <c r="J116">
         <v>45</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>24</v>
       </c>
       <c r="B117" t="s">
         <v>22</v>
       </c>
-      <c r="C117" t="s">
-        <v>30</v>
+      <c r="C117" s="4">
+        <v>46182</v>
       </c>
       <c r="D117" t="s">
-        <v>28</v>
-      </c>
-      <c r="E117">
-        <v>2026</v>
-      </c>
-      <c r="F117" t="s">
-        <v>31</v>
-      </c>
-      <c r="G117">
+        <v>30</v>
+      </c>
+      <c r="E117" t="s">
+        <v>28</v>
+      </c>
+      <c r="F117">
+        <v>2026</v>
+      </c>
+      <c r="G117" t="s">
+        <v>31</v>
+      </c>
+      <c r="H117">
         <v>95</v>
       </c>
-      <c r="H117">
+      <c r="I117">
         <v>38.125</v>
       </c>
-      <c r="I117">
+      <c r="J117">
         <v>47</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>25</v>
       </c>
       <c r="B118" t="s">
         <v>10</v>
       </c>
-      <c r="C118" t="s">
-        <v>30</v>
+      <c r="C118" s="4">
+        <v>46183</v>
       </c>
       <c r="D118" t="s">
-        <v>28</v>
-      </c>
-      <c r="E118">
-        <v>2026</v>
-      </c>
-      <c r="F118" t="s">
+        <v>30</v>
+      </c>
+      <c r="E118" t="s">
+        <v>28</v>
+      </c>
+      <c r="F118">
+        <v>2026</v>
+      </c>
+      <c r="G118" t="s">
         <v>33</v>
       </c>
-      <c r="G118">
+      <c r="H118">
         <v>80</v>
       </c>
-      <c r="H118">
+      <c r="I118">
         <v>14.5</v>
       </c>
-      <c r="I118">
+      <c r="J118">
         <v>16.5</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>25</v>
       </c>
       <c r="B119" t="s">
         <v>10</v>
       </c>
-      <c r="C119" t="s">
-        <v>30</v>
+      <c r="C119" s="4">
+        <v>46183</v>
       </c>
       <c r="D119" t="s">
-        <v>28</v>
-      </c>
-      <c r="E119">
-        <v>2026</v>
-      </c>
-      <c r="F119" t="s">
-        <v>31</v>
-      </c>
-      <c r="G119">
+        <v>30</v>
+      </c>
+      <c r="E119" t="s">
+        <v>28</v>
+      </c>
+      <c r="F119">
+        <v>2026</v>
+      </c>
+      <c r="G119" t="s">
+        <v>31</v>
+      </c>
+      <c r="H119">
         <v>5</v>
       </c>
-      <c r="H119">
-        <v>28</v>
-      </c>
       <c r="I119">
         <v>28</v>
       </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J119">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>25</v>
       </c>
       <c r="B120" t="s">
         <v>11</v>
       </c>
-      <c r="C120" t="s">
-        <v>30</v>
+      <c r="C120" s="4">
+        <v>46183</v>
       </c>
       <c r="D120" t="s">
-        <v>28</v>
-      </c>
-      <c r="E120">
-        <v>2026</v>
-      </c>
-      <c r="F120" t="s">
-        <v>31</v>
-      </c>
-      <c r="G120">
+        <v>30</v>
+      </c>
+      <c r="E120" t="s">
+        <v>28</v>
+      </c>
+      <c r="F120">
+        <v>2026</v>
+      </c>
+      <c r="G120" t="s">
+        <v>31</v>
+      </c>
+      <c r="H120">
         <v>10</v>
       </c>
-      <c r="H120">
+      <c r="I120">
         <v>33</v>
       </c>
-      <c r="I120">
+      <c r="J120">
         <v>35</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>25</v>
       </c>
       <c r="B121" t="s">
         <v>11</v>
       </c>
-      <c r="C121" t="s">
-        <v>30</v>
+      <c r="C121" s="4">
+        <v>46183</v>
       </c>
       <c r="D121" t="s">
-        <v>28</v>
-      </c>
-      <c r="E121">
-        <v>2026</v>
-      </c>
-      <c r="F121" t="s">
+        <v>30</v>
+      </c>
+      <c r="E121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F121">
+        <v>2026</v>
+      </c>
+      <c r="G121" t="s">
         <v>33</v>
       </c>
-      <c r="G121">
+      <c r="H121">
         <v>75</v>
       </c>
-      <c r="H121">
+      <c r="I121">
         <v>15.375</v>
       </c>
-      <c r="I121">
+      <c r="J121">
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>25</v>
       </c>
       <c r="B122" t="s">
         <v>12</v>
       </c>
-      <c r="C122" t="s">
-        <v>30</v>
+      <c r="C122" s="4">
+        <v>46183</v>
       </c>
       <c r="D122" t="s">
-        <v>28</v>
-      </c>
-      <c r="E122">
-        <v>2026</v>
-      </c>
-      <c r="F122" t="s">
+        <v>30</v>
+      </c>
+      <c r="E122" t="s">
+        <v>28</v>
+      </c>
+      <c r="F122">
+        <v>2026</v>
+      </c>
+      <c r="G122" t="s">
         <v>34</v>
       </c>
-      <c r="G122">
+      <c r="H122">
         <v>95</v>
       </c>
-      <c r="H122">
+      <c r="I122">
         <v>35.625</v>
       </c>
-      <c r="I122">
+      <c r="J122">
         <v>37.5</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>25</v>
       </c>
       <c r="B123" t="s">
         <v>23</v>
       </c>
-      <c r="C123" t="s">
-        <v>30</v>
+      <c r="C123" s="4">
+        <v>46183</v>
       </c>
       <c r="D123" t="s">
-        <v>28</v>
-      </c>
-      <c r="E123">
-        <v>2026</v>
-      </c>
-      <c r="F123" t="s">
-        <v>31</v>
-      </c>
-      <c r="G123">
+        <v>30</v>
+      </c>
+      <c r="E123" t="s">
+        <v>28</v>
+      </c>
+      <c r="F123">
+        <v>2026</v>
+      </c>
+      <c r="G123" t="s">
+        <v>31</v>
+      </c>
+      <c r="H123">
         <v>60</v>
       </c>
-      <c r="H123">
+      <c r="I123">
         <v>54.125</v>
       </c>
-      <c r="I123">
+      <c r="J123">
         <v>95</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>25</v>
       </c>
       <c r="B124" t="s">
         <v>23</v>
       </c>
-      <c r="C124" t="s">
-        <v>30</v>
+      <c r="C124" s="4">
+        <v>46183</v>
       </c>
       <c r="D124" t="s">
-        <v>28</v>
-      </c>
-      <c r="E124">
-        <v>2026</v>
-      </c>
-      <c r="F124" t="s">
+        <v>30</v>
+      </c>
+      <c r="E124" t="s">
+        <v>28</v>
+      </c>
+      <c r="F124">
+        <v>2026</v>
+      </c>
+      <c r="G124" t="s">
         <v>35</v>
       </c>
-      <c r="G124">
+      <c r="H124">
         <v>20</v>
       </c>
-      <c r="H124">
+      <c r="I124">
         <v>77.25</v>
       </c>
-      <c r="I124">
+      <c r="J124">
         <v>56.5</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>25</v>
       </c>
       <c r="B125" t="s">
         <v>13</v>
       </c>
-      <c r="C125" t="s">
-        <v>30</v>
+      <c r="C125" s="4">
+        <v>46183</v>
       </c>
       <c r="D125" t="s">
-        <v>28</v>
-      </c>
-      <c r="E125">
-        <v>2026</v>
-      </c>
-      <c r="F125" t="s">
-        <v>31</v>
-      </c>
-      <c r="G125">
+        <v>30</v>
+      </c>
+      <c r="E125" t="s">
+        <v>28</v>
+      </c>
+      <c r="F125">
+        <v>2026</v>
+      </c>
+      <c r="G125" t="s">
+        <v>31</v>
+      </c>
+      <c r="H125">
         <v>35</v>
       </c>
-      <c r="H125">
+      <c r="I125">
         <v>44.375</v>
       </c>
-      <c r="I125">
+      <c r="J125">
         <v>51</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>25</v>
       </c>
       <c r="B126" t="s">
         <v>13</v>
       </c>
-      <c r="C126" t="s">
-        <v>30</v>
+      <c r="C126" s="4">
+        <v>46183</v>
       </c>
       <c r="D126" t="s">
-        <v>28</v>
-      </c>
-      <c r="E126">
-        <v>2026</v>
-      </c>
-      <c r="F126" t="s">
+        <v>30</v>
+      </c>
+      <c r="E126" t="s">
+        <v>28</v>
+      </c>
+      <c r="F126">
+        <v>2026</v>
+      </c>
+      <c r="G126" t="s">
         <v>35</v>
       </c>
-      <c r="G126">
+      <c r="H126">
         <v>45</v>
       </c>
-      <c r="H126">
+      <c r="I126">
         <v>68.25</v>
       </c>
-      <c r="I126">
+      <c r="J126">
         <v>71</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>25</v>
       </c>
       <c r="B127" t="s">
         <v>14</v>
       </c>
-      <c r="C127" t="s">
-        <v>30</v>
+      <c r="C127" s="4">
+        <v>46183</v>
       </c>
       <c r="D127" t="s">
-        <v>28</v>
-      </c>
-      <c r="E127">
-        <v>2026</v>
-      </c>
-      <c r="F127" t="s">
-        <v>31</v>
-      </c>
-      <c r="G127">
+        <v>30</v>
+      </c>
+      <c r="E127" t="s">
+        <v>28</v>
+      </c>
+      <c r="F127">
+        <v>2026</v>
+      </c>
+      <c r="G127" t="s">
+        <v>31</v>
+      </c>
+      <c r="H127">
         <v>15</v>
       </c>
-      <c r="H127">
+      <c r="I127">
         <v>45.75</v>
       </c>
-      <c r="I127">
+      <c r="J127">
         <v>55</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>25</v>
       </c>
       <c r="B128" t="s">
         <v>14</v>
       </c>
-      <c r="C128" t="s">
-        <v>30</v>
+      <c r="C128" s="4">
+        <v>46183</v>
       </c>
       <c r="D128" t="s">
-        <v>28</v>
-      </c>
-      <c r="E128">
-        <v>2026</v>
-      </c>
-      <c r="F128" t="s">
+        <v>30</v>
+      </c>
+      <c r="E128" t="s">
+        <v>28</v>
+      </c>
+      <c r="F128">
+        <v>2026</v>
+      </c>
+      <c r="G128" t="s">
         <v>33</v>
       </c>
-      <c r="G128">
+      <c r="H128">
         <v>80</v>
       </c>
-      <c r="H128">
-        <v>25</v>
-      </c>
       <c r="I128">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="J128">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>25</v>
       </c>
       <c r="B129" t="s">
         <v>14</v>
       </c>
-      <c r="C129" t="s">
-        <v>30</v>
+      <c r="C129" s="4">
+        <v>46183</v>
       </c>
       <c r="D129" t="s">
-        <v>28</v>
-      </c>
-      <c r="E129">
-        <v>2026</v>
-      </c>
-      <c r="F129" t="s">
+        <v>30</v>
+      </c>
+      <c r="E129" t="s">
+        <v>28</v>
+      </c>
+      <c r="F129">
+        <v>2026</v>
+      </c>
+      <c r="G129" t="s">
         <v>35</v>
       </c>
-      <c r="G129">
+      <c r="H129">
         <v>20</v>
       </c>
-      <c r="H129">
+      <c r="I129">
         <v>64.25</v>
       </c>
-      <c r="I129">
+      <c r="J129">
         <v>7.15</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>25</v>
       </c>
       <c r="B130" t="s">
         <v>15</v>
       </c>
-      <c r="C130" t="s">
-        <v>30</v>
+      <c r="C130" s="4">
+        <v>46183</v>
       </c>
       <c r="D130" t="s">
-        <v>28</v>
-      </c>
-      <c r="E130">
-        <v>2026</v>
-      </c>
-      <c r="F130" t="s">
+        <v>30</v>
+      </c>
+      <c r="E130" t="s">
+        <v>28</v>
+      </c>
+      <c r="F130">
+        <v>2026</v>
+      </c>
+      <c r="G130" t="s">
         <v>34</v>
       </c>
-      <c r="G130">
+      <c r="H130">
         <v>90</v>
       </c>
-      <c r="H130">
+      <c r="I130">
         <v>30.125</v>
       </c>
-      <c r="I130">
+      <c r="J130">
         <v>33.5</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>25</v>
       </c>
       <c r="B131" t="s">
         <v>15</v>
       </c>
-      <c r="C131" t="s">
-        <v>30</v>
+      <c r="C131" s="4">
+        <v>46183</v>
       </c>
       <c r="D131" t="s">
-        <v>28</v>
-      </c>
-      <c r="E131">
-        <v>2026</v>
-      </c>
-      <c r="F131" t="s">
-        <v>31</v>
-      </c>
-      <c r="G131">
+        <v>30</v>
+      </c>
+      <c r="E131" t="s">
+        <v>28</v>
+      </c>
+      <c r="F131">
+        <v>2026</v>
+      </c>
+      <c r="G131" t="s">
+        <v>31</v>
+      </c>
+      <c r="H131">
         <v>5</v>
       </c>
-      <c r="H131">
+      <c r="I131">
         <v>27.25</v>
       </c>
-      <c r="I131">
+      <c r="J131">
         <v>30.5</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>25</v>
       </c>
       <c r="B132" t="s">
         <v>16</v>
       </c>
-      <c r="C132" t="s">
-        <v>30</v>
+      <c r="C132" s="4">
+        <v>46183</v>
       </c>
       <c r="D132" t="s">
-        <v>28</v>
-      </c>
-      <c r="E132">
-        <v>2026</v>
-      </c>
-      <c r="F132" t="s">
-        <v>31</v>
-      </c>
-      <c r="G132">
+        <v>30</v>
+      </c>
+      <c r="E132" t="s">
+        <v>28</v>
+      </c>
+      <c r="F132">
+        <v>2026</v>
+      </c>
+      <c r="G132" t="s">
+        <v>31</v>
+      </c>
+      <c r="H132">
         <v>20</v>
       </c>
-      <c r="H132" s="3">
+      <c r="I132" s="3">
         <v>34.875</v>
       </c>
-      <c r="I132">
+      <c r="J132">
         <v>42.5</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>25</v>
       </c>
       <c r="B133" t="s">
         <v>16</v>
       </c>
-      <c r="C133" t="s">
-        <v>30</v>
+      <c r="C133" s="4">
+        <v>46183</v>
       </c>
       <c r="D133" t="s">
-        <v>28</v>
-      </c>
-      <c r="E133">
-        <v>2026</v>
-      </c>
-      <c r="F133" t="s">
+        <v>30</v>
+      </c>
+      <c r="E133" t="s">
+        <v>28</v>
+      </c>
+      <c r="F133">
+        <v>2026</v>
+      </c>
+      <c r="G133" t="s">
         <v>33</v>
       </c>
-      <c r="G133">
+      <c r="H133">
         <v>75</v>
       </c>
-      <c r="H133">
+      <c r="I133">
         <v>16.25</v>
       </c>
-      <c r="I133">
+      <c r="J133">
         <v>19</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>25</v>
       </c>
       <c r="B134" t="s">
         <v>17</v>
       </c>
-      <c r="C134" t="s">
-        <v>30</v>
+      <c r="C134" s="4">
+        <v>46183</v>
       </c>
       <c r="D134" t="s">
-        <v>28</v>
-      </c>
-      <c r="E134">
-        <v>2026</v>
-      </c>
-      <c r="F134" t="s">
-        <v>31</v>
-      </c>
-      <c r="G134">
+        <v>30</v>
+      </c>
+      <c r="E134" t="s">
+        <v>28</v>
+      </c>
+      <c r="F134">
+        <v>2026</v>
+      </c>
+      <c r="G134" t="s">
+        <v>31</v>
+      </c>
+      <c r="H134">
         <v>20</v>
       </c>
-      <c r="H134">
+      <c r="I134">
         <v>24.83</v>
       </c>
-      <c r="I134">
+      <c r="J134">
         <v>32.5</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>25</v>
       </c>
       <c r="B135" t="s">
         <v>17</v>
       </c>
-      <c r="C135" t="s">
-        <v>30</v>
+      <c r="C135" s="4">
+        <v>46183</v>
       </c>
       <c r="D135" t="s">
-        <v>28</v>
-      </c>
-      <c r="E135">
-        <v>2026</v>
-      </c>
-      <c r="F135" t="s">
+        <v>30</v>
+      </c>
+      <c r="E135" t="s">
+        <v>28</v>
+      </c>
+      <c r="F135">
+        <v>2026</v>
+      </c>
+      <c r="G135" t="s">
         <v>33</v>
       </c>
-      <c r="G135">
+      <c r="H135">
         <v>75</v>
       </c>
-      <c r="H135">
+      <c r="I135">
         <v>16.375</v>
       </c>
-      <c r="I135">
+      <c r="J135">
         <v>19</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>25</v>
       </c>
       <c r="B136" t="s">
         <v>18</v>
       </c>
-      <c r="C136" t="s">
-        <v>30</v>
+      <c r="C136" s="4">
+        <v>46183</v>
       </c>
       <c r="D136" t="s">
-        <v>28</v>
-      </c>
-      <c r="E136">
-        <v>2026</v>
-      </c>
-      <c r="F136" t="s">
-        <v>31</v>
-      </c>
-      <c r="G136">
+        <v>30</v>
+      </c>
+      <c r="E136" t="s">
+        <v>28</v>
+      </c>
+      <c r="F136">
+        <v>2026</v>
+      </c>
+      <c r="G136" t="s">
+        <v>31</v>
+      </c>
+      <c r="H136">
         <v>40</v>
       </c>
-      <c r="H136">
+      <c r="I136">
         <v>43</v>
       </c>
-      <c r="I136">
+      <c r="J136">
         <v>53</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>25</v>
       </c>
       <c r="B137" t="s">
         <v>18</v>
       </c>
-      <c r="C137" t="s">
-        <v>30</v>
+      <c r="C137" s="4">
+        <v>46183</v>
       </c>
       <c r="D137" t="s">
-        <v>28</v>
-      </c>
-      <c r="E137">
-        <v>2026</v>
-      </c>
-      <c r="F137" t="s">
+        <v>30</v>
+      </c>
+      <c r="E137" t="s">
+        <v>28</v>
+      </c>
+      <c r="F137">
+        <v>2026</v>
+      </c>
+      <c r="G137" t="s">
         <v>33</v>
       </c>
-      <c r="G137">
+      <c r="H137">
         <v>50</v>
       </c>
-      <c r="H137">
+      <c r="I137">
         <v>21.875</v>
       </c>
-      <c r="I137">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J137">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>25</v>
       </c>
       <c r="B138" t="s">
         <v>18</v>
       </c>
-      <c r="C138" t="s">
-        <v>30</v>
+      <c r="C138" s="4">
+        <v>46183</v>
       </c>
       <c r="D138" t="s">
-        <v>28</v>
-      </c>
-      <c r="E138">
-        <v>2026</v>
-      </c>
-      <c r="F138" t="s">
+        <v>30</v>
+      </c>
+      <c r="E138" t="s">
+        <v>28</v>
+      </c>
+      <c r="F138">
+        <v>2026</v>
+      </c>
+      <c r="G138" t="s">
         <v>35</v>
       </c>
-      <c r="G138">
+      <c r="H138">
         <v>10</v>
       </c>
-      <c r="H138">
+      <c r="I138">
         <v>53.167000000000002</v>
       </c>
-      <c r="I138">
+      <c r="J138">
         <v>60</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>25</v>
       </c>
       <c r="B139" t="s">
         <v>20</v>
       </c>
-      <c r="C139" t="s">
-        <v>30</v>
+      <c r="C139" s="4">
+        <v>46183</v>
       </c>
       <c r="D139" t="s">
-        <v>28</v>
-      </c>
-      <c r="E139">
-        <v>2026</v>
-      </c>
-      <c r="F139" t="s">
-        <v>31</v>
-      </c>
-      <c r="G139">
+        <v>30</v>
+      </c>
+      <c r="E139" t="s">
+        <v>28</v>
+      </c>
+      <c r="F139">
+        <v>2026</v>
+      </c>
+      <c r="G139" t="s">
+        <v>31</v>
+      </c>
+      <c r="H139">
         <v>35</v>
       </c>
-      <c r="H139">
+      <c r="I139">
         <v>48</v>
       </c>
-      <c r="I139">
+      <c r="J139">
         <v>64</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>25</v>
       </c>
       <c r="B140" t="s">
         <v>20</v>
       </c>
-      <c r="C140" t="s">
-        <v>30</v>
+      <c r="C140" s="4">
+        <v>46183</v>
       </c>
       <c r="D140" t="s">
-        <v>28</v>
-      </c>
-      <c r="E140">
-        <v>2026</v>
-      </c>
-      <c r="F140" t="s">
+        <v>30</v>
+      </c>
+      <c r="E140" t="s">
+        <v>28</v>
+      </c>
+      <c r="F140">
+        <v>2026</v>
+      </c>
+      <c r="G140" t="s">
         <v>33</v>
       </c>
-      <c r="G140">
+      <c r="H140">
         <v>55</v>
       </c>
-      <c r="H140">
+      <c r="I140">
         <v>20.75</v>
       </c>
-      <c r="I140">
+      <c r="J140">
         <v>23</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>25</v>
       </c>
       <c r="B141" t="s">
         <v>20</v>
       </c>
-      <c r="C141" t="s">
-        <v>30</v>
+      <c r="C141" s="4">
+        <v>46183</v>
       </c>
       <c r="D141" t="s">
-        <v>28</v>
-      </c>
-      <c r="E141">
-        <v>2026</v>
-      </c>
-      <c r="F141" t="s">
+        <v>30</v>
+      </c>
+      <c r="E141" t="s">
+        <v>28</v>
+      </c>
+      <c r="F141">
+        <v>2026</v>
+      </c>
+      <c r="G141" t="s">
         <v>35</v>
       </c>
-      <c r="G141">
+      <c r="H141">
         <v>15</v>
       </c>
-      <c r="H141">
+      <c r="I141">
         <v>48.75</v>
       </c>
-      <c r="I141">
+      <c r="J141">
         <v>53</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>25</v>
       </c>
       <c r="B142" t="s">
         <v>19</v>
       </c>
-      <c r="C142" t="s">
-        <v>30</v>
+      <c r="C142" s="4">
+        <v>46183</v>
       </c>
       <c r="D142" t="s">
-        <v>28</v>
-      </c>
-      <c r="E142">
-        <v>2026</v>
-      </c>
-      <c r="F142" t="s">
-        <v>31</v>
-      </c>
-      <c r="G142">
-        <v>25</v>
+        <v>30</v>
+      </c>
+      <c r="E142" t="s">
+        <v>28</v>
+      </c>
+      <c r="F142">
+        <v>2026</v>
+      </c>
+      <c r="G142" t="s">
+        <v>31</v>
       </c>
       <c r="H142">
+        <v>25</v>
+      </c>
+      <c r="I142">
         <v>48.75</v>
       </c>
-      <c r="I142">
+      <c r="J142">
         <v>51</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>25</v>
       </c>
       <c r="B143" t="s">
         <v>19</v>
       </c>
-      <c r="C143" t="s">
-        <v>30</v>
+      <c r="C143" s="4">
+        <v>46183</v>
       </c>
       <c r="D143" t="s">
-        <v>28</v>
-      </c>
-      <c r="E143">
-        <v>2026</v>
-      </c>
-      <c r="F143" t="s">
+        <v>30</v>
+      </c>
+      <c r="E143" t="s">
+        <v>28</v>
+      </c>
+      <c r="F143">
+        <v>2026</v>
+      </c>
+      <c r="G143" t="s">
         <v>35</v>
       </c>
-      <c r="G143">
+      <c r="H143">
         <v>35</v>
       </c>
-      <c r="H143">
+      <c r="I143">
         <v>55.25</v>
       </c>
-      <c r="I143">
+      <c r="J143">
         <v>62</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>25</v>
       </c>
       <c r="B144" t="s">
         <v>19</v>
       </c>
-      <c r="C144" t="s">
-        <v>30</v>
+      <c r="C144" s="4">
+        <v>46183</v>
       </c>
       <c r="D144" t="s">
-        <v>28</v>
-      </c>
-      <c r="E144">
-        <v>2026</v>
-      </c>
-      <c r="F144" t="s">
+        <v>30</v>
+      </c>
+      <c r="E144" t="s">
+        <v>28</v>
+      </c>
+      <c r="F144">
+        <v>2026</v>
+      </c>
+      <c r="G144" t="s">
         <v>33</v>
       </c>
-      <c r="G144">
+      <c r="H144">
         <v>45</v>
       </c>
-      <c r="H144">
+      <c r="I144">
         <v>25.5</v>
       </c>
-      <c r="I144">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J144">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>25</v>
       </c>
       <c r="B145" t="s">
         <v>21</v>
       </c>
-      <c r="C145" t="s">
-        <v>30</v>
+      <c r="C145" s="4">
+        <v>46183</v>
       </c>
       <c r="D145" t="s">
-        <v>28</v>
-      </c>
-      <c r="E145">
-        <v>2026</v>
-      </c>
-      <c r="F145" t="s">
+        <v>30</v>
+      </c>
+      <c r="E145" t="s">
+        <v>28</v>
+      </c>
+      <c r="F145">
+        <v>2026</v>
+      </c>
+      <c r="G145" t="s">
         <v>35</v>
       </c>
-      <c r="G145">
+      <c r="H145">
         <v>20</v>
       </c>
-      <c r="H145">
+      <c r="I145">
         <v>53.75</v>
       </c>
-      <c r="I145">
+      <c r="J145">
         <v>57</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>25</v>
       </c>
       <c r="B146" t="s">
         <v>21</v>
       </c>
-      <c r="C146" t="s">
-        <v>30</v>
+      <c r="C146" s="4">
+        <v>46183</v>
       </c>
       <c r="D146" t="s">
-        <v>28</v>
-      </c>
-      <c r="E146">
-        <v>2026</v>
-      </c>
-      <c r="F146" t="s">
-        <v>31</v>
-      </c>
-      <c r="G146">
-        <v>25</v>
+        <v>30</v>
+      </c>
+      <c r="E146" t="s">
+        <v>28</v>
+      </c>
+      <c r="F146">
+        <v>2026</v>
+      </c>
+      <c r="G146" t="s">
+        <v>31</v>
       </c>
       <c r="H146">
+        <v>25</v>
+      </c>
+      <c r="I146">
         <v>33.75</v>
       </c>
-      <c r="I146">
+      <c r="J146">
         <v>38</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>25</v>
       </c>
       <c r="B147" t="s">
         <v>21</v>
       </c>
-      <c r="C147" t="s">
-        <v>30</v>
+      <c r="C147" s="4">
+        <v>46183</v>
       </c>
       <c r="D147" t="s">
-        <v>28</v>
-      </c>
-      <c r="E147">
-        <v>2026</v>
-      </c>
-      <c r="F147" t="s">
+        <v>30</v>
+      </c>
+      <c r="E147" t="s">
+        <v>28</v>
+      </c>
+      <c r="F147">
+        <v>2026</v>
+      </c>
+      <c r="G147" t="s">
         <v>33</v>
       </c>
-      <c r="G147">
+      <c r="H147">
         <v>65</v>
       </c>
-      <c r="H147">
+      <c r="I147">
         <v>23.375</v>
       </c>
-      <c r="I147">
+      <c r="J147">
         <v>24.5</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>25</v>
       </c>
       <c r="B148" t="s">
         <v>22</v>
       </c>
-      <c r="C148" t="s">
-        <v>30</v>
+      <c r="C148" s="4">
+        <v>46183</v>
       </c>
       <c r="D148" t="s">
-        <v>28</v>
-      </c>
-      <c r="E148">
-        <v>2026</v>
-      </c>
-      <c r="F148" t="s">
+        <v>30</v>
+      </c>
+      <c r="E148" t="s">
+        <v>28</v>
+      </c>
+      <c r="F148">
+        <v>2026</v>
+      </c>
+      <c r="G148" t="s">
         <v>34</v>
       </c>
-      <c r="G148">
+      <c r="H148">
         <v>90</v>
       </c>
-      <c r="H148">
-        <v>31</v>
-      </c>
       <c r="I148">
+        <v>31</v>
+      </c>
+      <c r="J148">
         <v>33</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>25</v>
       </c>
       <c r="B149" t="s">
         <v>22</v>
       </c>
-      <c r="C149" t="s">
-        <v>30</v>
+      <c r="C149" s="4">
+        <v>46183</v>
       </c>
       <c r="D149" t="s">
-        <v>28</v>
-      </c>
-      <c r="E149">
-        <v>2026</v>
-      </c>
-      <c r="F149" t="s">
+        <v>30</v>
+      </c>
+      <c r="E149" t="s">
+        <v>28</v>
+      </c>
+      <c r="F149">
+        <v>2026</v>
+      </c>
+      <c r="G149" t="s">
         <v>35</v>
       </c>
-      <c r="G149">
+      <c r="H149">
         <v>5</v>
-      </c>
-      <c r="H149">
-        <v>56</v>
       </c>
       <c r="I149">
         <v>56</v>
       </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J149">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>26</v>
       </c>
       <c r="B150" t="s">
         <v>10</v>
       </c>
-      <c r="C150" t="s">
-        <v>30</v>
+      <c r="C150" s="4">
+        <v>46185</v>
       </c>
       <c r="D150" t="s">
-        <v>28</v>
-      </c>
-      <c r="E150">
-        <v>2026</v>
-      </c>
-      <c r="F150" t="s">
-        <v>31</v>
-      </c>
-      <c r="G150">
+        <v>30</v>
+      </c>
+      <c r="E150" t="s">
+        <v>28</v>
+      </c>
+      <c r="F150">
+        <v>2026</v>
+      </c>
+      <c r="G150" t="s">
+        <v>31</v>
+      </c>
+      <c r="H150">
         <v>35</v>
       </c>
-      <c r="H150">
+      <c r="I150">
         <v>57</v>
       </c>
-      <c r="I150">
+      <c r="J150">
         <v>66</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>26</v>
       </c>
       <c r="B151" t="s">
         <v>10</v>
       </c>
-      <c r="C151" t="s">
-        <v>30</v>
+      <c r="C151" s="4">
+        <v>46185</v>
       </c>
       <c r="D151" t="s">
-        <v>28</v>
-      </c>
-      <c r="E151">
-        <v>2026</v>
-      </c>
-      <c r="F151" t="s">
+        <v>30</v>
+      </c>
+      <c r="E151" t="s">
+        <v>28</v>
+      </c>
+      <c r="F151">
+        <v>2026</v>
+      </c>
+      <c r="G151" t="s">
         <v>35</v>
       </c>
-      <c r="G151">
+      <c r="H151">
         <v>35</v>
       </c>
-      <c r="H151">
+      <c r="I151">
         <v>67.125</v>
       </c>
-      <c r="I151">
+      <c r="J151">
         <v>76</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>26</v>
       </c>
       <c r="B152" t="s">
         <v>11</v>
       </c>
-      <c r="C152" t="s">
-        <v>30</v>
+      <c r="C152" s="4">
+        <v>46185</v>
       </c>
       <c r="D152" t="s">
-        <v>28</v>
-      </c>
-      <c r="E152">
-        <v>2026</v>
-      </c>
-      <c r="F152" t="s">
-        <v>31</v>
-      </c>
-      <c r="G152">
+        <v>30</v>
+      </c>
+      <c r="E152" t="s">
+        <v>28</v>
+      </c>
+      <c r="F152">
+        <v>2026</v>
+      </c>
+      <c r="G152" t="s">
+        <v>31</v>
+      </c>
+      <c r="H152">
         <v>75</v>
       </c>
-      <c r="H152">
+      <c r="I152">
         <v>51.625</v>
       </c>
-      <c r="I152">
+      <c r="J152">
         <v>69.5</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>26</v>
       </c>
       <c r="B153" t="s">
         <v>12</v>
       </c>
-      <c r="C153" t="s">
-        <v>30</v>
+      <c r="C153" s="4">
+        <v>46185</v>
       </c>
       <c r="D153" t="s">
-        <v>28</v>
-      </c>
-      <c r="E153">
-        <v>2026</v>
-      </c>
-      <c r="F153" t="s">
-        <v>31</v>
-      </c>
-      <c r="G153">
+        <v>30</v>
+      </c>
+      <c r="E153" t="s">
+        <v>28</v>
+      </c>
+      <c r="F153">
+        <v>2026</v>
+      </c>
+      <c r="G153" t="s">
+        <v>31</v>
+      </c>
+      <c r="H153">
         <v>60</v>
       </c>
-      <c r="H153">
+      <c r="I153">
         <v>61.125</v>
       </c>
-      <c r="I153">
+      <c r="J153">
         <v>65</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>26</v>
       </c>
       <c r="B154" t="s">
         <v>23</v>
       </c>
-      <c r="C154" t="s">
-        <v>30</v>
+      <c r="C154" s="4">
+        <v>46185</v>
       </c>
       <c r="D154" t="s">
-        <v>28</v>
-      </c>
-      <c r="E154">
-        <v>2026</v>
-      </c>
-      <c r="F154" t="s">
-        <v>31</v>
-      </c>
-      <c r="G154">
+        <v>30</v>
+      </c>
+      <c r="E154" t="s">
+        <v>28</v>
+      </c>
+      <c r="F154">
+        <v>2026</v>
+      </c>
+      <c r="G154" t="s">
+        <v>31</v>
+      </c>
+      <c r="H154">
         <v>65</v>
       </c>
-      <c r="H154">
+      <c r="I154">
         <v>46</v>
       </c>
-      <c r="I154">
+      <c r="J154">
         <v>55</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>26</v>
       </c>
       <c r="B155" t="s">
         <v>13</v>
       </c>
-      <c r="C155" t="s">
-        <v>30</v>
+      <c r="C155" s="4">
+        <v>46185</v>
       </c>
       <c r="D155" t="s">
-        <v>28</v>
-      </c>
-      <c r="E155">
-        <v>2026</v>
-      </c>
-      <c r="F155" t="s">
-        <v>31</v>
-      </c>
-      <c r="G155">
+        <v>30</v>
+      </c>
+      <c r="E155" t="s">
+        <v>28</v>
+      </c>
+      <c r="F155">
+        <v>2026</v>
+      </c>
+      <c r="G155" t="s">
+        <v>31</v>
+      </c>
+      <c r="H155">
         <v>80</v>
       </c>
-      <c r="H155">
+      <c r="I155">
         <v>58.75</v>
       </c>
-      <c r="I155">
+      <c r="J155">
         <v>69</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>26</v>
       </c>
       <c r="B156" t="s">
         <v>14</v>
       </c>
-      <c r="C156" t="s">
-        <v>30</v>
+      <c r="C156" s="4">
+        <v>46185</v>
       </c>
       <c r="D156" t="s">
-        <v>28</v>
-      </c>
-      <c r="E156">
-        <v>2026</v>
-      </c>
-      <c r="F156" t="s">
-        <v>31</v>
-      </c>
-      <c r="G156">
+        <v>30</v>
+      </c>
+      <c r="E156" t="s">
+        <v>28</v>
+      </c>
+      <c r="F156">
+        <v>2026</v>
+      </c>
+      <c r="G156" t="s">
+        <v>31</v>
+      </c>
+      <c r="H156">
         <v>95</v>
       </c>
-      <c r="H156">
+      <c r="I156">
         <v>55.5</v>
       </c>
-      <c r="I156">
+      <c r="J156">
         <v>58.5</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>26</v>
       </c>
       <c r="B157" t="s">
         <v>15</v>
       </c>
-      <c r="C157" t="s">
-        <v>30</v>
+      <c r="C157" s="4">
+        <v>46185</v>
       </c>
       <c r="D157" t="s">
-        <v>28</v>
-      </c>
-      <c r="E157">
-        <v>2026</v>
-      </c>
-      <c r="F157" t="s">
-        <v>31</v>
-      </c>
-      <c r="G157">
+        <v>30</v>
+      </c>
+      <c r="E157" t="s">
+        <v>28</v>
+      </c>
+      <c r="F157">
+        <v>2026</v>
+      </c>
+      <c r="G157" t="s">
+        <v>31</v>
+      </c>
+      <c r="H157">
         <v>95</v>
       </c>
-      <c r="H157">
+      <c r="I157">
         <v>49.125</v>
       </c>
-      <c r="I157">
+      <c r="J157">
         <v>60</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>26</v>
       </c>
       <c r="B158" t="s">
         <v>16</v>
       </c>
-      <c r="C158" t="s">
-        <v>30</v>
+      <c r="C158" s="4">
+        <v>46185</v>
       </c>
       <c r="D158" t="s">
-        <v>28</v>
-      </c>
-      <c r="E158">
-        <v>2026</v>
-      </c>
-      <c r="F158" t="s">
+        <v>30</v>
+      </c>
+      <c r="E158" t="s">
+        <v>28</v>
+      </c>
+      <c r="F158">
+        <v>2026</v>
+      </c>
+      <c r="G158" t="s">
         <v>35</v>
       </c>
-      <c r="G158">
+      <c r="H158">
         <v>40</v>
       </c>
-      <c r="H158">
+      <c r="I158">
         <v>77.75</v>
       </c>
-      <c r="I158">
+      <c r="J158">
         <v>85</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>26</v>
       </c>
       <c r="B159" t="s">
         <v>16</v>
       </c>
-      <c r="C159" t="s">
-        <v>30</v>
+      <c r="C159" s="4">
+        <v>46185</v>
       </c>
       <c r="D159" t="s">
-        <v>28</v>
-      </c>
-      <c r="E159">
-        <v>2026</v>
-      </c>
-      <c r="F159" t="s">
-        <v>31</v>
-      </c>
-      <c r="G159">
-        <v>30</v>
+        <v>30</v>
+      </c>
+      <c r="E159" t="s">
+        <v>28</v>
+      </c>
+      <c r="F159">
+        <v>2026</v>
+      </c>
+      <c r="G159" t="s">
+        <v>31</v>
       </c>
       <c r="H159">
+        <v>30</v>
+      </c>
+      <c r="I159">
         <v>53.75</v>
       </c>
-      <c r="I159">
+      <c r="J159">
         <v>56</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>26</v>
       </c>
       <c r="B160" t="s">
         <v>17</v>
       </c>
-      <c r="C160" t="s">
-        <v>30</v>
+      <c r="C160" s="4">
+        <v>46185</v>
       </c>
       <c r="D160" t="s">
-        <v>28</v>
-      </c>
-      <c r="E160">
-        <v>2026</v>
-      </c>
-      <c r="F160" t="s">
+        <v>30</v>
+      </c>
+      <c r="E160" t="s">
+        <v>28</v>
+      </c>
+      <c r="F160">
+        <v>2026</v>
+      </c>
+      <c r="G160" t="s">
         <v>35</v>
       </c>
-      <c r="G160">
+      <c r="H160">
         <v>35</v>
       </c>
-      <c r="H160">
+      <c r="I160">
         <v>87.25</v>
       </c>
-      <c r="I160">
+      <c r="J160">
         <v>93</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>26</v>
       </c>
       <c r="B161" t="s">
         <v>17</v>
       </c>
-      <c r="C161" t="s">
-        <v>30</v>
+      <c r="C161" s="4">
+        <v>46185</v>
       </c>
       <c r="D161" t="s">
-        <v>28</v>
-      </c>
-      <c r="E161">
-        <v>2026</v>
-      </c>
-      <c r="F161" t="s">
-        <v>31</v>
-      </c>
-      <c r="G161">
-        <v>30</v>
+        <v>30</v>
+      </c>
+      <c r="E161" t="s">
+        <v>28</v>
+      </c>
+      <c r="F161">
+        <v>2026</v>
+      </c>
+      <c r="G161" t="s">
+        <v>31</v>
       </c>
       <c r="H161">
+        <v>30</v>
+      </c>
+      <c r="I161">
         <v>54.5</v>
       </c>
-      <c r="I161">
+      <c r="J161">
         <v>68</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>26</v>
       </c>
       <c r="B162" t="s">
         <v>18</v>
       </c>
-      <c r="C162" t="s">
-        <v>30</v>
+      <c r="C162" s="4">
+        <v>46185</v>
       </c>
       <c r="D162" t="s">
-        <v>28</v>
-      </c>
-      <c r="E162">
-        <v>2026</v>
-      </c>
-      <c r="F162" t="s">
-        <v>31</v>
-      </c>
-      <c r="G162">
+        <v>30</v>
+      </c>
+      <c r="E162" t="s">
+        <v>28</v>
+      </c>
+      <c r="F162">
+        <v>2026</v>
+      </c>
+      <c r="G162" t="s">
+        <v>31</v>
+      </c>
+      <c r="H162">
         <v>80</v>
       </c>
-      <c r="H162">
+      <c r="I162">
         <v>50</v>
       </c>
-      <c r="I162">
+      <c r="J162">
         <v>55</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>26</v>
       </c>
       <c r="B163" t="s">
         <v>20</v>
       </c>
-      <c r="C163" t="s">
-        <v>30</v>
+      <c r="C163" s="4">
+        <v>46185</v>
       </c>
       <c r="D163" t="s">
-        <v>28</v>
-      </c>
-      <c r="E163">
-        <v>2026</v>
-      </c>
-      <c r="F163" t="s">
-        <v>31</v>
-      </c>
-      <c r="G163">
+        <v>30</v>
+      </c>
+      <c r="E163" t="s">
+        <v>28</v>
+      </c>
+      <c r="F163">
+        <v>2026</v>
+      </c>
+      <c r="G163" t="s">
+        <v>31</v>
+      </c>
+      <c r="H163">
         <v>90</v>
       </c>
-      <c r="H163">
+      <c r="I163">
         <v>52.125</v>
       </c>
-      <c r="I163">
+      <c r="J163">
         <v>56</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>26</v>
       </c>
       <c r="B164" t="s">
         <v>19</v>
       </c>
-      <c r="C164" t="s">
-        <v>30</v>
+      <c r="C164" s="4">
+        <v>46185</v>
       </c>
       <c r="D164" t="s">
-        <v>28</v>
-      </c>
-      <c r="E164">
-        <v>2026</v>
-      </c>
-      <c r="F164" t="s">
-        <v>31</v>
-      </c>
-      <c r="G164">
+        <v>30</v>
+      </c>
+      <c r="E164" t="s">
+        <v>28</v>
+      </c>
+      <c r="F164">
+        <v>2026</v>
+      </c>
+      <c r="G164" t="s">
+        <v>31</v>
+      </c>
+      <c r="H164">
         <v>85</v>
       </c>
-      <c r="H164">
+      <c r="I164">
         <v>61.75</v>
       </c>
-      <c r="I164">
+      <c r="J164">
         <v>65</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>26</v>
       </c>
       <c r="B165" t="s">
         <v>21</v>
       </c>
-      <c r="C165" t="s">
-        <v>30</v>
+      <c r="C165" s="4">
+        <v>46185</v>
       </c>
       <c r="D165" t="s">
-        <v>28</v>
-      </c>
-      <c r="E165">
-        <v>2026</v>
-      </c>
-      <c r="F165" t="s">
-        <v>31</v>
-      </c>
-      <c r="G165">
+        <v>30</v>
+      </c>
+      <c r="E165" t="s">
+        <v>28</v>
+      </c>
+      <c r="F165">
+        <v>2026</v>
+      </c>
+      <c r="G165" t="s">
+        <v>31</v>
+      </c>
+      <c r="H165">
         <v>95</v>
       </c>
-      <c r="H165">
+      <c r="I165">
         <v>56</v>
       </c>
-      <c r="I165">
+      <c r="J165">
         <v>59.5</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>26</v>
       </c>
       <c r="B166" t="s">
         <v>22</v>
       </c>
-      <c r="C166" t="s">
-        <v>30</v>
+      <c r="C166" s="4">
+        <v>46185</v>
       </c>
       <c r="D166" t="s">
-        <v>28</v>
-      </c>
-      <c r="E166">
-        <v>2026</v>
-      </c>
-      <c r="F166" t="s">
-        <v>31</v>
-      </c>
-      <c r="G166">
+        <v>30</v>
+      </c>
+      <c r="E166" t="s">
+        <v>28</v>
+      </c>
+      <c r="F166">
+        <v>2026</v>
+      </c>
+      <c r="G166" t="s">
+        <v>31</v>
+      </c>
+      <c r="H166">
         <v>95</v>
       </c>
-      <c r="H166">
+      <c r="I166">
         <v>50.25</v>
       </c>
-      <c r="I166">
+      <c r="J166">
         <v>58</v>
       </c>
     </row>

--- a/data/veg_final.xlsx
+++ b/data/veg_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailsfsu-my.sharepoint.com/personal/924318106_sfsu_edu/Documents/ProjectData/GitHub/DepositionSFB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="909" documentId="8_{59CBD094-BD12-4802-82EC-BFBFD8F2B4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21FBB276-CC88-4175-937F-9288CFC7A9B4}"/>
+  <xr:revisionPtr revIDLastSave="1440" documentId="8_{59CBD094-BD12-4802-82EC-BFBFD8F2B4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7C4A0BD-5660-4879-AAED-5EA9C13969A3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{09619B10-7E90-4FB8-AF45-F23757B21A39}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{09619B10-7E90-4FB8-AF45-F23757B21A39}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,32 +44,7 @@
     <author>Savannah Miller</author>
   </authors>
   <commentList>
-    <comment ref="G43" authorId="0" shapeId="0" xr:uid="{389FEA95-7DDE-4177-A949-5F8D55991682}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Savannah Miller:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-SPECIES ID QUESTIONED IN THE NOTES
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G73" authorId="0" shapeId="0" xr:uid="{318148E9-2D79-44B9-82CD-E08367CB215B}">
+    <comment ref="G118" authorId="0" shapeId="0" xr:uid="{318148E9-2D79-44B9-82CD-E08367CB215B}">
       <text>
         <r>
           <rPr>
@@ -98,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="40">
   <si>
     <t>Site</t>
   </si>
@@ -208,20 +183,23 @@
     <t>SPFO</t>
   </si>
   <si>
-    <t>Seaweed</t>
-  </si>
-  <si>
     <t>NA</t>
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>LICA</t>
+  </si>
+  <si>
+    <t>GRST</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,19 +234,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -647,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C24C2CBB-D018-4603-A1EC-5007D4D3E68F}">
-  <dimension ref="A1:J166"/>
+  <dimension ref="A1:J247"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -662,7 +627,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -723,7 +688,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4">
         <v>46074</v>
@@ -738,16 +703,16 @@
         <v>2026</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H3">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="I3">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="J3">
-        <v>39</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -755,7 +720,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="4">
         <v>46074</v>
@@ -773,13 +738,13 @@
         <v>31</v>
       </c>
       <c r="H4">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I4">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J4">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -787,7 +752,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C5" s="4">
         <v>46074</v>
@@ -802,16 +767,16 @@
         <v>2026</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H5">
-        <v>90</v>
-      </c>
-      <c r="I5">
-        <v>34</v>
-      </c>
-      <c r="J5">
-        <v>41.5</v>
+        <v>15</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -819,7 +784,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="4">
         <v>46074</v>
@@ -834,16 +799,16 @@
         <v>2026</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="J6">
-        <v>18.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -851,7 +816,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="4">
         <v>46074</v>
@@ -866,15 +831,15 @@
         <v>2026</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>20</v>
-      </c>
-      <c r="I7">
-        <v>25</v>
-      </c>
-      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="I7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" t="s">
         <v>36</v>
       </c>
     </row>
@@ -883,7 +848,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C8" s="4">
         <v>46074</v>
@@ -898,16 +863,16 @@
         <v>2026</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H8">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="J8">
-        <v>18.5</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -915,7 +880,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="4">
         <v>46074</v>
@@ -930,16 +895,16 @@
         <v>2026</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H9">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I9">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -947,7 +912,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" s="4">
         <v>46074</v>
@@ -965,13 +930,13 @@
         <v>31</v>
       </c>
       <c r="H10">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="I10">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="J10">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -979,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C11" s="4">
         <v>46074</v>
@@ -994,16 +959,16 @@
         <v>2026</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H11">
-        <v>60</v>
-      </c>
-      <c r="I11">
-        <v>26</v>
-      </c>
-      <c r="J11">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="I11" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -1011,7 +976,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C12" s="4">
         <v>46074</v>
@@ -1026,16 +991,16 @@
         <v>2026</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H12">
-        <v>10</v>
-      </c>
-      <c r="I12">
-        <v>66</v>
-      </c>
-      <c r="J12">
-        <v>75</v>
+        <v>5</v>
+      </c>
+      <c r="I12" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -1043,7 +1008,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C13" s="4">
         <v>46074</v>
@@ -1058,16 +1023,16 @@
         <v>2026</v>
       </c>
       <c r="G13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H13">
-        <v>40</v>
-      </c>
-      <c r="I13">
-        <v>40</v>
-      </c>
-      <c r="J13">
-        <v>59</v>
+        <v>10</v>
+      </c>
+      <c r="I13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -1075,7 +1040,7 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C14" s="4">
         <v>46074</v>
@@ -1090,16 +1055,16 @@
         <v>2026</v>
       </c>
       <c r="G14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H14">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I14">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="J14">
-        <v>40</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -1107,7 +1072,7 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C15" s="4">
         <v>46074</v>
@@ -1125,13 +1090,13 @@
         <v>31</v>
       </c>
       <c r="H15">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="I15">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J15">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1139,7 +1104,7 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C16" s="4">
         <v>46074</v>
@@ -1154,16 +1119,16 @@
         <v>2026</v>
       </c>
       <c r="G16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H16">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="I16">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J16">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -1171,7 +1136,7 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C17" s="4">
         <v>46074</v>
@@ -1186,16 +1151,16 @@
         <v>2026</v>
       </c>
       <c r="G17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H17">
-        <v>40</v>
-      </c>
-      <c r="I17">
-        <v>16</v>
-      </c>
-      <c r="J17">
-        <v>24</v>
+        <v>15</v>
+      </c>
+      <c r="I17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -1203,7 +1168,7 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C18" s="4">
         <v>46074</v>
@@ -1218,16 +1183,16 @@
         <v>2026</v>
       </c>
       <c r="G18" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H18">
         <v>20</v>
       </c>
-      <c r="I18">
-        <v>25</v>
-      </c>
-      <c r="J18">
-        <v>29</v>
+      <c r="I18" t="s">
+        <v>36</v>
+      </c>
+      <c r="J18" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -1235,7 +1200,7 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C19" s="4">
         <v>46074</v>
@@ -1253,21 +1218,18 @@
         <v>31</v>
       </c>
       <c r="H19">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="I19">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J19">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>9</v>
-      </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C20" s="4">
         <v>46074</v>
@@ -1282,27 +1244,24 @@
         <v>2026</v>
       </c>
       <c r="G20" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H20">
-        <v>70</v>
-      </c>
-      <c r="I20">
-        <v>38</v>
-      </c>
-      <c r="J20">
-        <v>42</v>
+        <v>20</v>
+      </c>
+      <c r="I20" t="s">
+        <v>36</v>
+      </c>
+      <c r="J20" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>24</v>
-      </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C21" s="4">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="D21" t="s">
         <v>29</v>
@@ -1317,24 +1276,24 @@
         <v>34</v>
       </c>
       <c r="H21">
-        <v>60</v>
-      </c>
-      <c r="I21">
-        <v>15</v>
-      </c>
-      <c r="J21">
-        <v>20.5</v>
+        <v>5</v>
+      </c>
+      <c r="I21" t="s">
+        <v>36</v>
+      </c>
+      <c r="J21" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C22" s="4">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="D22" t="s">
         <v>29</v>
@@ -1346,27 +1305,27 @@
         <v>2026</v>
       </c>
       <c r="G22" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H22">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I22">
         <v>26</v>
       </c>
       <c r="J22">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C23" s="4">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="D23" t="s">
         <v>29</v>
@@ -1378,27 +1337,27 @@
         <v>2026</v>
       </c>
       <c r="G23" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H23">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="J23">
-        <v>31</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C24" s="4">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="D24" t="s">
         <v>29</v>
@@ -1413,24 +1372,21 @@
         <v>31</v>
       </c>
       <c r="H24">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J24">
-        <v>42.5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C25" s="4">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="D25" t="s">
         <v>29</v>
@@ -1442,27 +1398,27 @@
         <v>2026</v>
       </c>
       <c r="G25" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H25">
-        <v>60</v>
-      </c>
-      <c r="I25">
-        <v>51</v>
-      </c>
-      <c r="J25">
-        <v>71</v>
+        <v>10</v>
+      </c>
+      <c r="I25" t="s">
+        <v>36</v>
+      </c>
+      <c r="J25" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C26" s="4">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="D26" t="s">
         <v>29</v>
@@ -1480,21 +1436,18 @@
         <v>80</v>
       </c>
       <c r="I26">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="J26">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>24</v>
-      </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C27" s="4">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="D27" t="s">
         <v>29</v>
@@ -1506,59 +1459,56 @@
         <v>2026</v>
       </c>
       <c r="G27" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H27">
-        <v>85</v>
-      </c>
-      <c r="I27">
-        <v>38</v>
-      </c>
-      <c r="J27">
-        <v>44</v>
+        <v>20</v>
+      </c>
+      <c r="I27" t="s">
+        <v>36</v>
+      </c>
+      <c r="J27" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>24</v>
-      </c>
       <c r="B28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="4">
+        <v>46074</v>
+      </c>
+      <c r="D28" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28">
+        <v>2026</v>
+      </c>
+      <c r="G28" t="s">
+        <v>33</v>
+      </c>
+      <c r="H28">
         <v>15</v>
       </c>
-      <c r="C28" s="4">
-        <v>46073</v>
-      </c>
-      <c r="D28" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" t="s">
-        <v>27</v>
-      </c>
-      <c r="F28">
-        <v>2026</v>
-      </c>
-      <c r="G28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H28">
-        <v>45</v>
-      </c>
-      <c r="I28">
-        <v>36</v>
-      </c>
-      <c r="J28">
-        <v>45</v>
+      <c r="I28" t="s">
+        <v>36</v>
+      </c>
+      <c r="J28" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C29" s="4">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="D29" t="s">
         <v>29</v>
@@ -1573,56 +1523,50 @@
         <v>31</v>
       </c>
       <c r="H29">
+        <v>80</v>
+      </c>
+      <c r="I29">
+        <v>37</v>
+      </c>
+      <c r="J29">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="4">
+        <v>46074</v>
+      </c>
+      <c r="D30" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30">
+        <v>2026</v>
+      </c>
+      <c r="G30" t="s">
+        <v>34</v>
+      </c>
+      <c r="H30">
         <v>10</v>
       </c>
-      <c r="I29">
-        <v>28</v>
-      </c>
-      <c r="J29">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="4">
-        <v>46073</v>
-      </c>
-      <c r="D30" t="s">
-        <v>29</v>
-      </c>
-      <c r="E30" t="s">
-        <v>27</v>
-      </c>
-      <c r="F30">
-        <v>2026</v>
-      </c>
-      <c r="G30" t="s">
-        <v>31</v>
-      </c>
-      <c r="H30">
-        <v>50</v>
-      </c>
-      <c r="I30">
-        <v>23.5</v>
-      </c>
-      <c r="J30">
-        <v>29</v>
+      <c r="I30" t="s">
+        <v>36</v>
+      </c>
+      <c r="J30" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>24</v>
-      </c>
       <c r="B31" t="s">
         <v>18</v>
       </c>
       <c r="C31" s="4">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="D31" t="s">
         <v>29</v>
@@ -1634,27 +1578,27 @@
         <v>2026</v>
       </c>
       <c r="G31" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H31">
-        <v>90</v>
-      </c>
-      <c r="I31">
-        <v>33</v>
-      </c>
-      <c r="J31">
-        <v>37.5</v>
+        <v>5</v>
+      </c>
+      <c r="I31" t="s">
+        <v>36</v>
+      </c>
+      <c r="J31" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B32" t="s">
         <v>20</v>
       </c>
       <c r="C32" s="4">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="D32" t="s">
         <v>29</v>
@@ -1669,24 +1613,21 @@
         <v>31</v>
       </c>
       <c r="H32">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="I32">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J32">
-        <v>45.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>24</v>
-      </c>
       <c r="B33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C33" s="4">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -1698,27 +1639,24 @@
         <v>2026</v>
       </c>
       <c r="G33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H33">
-        <v>75</v>
-      </c>
-      <c r="I33">
-        <v>37</v>
-      </c>
-      <c r="J33">
-        <v>43</v>
+        <v>10</v>
+      </c>
+      <c r="I33" t="s">
+        <v>36</v>
+      </c>
+      <c r="J33" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>24</v>
-      </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C34" s="4">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="D34" t="s">
         <v>29</v>
@@ -1730,155 +1668,149 @@
         <v>2026</v>
       </c>
       <c r="G34" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H34">
-        <v>70</v>
-      </c>
-      <c r="I34">
-        <v>41</v>
-      </c>
-      <c r="J34">
-        <v>46</v>
+        <v>25</v>
+      </c>
+      <c r="I34" t="s">
+        <v>36</v>
+      </c>
+      <c r="J34" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="4">
+        <v>46074</v>
+      </c>
+      <c r="D35" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35">
+        <v>2026</v>
+      </c>
+      <c r="G35" t="s">
+        <v>32</v>
+      </c>
+      <c r="H35">
+        <v>40</v>
+      </c>
+      <c r="I35">
+        <v>16</v>
+      </c>
+      <c r="J35">
         <v>24</v>
-      </c>
-      <c r="B35" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" s="4">
-        <v>46073</v>
-      </c>
-      <c r="D35" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" t="s">
-        <v>27</v>
-      </c>
-      <c r="F35">
-        <v>2026</v>
-      </c>
-      <c r="G35" t="s">
-        <v>31</v>
-      </c>
-      <c r="H35">
-        <v>90</v>
-      </c>
-      <c r="I35">
-        <v>37</v>
-      </c>
-      <c r="J35">
-        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="4">
+        <v>46074</v>
+      </c>
+      <c r="D36" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36">
+        <v>2026</v>
+      </c>
+      <c r="G36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36">
+        <v>20</v>
+      </c>
+      <c r="I36">
+        <v>25</v>
+      </c>
+      <c r="J36">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="4">
+        <v>46074</v>
+      </c>
+      <c r="D37" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37">
+        <v>2026</v>
+      </c>
+      <c r="G37" t="s">
+        <v>34</v>
+      </c>
+      <c r="H37">
         <v>10</v>
       </c>
-      <c r="C36" s="4">
-        <v>46060</v>
-      </c>
-      <c r="D36" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" t="s">
-        <v>27</v>
-      </c>
-      <c r="F36">
-        <v>2026</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="I37" t="s">
+        <v>36</v>
+      </c>
+      <c r="J37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="4">
+        <v>46074</v>
+      </c>
+      <c r="D38" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38">
+        <v>2026</v>
+      </c>
+      <c r="G38" t="s">
         <v>33</v>
       </c>
-      <c r="H36">
-        <v>70</v>
-      </c>
-      <c r="I36">
-        <v>14</v>
-      </c>
-      <c r="J36">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>25</v>
-      </c>
-      <c r="B37" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="4">
-        <v>46060</v>
-      </c>
-      <c r="D37" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" t="s">
-        <v>27</v>
-      </c>
-      <c r="F37">
-        <v>2026</v>
-      </c>
-      <c r="G37" t="s">
-        <v>31</v>
-      </c>
-      <c r="H37">
-        <v>15</v>
-      </c>
-      <c r="I37">
-        <v>22</v>
-      </c>
-      <c r="J37">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>25</v>
-      </c>
-      <c r="B38" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="4">
-        <v>46060</v>
-      </c>
-      <c r="D38" t="s">
-        <v>29</v>
-      </c>
-      <c r="E38" t="s">
-        <v>27</v>
-      </c>
-      <c r="F38">
-        <v>2026</v>
-      </c>
-      <c r="G38" t="s">
-        <v>31</v>
-      </c>
       <c r="H38">
-        <v>10</v>
-      </c>
-      <c r="I38">
-        <v>35</v>
-      </c>
-      <c r="J38">
-        <v>35</v>
+        <v>30</v>
+      </c>
+      <c r="I38" t="s">
+        <v>36</v>
+      </c>
+      <c r="J38" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C39" s="4">
-        <v>46060</v>
+        <v>46074</v>
       </c>
       <c r="D39" t="s">
         <v>29</v>
@@ -1890,91 +1822,85 @@
         <v>2026</v>
       </c>
       <c r="G39" t="s">
+        <v>31</v>
+      </c>
+      <c r="H39">
+        <v>65</v>
+      </c>
+      <c r="I39">
+        <v>42</v>
+      </c>
+      <c r="J39">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="4">
+        <v>46074</v>
+      </c>
+      <c r="D40" t="s">
+        <v>29</v>
+      </c>
+      <c r="E40" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40">
+        <v>2026</v>
+      </c>
+      <c r="G40" t="s">
         <v>33</v>
       </c>
-      <c r="H39">
-        <v>70</v>
-      </c>
-      <c r="I39">
-        <v>15</v>
-      </c>
-      <c r="J39">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>25</v>
-      </c>
-      <c r="B40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="4">
-        <v>46060</v>
-      </c>
-      <c r="D40" t="s">
-        <v>29</v>
-      </c>
-      <c r="E40" t="s">
-        <v>27</v>
-      </c>
-      <c r="F40">
-        <v>2026</v>
-      </c>
-      <c r="G40" t="s">
+      <c r="H40">
+        <v>25</v>
+      </c>
+      <c r="I40" t="s">
+        <v>36</v>
+      </c>
+      <c r="J40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="4">
+        <v>46074</v>
+      </c>
+      <c r="D41" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41">
+        <v>2026</v>
+      </c>
+      <c r="G41" t="s">
         <v>34</v>
       </c>
-      <c r="H40">
-        <v>90</v>
-      </c>
-      <c r="I40">
-        <v>25</v>
-      </c>
-      <c r="J40">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>25</v>
-      </c>
-      <c r="B41" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" s="4">
-        <v>46060</v>
-      </c>
-      <c r="D41" t="s">
-        <v>29</v>
-      </c>
-      <c r="E41" t="s">
-        <v>27</v>
-      </c>
-      <c r="F41">
-        <v>2026</v>
-      </c>
-      <c r="G41" t="s">
-        <v>31</v>
-      </c>
       <c r="H41">
-        <v>15</v>
-      </c>
-      <c r="I41">
-        <v>31</v>
-      </c>
-      <c r="J41">
-        <v>30.5</v>
+        <v>20</v>
+      </c>
+      <c r="I41" t="s">
+        <v>36</v>
+      </c>
+      <c r="J41" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" s="4">
-        <v>46060</v>
+        <v>46074</v>
       </c>
       <c r="D42" t="s">
         <v>29</v>
@@ -1989,24 +1915,21 @@
         <v>31</v>
       </c>
       <c r="H42">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I42">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="J42">
-        <v>62</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>25</v>
-      </c>
       <c r="B43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C43" s="4">
-        <v>46060</v>
+        <v>46074</v>
       </c>
       <c r="D43" t="s">
         <v>29</v>
@@ -2017,28 +1940,25 @@
       <c r="F43">
         <v>2026</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>35</v>
+      <c r="G43" t="s">
+        <v>34</v>
       </c>
       <c r="H43">
-        <v>15</v>
-      </c>
-      <c r="I43">
-        <v>71</v>
-      </c>
-      <c r="J43">
-        <v>98</v>
+        <v>20</v>
+      </c>
+      <c r="I43" t="s">
+        <v>36</v>
+      </c>
+      <c r="J43" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>25</v>
-      </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C44" s="4">
-        <v>46060</v>
+        <v>46074</v>
       </c>
       <c r="D44" t="s">
         <v>29</v>
@@ -2050,27 +1970,27 @@
         <v>2026</v>
       </c>
       <c r="G44" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H44">
-        <v>65</v>
-      </c>
-      <c r="I44">
-        <v>46</v>
-      </c>
-      <c r="J44">
-        <v>48</v>
+        <v>25</v>
+      </c>
+      <c r="I44" t="s">
+        <v>36</v>
+      </c>
+      <c r="J44" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C45" s="4">
-        <v>46060</v>
+        <v>46073</v>
       </c>
       <c r="D45" t="s">
         <v>29</v>
@@ -2082,27 +2002,27 @@
         <v>2026</v>
       </c>
       <c r="G45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H45">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I45">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="J45">
-        <v>81</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B46" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C46" s="4">
-        <v>46060</v>
+        <v>46073</v>
       </c>
       <c r="D46" t="s">
         <v>29</v>
@@ -2117,24 +2037,21 @@
         <v>31</v>
       </c>
       <c r="H46">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="I46">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="J46">
-        <v>56</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>25</v>
-      </c>
       <c r="B47" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C47" s="4">
-        <v>46060</v>
+        <v>46073</v>
       </c>
       <c r="D47" t="s">
         <v>29</v>
@@ -2146,27 +2063,27 @@
         <v>2026</v>
       </c>
       <c r="G47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H47">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I47">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="J47">
-        <v>74</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C48" s="4">
-        <v>46060</v>
+        <v>46073</v>
       </c>
       <c r="D48" t="s">
         <v>29</v>
@@ -2178,59 +2095,56 @@
         <v>2026</v>
       </c>
       <c r="G48" t="s">
+        <v>31</v>
+      </c>
+      <c r="H48">
+        <v>50</v>
+      </c>
+      <c r="I48">
+        <v>29</v>
+      </c>
+      <c r="J48">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="4">
+        <v>46073</v>
+      </c>
+      <c r="D49" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" t="s">
+        <v>27</v>
+      </c>
+      <c r="F49">
+        <v>2026</v>
+      </c>
+      <c r="G49" t="s">
         <v>34</v>
-      </c>
-      <c r="H48">
-        <v>75</v>
-      </c>
-      <c r="I48">
-        <v>34</v>
-      </c>
-      <c r="J48">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>25</v>
-      </c>
-      <c r="B49" t="s">
-        <v>15</v>
-      </c>
-      <c r="C49" s="4">
-        <v>46060</v>
-      </c>
-      <c r="D49" t="s">
-        <v>29</v>
-      </c>
-      <c r="E49" t="s">
-        <v>27</v>
-      </c>
-      <c r="F49">
-        <v>2026</v>
-      </c>
-      <c r="G49" t="s">
-        <v>31</v>
       </c>
       <c r="H49">
         <v>15</v>
       </c>
-      <c r="I49" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>37</v>
+      <c r="I49" t="s">
+        <v>36</v>
+      </c>
+      <c r="J49" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C50" s="4">
-        <v>46060</v>
+        <v>46073</v>
       </c>
       <c r="D50" t="s">
         <v>29</v>
@@ -2245,24 +2159,24 @@
         <v>31</v>
       </c>
       <c r="H50">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="I50">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J50">
-        <v>39</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B51" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C51" s="4">
-        <v>46060</v>
+        <v>46073</v>
       </c>
       <c r="D51" t="s">
         <v>29</v>
@@ -2274,27 +2188,27 @@
         <v>2026</v>
       </c>
       <c r="G51" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H51">
-        <v>50</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>37</v>
+        <v>60</v>
+      </c>
+      <c r="I51">
+        <v>51</v>
+      </c>
+      <c r="J51">
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C52" s="4">
-        <v>46060</v>
+        <v>46073</v>
       </c>
       <c r="D52" t="s">
         <v>29</v>
@@ -2309,24 +2223,24 @@
         <v>31</v>
       </c>
       <c r="H52">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="I52">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J52">
-        <v>31.5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B53" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C53" s="4">
-        <v>46060</v>
+        <v>46073</v>
       </c>
       <c r="D53" t="s">
         <v>29</v>
@@ -2338,27 +2252,27 @@
         <v>2026</v>
       </c>
       <c r="G53" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H53">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="I53">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="J53">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B54" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C54" s="4">
-        <v>46060</v>
+        <v>46073</v>
       </c>
       <c r="D54" t="s">
         <v>29</v>
@@ -2370,27 +2284,27 @@
         <v>2026</v>
       </c>
       <c r="G54" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H54">
-        <v>45</v>
-      </c>
-      <c r="I54">
-        <v>48</v>
-      </c>
-      <c r="J54">
-        <v>57</v>
+        <v>40</v>
+      </c>
+      <c r="I54" t="s">
+        <v>36</v>
+      </c>
+      <c r="J54" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B55" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C55" s="4">
-        <v>46060</v>
+        <v>46073</v>
       </c>
       <c r="D55" t="s">
         <v>29</v>
@@ -2402,27 +2316,27 @@
         <v>2026</v>
       </c>
       <c r="G55" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H55">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="I55">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="J55">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B56" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C56" s="4">
-        <v>46060</v>
+        <v>46073</v>
       </c>
       <c r="D56" t="s">
         <v>29</v>
@@ -2434,27 +2348,27 @@
         <v>2026</v>
       </c>
       <c r="G56" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H56">
-        <v>50</v>
-      </c>
-      <c r="I56">
-        <v>45</v>
-      </c>
-      <c r="J56">
-        <v>57</v>
+        <v>40</v>
+      </c>
+      <c r="I56" t="s">
+        <v>36</v>
+      </c>
+      <c r="J56" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B57" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C57" s="4">
-        <v>46060</v>
+        <v>46073</v>
       </c>
       <c r="D57" t="s">
         <v>29</v>
@@ -2466,27 +2380,27 @@
         <v>2026</v>
       </c>
       <c r="G57" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H57">
-        <v>45</v>
-      </c>
-      <c r="I57">
-        <v>48</v>
-      </c>
-      <c r="J57">
-        <v>55</v>
+        <v>10</v>
+      </c>
+      <c r="I57" t="s">
+        <v>36</v>
+      </c>
+      <c r="J57" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C58" s="4">
-        <v>46060</v>
+        <v>46073</v>
       </c>
       <c r="D58" t="s">
         <v>29</v>
@@ -2498,27 +2412,27 @@
         <v>2026</v>
       </c>
       <c r="G58" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H58">
         <v>40</v>
       </c>
-      <c r="I58">
-        <v>66</v>
-      </c>
-      <c r="J58">
-        <v>70</v>
+      <c r="I58" t="s">
+        <v>36</v>
+      </c>
+      <c r="J58" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B59" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C59" s="4">
-        <v>46060</v>
+        <v>46073</v>
       </c>
       <c r="D59" t="s">
         <v>29</v>
@@ -2530,27 +2444,27 @@
         <v>2026</v>
       </c>
       <c r="G59" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H59">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I59">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="J59">
-        <v>65</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C60" s="4">
-        <v>46060</v>
+        <v>46073</v>
       </c>
       <c r="D60" t="s">
         <v>29</v>
@@ -2565,24 +2479,24 @@
         <v>31</v>
       </c>
       <c r="H60">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I60">
-        <v>42</v>
+        <v>23.5</v>
       </c>
       <c r="J60">
-        <v>52</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B61" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C61" s="4">
-        <v>46060</v>
+        <v>46073</v>
       </c>
       <c r="D61" t="s">
         <v>29</v>
@@ -2594,27 +2508,27 @@
         <v>2026</v>
       </c>
       <c r="G61" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H61">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I61">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J61">
-        <v>44</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B62" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C62" s="4">
-        <v>46060</v>
+        <v>46073</v>
       </c>
       <c r="D62" t="s">
         <v>29</v>
@@ -2626,27 +2540,27 @@
         <v>2026</v>
       </c>
       <c r="G62" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H62">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="I62">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="J62">
-        <v>57.5</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B63" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C63" s="4">
-        <v>46059</v>
+        <v>46073</v>
       </c>
       <c r="D63" t="s">
         <v>29</v>
@@ -2661,24 +2575,24 @@
         <v>31</v>
       </c>
       <c r="H63">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I63">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="J63">
-        <v>66</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B64" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C64" s="4">
-        <v>46059</v>
+        <v>46073</v>
       </c>
       <c r="D64" t="s">
         <v>29</v>
@@ -2690,27 +2604,27 @@
         <v>2026</v>
       </c>
       <c r="G64" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H64">
-        <v>20</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
+      </c>
+      <c r="I64">
+        <v>41</v>
+      </c>
+      <c r="J64">
+        <v>46</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B65" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C65" s="4">
-        <v>46059</v>
+        <v>46073</v>
       </c>
       <c r="D65" t="s">
         <v>29</v>
@@ -2725,24 +2639,24 @@
         <v>31</v>
       </c>
       <c r="H65">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="I65">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="J65">
-        <v>62.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C66" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="D66" t="s">
         <v>29</v>
@@ -2754,27 +2668,27 @@
         <v>2026</v>
       </c>
       <c r="G66" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H66">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I66">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="J66">
-        <v>63</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C67" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="D67" t="s">
         <v>29</v>
@@ -2789,24 +2703,24 @@
         <v>31</v>
       </c>
       <c r="H67">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="I67">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="J67">
-        <v>51</v>
+        <v>25</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C68" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="D68" t="s">
         <v>29</v>
@@ -2818,27 +2732,27 @@
         <v>2026</v>
       </c>
       <c r="G68" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H68">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I68">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="J68">
-        <v>66.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C69" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="D69" t="s">
         <v>29</v>
@@ -2853,56 +2767,56 @@
         <v>31</v>
       </c>
       <c r="H69">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="I69">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="J69">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="4">
+        <v>46060</v>
+      </c>
+      <c r="D70" t="s">
+        <v>29</v>
+      </c>
+      <c r="E70" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70">
+        <v>2026</v>
+      </c>
+      <c r="G70" t="s">
+        <v>33</v>
+      </c>
+      <c r="H70">
+        <v>70</v>
+      </c>
+      <c r="I70">
         <v>15</v>
       </c>
-      <c r="C70" s="4">
-        <v>46059</v>
-      </c>
-      <c r="D70" t="s">
-        <v>29</v>
-      </c>
-      <c r="E70" t="s">
-        <v>27</v>
-      </c>
-      <c r="F70">
-        <v>2026</v>
-      </c>
-      <c r="G70" t="s">
-        <v>31</v>
-      </c>
-      <c r="H70">
-        <v>90</v>
-      </c>
-      <c r="I70">
-        <v>56</v>
-      </c>
       <c r="J70">
-        <v>61.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C71" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="D71" t="s">
         <v>29</v>
@@ -2914,27 +2828,27 @@
         <v>2026</v>
       </c>
       <c r="G71" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H71">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I71">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="J71">
-        <v>67.5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B72" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C72" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="D72" t="s">
         <v>29</v>
@@ -2946,91 +2860,91 @@
         <v>2026</v>
       </c>
       <c r="G72" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H72">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I72">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="J72">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" t="s">
+        <v>12</v>
       </c>
       <c r="C73" s="4">
-        <v>46059</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F73" s="1">
-        <v>2026</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H73" s="1">
-        <v>20</v>
-      </c>
-      <c r="I73" s="1">
-        <v>70</v>
-      </c>
-      <c r="J73" s="1">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>17</v>
+        <v>46060</v>
+      </c>
+      <c r="D73" t="s">
+        <v>29</v>
+      </c>
+      <c r="E73" t="s">
+        <v>27</v>
+      </c>
+      <c r="F73">
+        <v>2026</v>
+      </c>
+      <c r="G73" t="s">
+        <v>31</v>
+      </c>
+      <c r="H73">
+        <v>15</v>
+      </c>
+      <c r="I73">
+        <v>31</v>
+      </c>
+      <c r="J73">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>25</v>
+      </c>
+      <c r="B74" t="s">
+        <v>23</v>
       </c>
       <c r="C74" s="4">
-        <v>46059</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F74" s="1">
-        <v>2026</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H74" s="1">
-        <v>35</v>
-      </c>
-      <c r="I74" s="1">
-        <v>55</v>
-      </c>
-      <c r="J74" s="1">
-        <v>65.5</v>
+        <v>46060</v>
+      </c>
+      <c r="D74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E74" t="s">
+        <v>27</v>
+      </c>
+      <c r="F74">
+        <v>2026</v>
+      </c>
+      <c r="G74" t="s">
+        <v>31</v>
+      </c>
+      <c r="H74">
+        <v>50</v>
+      </c>
+      <c r="I74">
+        <v>53</v>
+      </c>
+      <c r="J74">
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B75" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C75" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="D75" t="s">
         <v>29</v>
@@ -3041,28 +2955,28 @@
       <c r="F75">
         <v>2026</v>
       </c>
-      <c r="G75" t="s">
-        <v>31</v>
+      <c r="G75" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="H75">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="I75">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="J75">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B76" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C76" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="D76" t="s">
         <v>29</v>
@@ -3077,24 +2991,24 @@
         <v>31</v>
       </c>
       <c r="H76">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="I76">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="J76">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B77" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C77" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="D77" t="s">
         <v>29</v>
@@ -3106,27 +3020,27 @@
         <v>2026</v>
       </c>
       <c r="G77" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H77">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="I77">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="J77">
-        <v>68.5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B78" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C78" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="D78" t="s">
         <v>29</v>
@@ -3138,27 +3052,27 @@
         <v>2026</v>
       </c>
       <c r="G78" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H78">
-        <v>70</v>
-      </c>
-      <c r="I78">
-        <v>57</v>
-      </c>
-      <c r="J78">
-        <v>62.5</v>
+        <v>10</v>
+      </c>
+      <c r="I78" t="s">
+        <v>36</v>
+      </c>
+      <c r="J78" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B79" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C79" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="D79" t="s">
         <v>29</v>
@@ -3173,30 +3087,30 @@
         <v>31</v>
       </c>
       <c r="H79">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I79">
-        <v>47.25</v>
+        <v>46</v>
       </c>
       <c r="J79">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B80" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C80" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D80" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F80">
         <v>2026</v>
@@ -3208,91 +3122,91 @@
         <v>30</v>
       </c>
       <c r="I80">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J80">
-        <v>95.5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B81" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C81" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D81" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F81">
         <v>2026</v>
       </c>
       <c r="G81" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H81">
-        <v>45</v>
-      </c>
-      <c r="I81">
-        <v>52.75</v>
-      </c>
-      <c r="J81">
-        <v>60</v>
+        <v>35</v>
+      </c>
+      <c r="I81" t="s">
+        <v>36</v>
+      </c>
+      <c r="J81" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B82" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C82" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D82" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F82">
         <v>2026</v>
       </c>
       <c r="G82" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H82">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="I82">
+        <v>34</v>
+      </c>
+      <c r="J82">
         <v>39</v>
-      </c>
-      <c r="J82">
-        <v>42</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C83" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D83" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F83">
         <v>2026</v>
@@ -3301,30 +3215,30 @@
         <v>31</v>
       </c>
       <c r="H83">
-        <v>90</v>
-      </c>
-      <c r="I83">
-        <v>39</v>
-      </c>
-      <c r="J83">
-        <v>44</v>
+        <v>15</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B84" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C84" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D84" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F84">
         <v>2026</v>
@@ -3333,10 +3247,10 @@
         <v>31</v>
       </c>
       <c r="H84">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="I84">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J84">
         <v>39</v>
@@ -3344,83 +3258,83 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B85" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C85" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D85" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F85">
         <v>2026</v>
       </c>
       <c r="G85" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H85">
-        <v>65</v>
-      </c>
-      <c r="I85">
-        <v>20.75</v>
-      </c>
-      <c r="J85">
-        <v>18.5</v>
+        <v>50</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B86" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C86" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F86">
         <v>2026</v>
       </c>
       <c r="G86" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H86">
-        <v>15</v>
-      </c>
-      <c r="I86">
-        <v>30.75</v>
-      </c>
-      <c r="J86">
         <v>35</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B87" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C87" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D87" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E87" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F87">
         <v>2026</v>
@@ -3429,222 +3343,222 @@
         <v>31</v>
       </c>
       <c r="H87">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I87">
-        <v>30.25</v>
+        <v>32</v>
       </c>
       <c r="J87">
-        <v>38.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B88" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C88" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D88" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E88" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F88">
         <v>2026</v>
       </c>
       <c r="G88" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H88">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I88">
-        <v>15.75</v>
+        <v>13</v>
       </c>
       <c r="J88">
-        <v>18.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B89" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C89" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D89" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E89" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F89">
         <v>2026</v>
       </c>
       <c r="G89" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H89">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="I89">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="J89">
-        <v>40.5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B90" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C90" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D90" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E90" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F90">
         <v>2026</v>
       </c>
       <c r="G90" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H90">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="I90">
-        <v>64.75</v>
+        <v>48</v>
       </c>
       <c r="J90">
-        <v>71.5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B91" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C91" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D91" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E91" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F91">
         <v>2026</v>
       </c>
       <c r="G91" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H91">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I91">
-        <v>40.125</v>
+        <v>70</v>
       </c>
       <c r="J91">
-        <v>46</v>
+        <v>81</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B92" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C92" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D92" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E92" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F92">
         <v>2026</v>
       </c>
       <c r="G92" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H92">
-        <v>55</v>
-      </c>
-      <c r="I92">
-        <v>33.875</v>
-      </c>
-      <c r="J92">
-        <v>35</v>
+        <v>30</v>
+      </c>
+      <c r="I92" t="s">
+        <v>36</v>
+      </c>
+      <c r="J92" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B93" t="s">
         <v>18</v>
       </c>
       <c r="C93" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D93" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E93" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F93">
         <v>2026</v>
       </c>
       <c r="G93" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H93">
-        <v>85</v>
-      </c>
-      <c r="I93">
-        <v>36.5</v>
-      </c>
-      <c r="J93">
-        <v>44</v>
+        <v>30</v>
+      </c>
+      <c r="I93" t="s">
+        <v>36</v>
+      </c>
+      <c r="J93" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B94" t="s">
         <v>20</v>
       </c>
       <c r="C94" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D94" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E94" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F94">
         <v>2026</v>
@@ -3653,126 +3567,126 @@
         <v>31</v>
       </c>
       <c r="H94">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="I94">
-        <v>35.25</v>
+        <v>45</v>
       </c>
       <c r="J94">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B95" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C95" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D95" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E95" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F95">
         <v>2026</v>
       </c>
       <c r="G95" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H95">
-        <v>70</v>
-      </c>
-      <c r="I95">
-        <v>21.5</v>
-      </c>
-      <c r="J95">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="I95" t="s">
+        <v>36</v>
+      </c>
+      <c r="J95" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B96" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C96" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D96" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E96" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F96">
         <v>2026</v>
       </c>
       <c r="G96" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H96">
-        <v>15</v>
-      </c>
-      <c r="I96">
-        <v>30</v>
-      </c>
-      <c r="J96">
-        <v>45</v>
+        <v>20</v>
+      </c>
+      <c r="I96" t="s">
+        <v>36</v>
+      </c>
+      <c r="J96" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B97" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C97" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D97" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E97" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F97">
         <v>2026</v>
       </c>
       <c r="G97" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H97">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="I97">
-        <v>42.125</v>
+        <v>55</v>
       </c>
       <c r="J97">
-        <v>55.5</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B98" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C98" s="4">
-        <v>46184</v>
+        <v>46060</v>
       </c>
       <c r="D98" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E98" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F98">
         <v>2026</v>
@@ -3781,414 +3695,414 @@
         <v>31</v>
       </c>
       <c r="H98">
+        <v>45</v>
+      </c>
+      <c r="I98">
+        <v>48</v>
+      </c>
+      <c r="J98">
         <v>55</v>
-      </c>
-      <c r="I98">
-        <v>40.5</v>
-      </c>
-      <c r="J98">
-        <v>46</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B99" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C99" s="4">
-        <v>46182</v>
+        <v>46060</v>
       </c>
       <c r="D99" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E99" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F99">
         <v>2026</v>
       </c>
       <c r="G99" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H99">
-        <v>30</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
+      </c>
+      <c r="I99">
+        <v>66</v>
       </c>
       <c r="J99">
-        <v>20.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B100" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C100" s="4">
-        <v>46182</v>
+        <v>46060</v>
       </c>
       <c r="D100" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E100" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F100">
         <v>2026</v>
       </c>
       <c r="G100" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H100">
-        <v>15</v>
-      </c>
-      <c r="I100">
-        <v>24.832999999999998</v>
-      </c>
-      <c r="J100">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="I100" t="s">
+        <v>36</v>
+      </c>
+      <c r="J100" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B101" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C101" s="4">
-        <v>46182</v>
+        <v>46060</v>
       </c>
       <c r="D101" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E101" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F101">
         <v>2026</v>
       </c>
       <c r="G101" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H101">
+        <v>15</v>
+      </c>
+      <c r="I101">
+        <v>60</v>
+      </c>
+      <c r="J101">
         <v>65</v>
-      </c>
-      <c r="I101">
-        <v>7.25</v>
-      </c>
-      <c r="J101">
-        <v>9</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B102" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C102" s="4">
-        <v>46182</v>
+        <v>46060</v>
       </c>
       <c r="D102" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E102" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F102">
         <v>2026</v>
       </c>
       <c r="G102" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H102">
-        <v>40</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J102" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
+      </c>
+      <c r="I102">
+        <v>42</v>
+      </c>
+      <c r="J102">
+        <v>52</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B103" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C103" s="4">
-        <v>46182</v>
+        <v>46060</v>
       </c>
       <c r="D103" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E103" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F103">
         <v>2026</v>
       </c>
       <c r="G103" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H103">
-        <v>50</v>
-      </c>
-      <c r="I103">
-        <v>33.625</v>
-      </c>
-      <c r="J103">
-        <v>35.5</v>
+        <v>25</v>
+      </c>
+      <c r="I103" t="s">
+        <v>36</v>
+      </c>
+      <c r="J103" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B104" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C104" s="4">
-        <v>46182</v>
+        <v>46060</v>
       </c>
       <c r="D104" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E104" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F104">
         <v>2026</v>
       </c>
       <c r="G104" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H104">
-        <v>85</v>
-      </c>
-      <c r="I104">
-        <v>39.625</v>
-      </c>
-      <c r="J104">
-        <v>43</v>
+        <v>25</v>
+      </c>
+      <c r="I104" t="s">
+        <v>36</v>
+      </c>
+      <c r="J104" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B105" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C105" s="4">
-        <v>46182</v>
+        <v>46060</v>
       </c>
       <c r="D105" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E105" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F105">
         <v>2026</v>
       </c>
       <c r="G105" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H105">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I105">
-        <v>46.25</v>
+        <v>34</v>
       </c>
       <c r="J105">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B106" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C106" s="4">
-        <v>46182</v>
+        <v>46060</v>
       </c>
       <c r="D106" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E106" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F106">
         <v>2026</v>
       </c>
       <c r="G106" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H106">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="I106">
-        <v>37.25</v>
+        <v>58</v>
       </c>
       <c r="J106">
-        <v>44</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B107" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C107" s="4">
-        <v>46182</v>
+        <v>46060</v>
       </c>
       <c r="D107" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E107" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F107">
         <v>2026</v>
       </c>
       <c r="G107" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H107">
-        <v>50</v>
-      </c>
-      <c r="I107">
-        <v>35.25</v>
-      </c>
-      <c r="J107">
-        <v>41.5</v>
+        <v>10</v>
+      </c>
+      <c r="I107" t="s">
+        <v>36</v>
+      </c>
+      <c r="J107" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B108" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C108" s="4">
-        <v>46182</v>
+        <v>46059</v>
       </c>
       <c r="D108" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E108" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F108">
         <v>2026</v>
       </c>
       <c r="G108" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H108">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="I108">
-        <v>19.875</v>
+        <v>57</v>
       </c>
       <c r="J108">
-        <v>23</v>
+        <v>66</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B109" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C109" s="4">
-        <v>46182</v>
+        <v>46059</v>
       </c>
       <c r="D109" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E109" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F109">
         <v>2026</v>
       </c>
       <c r="G109" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H109">
-        <v>75</v>
-      </c>
-      <c r="I109">
-        <v>19.25</v>
-      </c>
-      <c r="J109">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B110" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C110" s="4">
-        <v>46182</v>
+        <v>46059</v>
       </c>
       <c r="D110" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E110" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F110">
         <v>2026</v>
       </c>
       <c r="G110" t="s">
-        <v>37</v>
-      </c>
-      <c r="H110" t="s">
-        <v>37</v>
-      </c>
-      <c r="I110" t="s">
-        <v>37</v>
-      </c>
-      <c r="J110" t="s">
-        <v>37</v>
+        <v>31</v>
+      </c>
+      <c r="H110">
+        <v>70</v>
+      </c>
+      <c r="I110">
+        <v>53</v>
+      </c>
+      <c r="J110">
+        <v>62.5</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B111" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C111" s="4">
-        <v>46182</v>
+        <v>46059</v>
       </c>
       <c r="D111" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E111" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F111">
         <v>2026</v>
@@ -4197,62 +4111,62 @@
         <v>31</v>
       </c>
       <c r="H111">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I111">
-        <v>20.25</v>
+        <v>60</v>
       </c>
       <c r="J111">
-        <v>26.5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B112" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C112" s="4">
-        <v>46182</v>
+        <v>46059</v>
       </c>
       <c r="D112" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E112" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F112">
         <v>2026</v>
       </c>
       <c r="G112" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H112">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="I112">
-        <v>12.125</v>
+        <v>50</v>
       </c>
       <c r="J112">
-        <v>13.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B113" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C113" s="4">
-        <v>46182</v>
+        <v>46059</v>
       </c>
       <c r="D113" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E113" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F113">
         <v>2026</v>
@@ -4261,30 +4175,30 @@
         <v>31</v>
       </c>
       <c r="H113">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="I113">
-        <v>33.375</v>
+        <v>63</v>
       </c>
       <c r="J113">
-        <v>39</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B114" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C114" s="4">
-        <v>46182</v>
+        <v>46059</v>
       </c>
       <c r="D114" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E114" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F114">
         <v>2026</v>
@@ -4293,30 +4207,30 @@
         <v>31</v>
       </c>
       <c r="H114">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="I114">
-        <v>36.375</v>
+        <v>57</v>
       </c>
       <c r="J114">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B115" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C115" s="4">
-        <v>46182</v>
+        <v>46059</v>
       </c>
       <c r="D115" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E115" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F115">
         <v>2026</v>
@@ -4328,59 +4242,59 @@
         <v>90</v>
       </c>
       <c r="I115">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="J115">
-        <v>47</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B116" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C116" s="4">
-        <v>46182</v>
+        <v>46059</v>
       </c>
       <c r="D116" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E116" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F116">
         <v>2026</v>
       </c>
       <c r="G116" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H116">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="I116">
-        <v>42.25</v>
+        <v>67</v>
       </c>
       <c r="J116">
-        <v>45</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B117" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C117" s="4">
-        <v>46182</v>
+        <v>46059</v>
       </c>
       <c r="D117" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E117" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F117">
         <v>2026</v>
@@ -4389,94 +4303,94 @@
         <v>31</v>
       </c>
       <c r="H117">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="I117">
-        <v>38.125</v>
+        <v>52</v>
       </c>
       <c r="J117">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>25</v>
-      </c>
-      <c r="B118" t="s">
-        <v>10</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C118" s="4">
-        <v>46183</v>
-      </c>
-      <c r="D118" t="s">
-        <v>30</v>
-      </c>
-      <c r="E118" t="s">
-        <v>28</v>
-      </c>
-      <c r="F118">
-        <v>2026</v>
-      </c>
-      <c r="G118" t="s">
-        <v>33</v>
-      </c>
-      <c r="H118">
-        <v>80</v>
-      </c>
-      <c r="I118">
-        <v>14.5</v>
-      </c>
-      <c r="J118">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>25</v>
-      </c>
-      <c r="B119" t="s">
-        <v>10</v>
+        <v>46059</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F118" s="1">
+        <v>2026</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H118" s="1">
+        <v>20</v>
+      </c>
+      <c r="I118" s="1">
+        <v>70</v>
+      </c>
+      <c r="J118" s="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C119" s="4">
-        <v>46183</v>
-      </c>
-      <c r="D119" t="s">
-        <v>30</v>
-      </c>
-      <c r="E119" t="s">
-        <v>28</v>
-      </c>
-      <c r="F119">
-        <v>2026</v>
-      </c>
-      <c r="G119" t="s">
-        <v>31</v>
-      </c>
-      <c r="H119">
-        <v>5</v>
-      </c>
-      <c r="I119">
-        <v>28</v>
-      </c>
-      <c r="J119">
-        <v>28</v>
+        <v>46059</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F119" s="1">
+        <v>2026</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H119" s="1">
+        <v>35</v>
+      </c>
+      <c r="I119" s="1">
+        <v>55</v>
+      </c>
+      <c r="J119" s="1">
+        <v>65.5</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B120" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C120" s="4">
-        <v>46183</v>
+        <v>46059</v>
       </c>
       <c r="D120" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E120" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F120">
         <v>2026</v>
@@ -4485,94 +4399,94 @@
         <v>31</v>
       </c>
       <c r="H120">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="I120">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="J120">
-        <v>35</v>
+        <v>62</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B121" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C121" s="4">
-        <v>46183</v>
+        <v>46059</v>
       </c>
       <c r="D121" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E121" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F121">
         <v>2026</v>
       </c>
       <c r="G121" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H121">
         <v>75</v>
       </c>
       <c r="I121">
-        <v>15.375</v>
+        <v>54</v>
       </c>
       <c r="J121">
-        <v>18</v>
+        <v>57</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B122" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C122" s="4">
-        <v>46183</v>
+        <v>46059</v>
       </c>
       <c r="D122" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E122" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F122">
         <v>2026</v>
       </c>
       <c r="G122" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H122">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I122">
-        <v>35.625</v>
+        <v>65</v>
       </c>
       <c r="J122">
-        <v>37.5</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B123" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C123" s="4">
-        <v>46183</v>
+        <v>46059</v>
       </c>
       <c r="D123" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E123" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F123">
         <v>2026</v>
@@ -4581,56 +4495,56 @@
         <v>31</v>
       </c>
       <c r="H123">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I123">
-        <v>54.125</v>
+        <v>57</v>
       </c>
       <c r="J123">
-        <v>95</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B124" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C124" s="4">
-        <v>46183</v>
+        <v>46059</v>
       </c>
       <c r="D124" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E124" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F124">
         <v>2026</v>
       </c>
       <c r="G124" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H124">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="I124">
-        <v>77.25</v>
+        <v>47.25</v>
       </c>
       <c r="J124">
-        <v>56.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B125" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C125" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D125" t="s">
         <v>30</v>
@@ -4642,27 +4556,27 @@
         <v>2026</v>
       </c>
       <c r="G125" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H125">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I125">
-        <v>44.375</v>
+        <v>89.5</v>
       </c>
       <c r="J125">
-        <v>51</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B126" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C126" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D126" t="s">
         <v>30</v>
@@ -4674,27 +4588,27 @@
         <v>2026</v>
       </c>
       <c r="G126" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H126">
         <v>45</v>
       </c>
       <c r="I126">
-        <v>68.25</v>
+        <v>52.75</v>
       </c>
       <c r="J126">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B127" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C127" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D127" t="s">
         <v>30</v>
@@ -4709,24 +4623,24 @@
         <v>31</v>
       </c>
       <c r="H127">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="I127">
-        <v>45.75</v>
+        <v>39</v>
       </c>
       <c r="J127">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B128" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C128" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D128" t="s">
         <v>30</v>
@@ -4738,27 +4652,27 @@
         <v>2026</v>
       </c>
       <c r="G128" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H128">
-        <v>80</v>
-      </c>
-      <c r="I128">
-        <v>25</v>
-      </c>
-      <c r="J128">
-        <v>30</v>
+        <v>10</v>
+      </c>
+      <c r="I128" t="s">
+        <v>36</v>
+      </c>
+      <c r="J128" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B129" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C129" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D129" t="s">
         <v>30</v>
@@ -4770,27 +4684,27 @@
         <v>2026</v>
       </c>
       <c r="G129" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H129">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I129">
-        <v>64.25</v>
+        <v>39</v>
       </c>
       <c r="J129">
-        <v>7.15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B130" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C130" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D130" t="s">
         <v>30</v>
@@ -4805,24 +4719,24 @@
         <v>34</v>
       </c>
       <c r="H130">
-        <v>90</v>
-      </c>
-      <c r="I130">
-        <v>30.125</v>
-      </c>
-      <c r="J130">
-        <v>33.5</v>
+        <v>5</v>
+      </c>
+      <c r="I130" t="s">
+        <v>36</v>
+      </c>
+      <c r="J130" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B131" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C131" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D131" t="s">
         <v>30</v>
@@ -4837,24 +4751,24 @@
         <v>31</v>
       </c>
       <c r="H131">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="I131">
-        <v>27.25</v>
+        <v>37</v>
       </c>
       <c r="J131">
-        <v>30.5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B132" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C132" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D132" t="s">
         <v>30</v>
@@ -4866,27 +4780,27 @@
         <v>2026</v>
       </c>
       <c r="G132" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H132">
-        <v>20</v>
-      </c>
-      <c r="I132" s="3">
-        <v>34.875</v>
-      </c>
-      <c r="J132">
-        <v>42.5</v>
+        <v>5</v>
+      </c>
+      <c r="I132" t="s">
+        <v>36</v>
+      </c>
+      <c r="J132" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B133" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C133" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D133" t="s">
         <v>30</v>
@@ -4898,27 +4812,27 @@
         <v>2026</v>
       </c>
       <c r="G133" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H133">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="I133">
-        <v>16.25</v>
+        <v>21</v>
       </c>
       <c r="J133">
-        <v>19</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B134" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C134" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D134" t="s">
         <v>30</v>
@@ -4933,24 +4847,24 @@
         <v>31</v>
       </c>
       <c r="H134">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I134">
-        <v>24.83</v>
+        <v>31</v>
       </c>
       <c r="J134">
-        <v>32.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B135" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C135" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D135" t="s">
         <v>30</v>
@@ -4962,27 +4876,27 @@
         <v>2026</v>
       </c>
       <c r="G135" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H135">
-        <v>75</v>
-      </c>
-      <c r="I135">
-        <v>16.375</v>
-      </c>
-      <c r="J135">
-        <v>19</v>
+        <v>10</v>
+      </c>
+      <c r="I135" t="s">
+        <v>36</v>
+      </c>
+      <c r="J135" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B136" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C136" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D136" t="s">
         <v>30</v>
@@ -4994,27 +4908,27 @@
         <v>2026</v>
       </c>
       <c r="G136" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H136">
-        <v>40</v>
-      </c>
-      <c r="I136">
-        <v>43</v>
-      </c>
-      <c r="J136">
-        <v>53</v>
+        <v>5</v>
+      </c>
+      <c r="I136" t="s">
+        <v>36</v>
+      </c>
+      <c r="J136" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B137" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C137" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D137" t="s">
         <v>30</v>
@@ -5029,24 +4943,24 @@
         <v>33</v>
       </c>
       <c r="H137">
-        <v>50</v>
-      </c>
-      <c r="I137">
-        <v>21.875</v>
-      </c>
-      <c r="J137">
-        <v>25</v>
+        <v>10</v>
+      </c>
+      <c r="I137" t="s">
+        <v>36</v>
+      </c>
+      <c r="J137" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B138" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C138" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D138" t="s">
         <v>30</v>
@@ -5058,27 +4972,27 @@
         <v>2026</v>
       </c>
       <c r="G138" t="s">
+        <v>31</v>
+      </c>
+      <c r="H138">
         <v>35</v>
       </c>
-      <c r="H138">
-        <v>10</v>
-      </c>
       <c r="I138">
-        <v>53.167000000000002</v>
+        <v>30</v>
       </c>
       <c r="J138">
-        <v>60</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B139" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C139" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D139" t="s">
         <v>30</v>
@@ -5090,27 +5004,27 @@
         <v>2026</v>
       </c>
       <c r="G139" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H139">
-        <v>35</v>
-      </c>
-      <c r="I139">
-        <v>48</v>
-      </c>
-      <c r="J139">
-        <v>64</v>
+        <v>25</v>
+      </c>
+      <c r="I139" t="s">
+        <v>36</v>
+      </c>
+      <c r="J139" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B140" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C140" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D140" t="s">
         <v>30</v>
@@ -5122,27 +5036,27 @@
         <v>2026</v>
       </c>
       <c r="G140" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H140">
-        <v>55</v>
-      </c>
-      <c r="I140">
-        <v>20.75</v>
-      </c>
-      <c r="J140">
-        <v>23</v>
+        <v>15</v>
+      </c>
+      <c r="I140" t="s">
+        <v>36</v>
+      </c>
+      <c r="J140" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B141" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C141" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D141" t="s">
         <v>30</v>
@@ -5154,27 +5068,27 @@
         <v>2026</v>
       </c>
       <c r="G141" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H141">
-        <v>15</v>
-      </c>
-      <c r="I141">
-        <v>48.75</v>
-      </c>
-      <c r="J141">
-        <v>53</v>
+        <v>25</v>
+      </c>
+      <c r="I141" t="s">
+        <v>36</v>
+      </c>
+      <c r="J141" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B142" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C142" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D142" t="s">
         <v>30</v>
@@ -5186,27 +5100,27 @@
         <v>2026</v>
       </c>
       <c r="G142" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H142">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I142">
-        <v>48.75</v>
+        <v>16</v>
       </c>
       <c r="J142">
-        <v>51</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B143" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C143" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D143" t="s">
         <v>30</v>
@@ -5218,27 +5132,27 @@
         <v>2026</v>
       </c>
       <c r="G143" t="s">
+        <v>31</v>
+      </c>
+      <c r="H143">
+        <v>75</v>
+      </c>
+      <c r="I143">
         <v>35</v>
       </c>
-      <c r="H143">
-        <v>35</v>
-      </c>
-      <c r="I143">
-        <v>55.25</v>
-      </c>
       <c r="J143">
-        <v>62</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B144" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C144" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D144" t="s">
         <v>30</v>
@@ -5253,24 +5167,24 @@
         <v>33</v>
       </c>
       <c r="H144">
-        <v>45</v>
-      </c>
-      <c r="I144">
-        <v>25.5</v>
-      </c>
-      <c r="J144">
-        <v>28</v>
+        <v>15</v>
+      </c>
+      <c r="I144" t="s">
+        <v>36</v>
+      </c>
+      <c r="J144" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B145" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C145" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D145" t="s">
         <v>30</v>
@@ -5282,27 +5196,27 @@
         <v>2026</v>
       </c>
       <c r="G145" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H145">
-        <v>20</v>
-      </c>
-      <c r="I145">
-        <v>53.75</v>
-      </c>
-      <c r="J145">
-        <v>57</v>
+        <v>10</v>
+      </c>
+      <c r="I145" t="s">
+        <v>36</v>
+      </c>
+      <c r="J145" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B146" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C146" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D146" t="s">
         <v>30</v>
@@ -5314,27 +5228,27 @@
         <v>2026</v>
       </c>
       <c r="G146" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H146">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I146">
-        <v>33.75</v>
+        <v>65</v>
       </c>
       <c r="J146">
-        <v>38</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B147" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C147" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D147" t="s">
         <v>30</v>
@@ -5346,27 +5260,27 @@
         <v>2026</v>
       </c>
       <c r="G147" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H147">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="I147">
-        <v>23.375</v>
+        <v>40</v>
       </c>
       <c r="J147">
-        <v>24.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B148" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C148" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D148" t="s">
         <v>30</v>
@@ -5381,24 +5295,24 @@
         <v>34</v>
       </c>
       <c r="H148">
-        <v>90</v>
-      </c>
-      <c r="I148">
-        <v>31</v>
-      </c>
-      <c r="J148">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="I148" t="s">
+        <v>36</v>
+      </c>
+      <c r="J148" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B149" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C149" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D149" t="s">
         <v>30</v>
@@ -5410,27 +5324,27 @@
         <v>2026</v>
       </c>
       <c r="G149" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H149">
-        <v>5</v>
-      </c>
-      <c r="I149">
-        <v>56</v>
-      </c>
-      <c r="J149">
-        <v>56</v>
+        <v>45</v>
+      </c>
+      <c r="I149" t="s">
+        <v>36</v>
+      </c>
+      <c r="J149" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B150" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C150" s="4">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="D150" t="s">
         <v>30</v>
@@ -5445,24 +5359,24 @@
         <v>31</v>
       </c>
       <c r="H150">
+        <v>55</v>
+      </c>
+      <c r="I150">
+        <v>33.875</v>
+      </c>
+      <c r="J150">
         <v>35</v>
-      </c>
-      <c r="I150">
-        <v>57</v>
-      </c>
-      <c r="J150">
-        <v>66</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B151" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C151" s="4">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="D151" t="s">
         <v>30</v>
@@ -5474,27 +5388,27 @@
         <v>2026</v>
       </c>
       <c r="G151" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H151">
-        <v>35</v>
-      </c>
-      <c r="I151">
-        <v>67.125</v>
-      </c>
-      <c r="J151">
-        <v>76</v>
+        <v>20</v>
+      </c>
+      <c r="I151" t="s">
+        <v>36</v>
+      </c>
+      <c r="J151" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B152" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C152" s="4">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="D152" t="s">
         <v>30</v>
@@ -5506,27 +5420,27 @@
         <v>2026</v>
       </c>
       <c r="G152" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H152">
-        <v>75</v>
-      </c>
-      <c r="I152">
-        <v>51.625</v>
-      </c>
-      <c r="J152">
-        <v>69.5</v>
+        <v>30</v>
+      </c>
+      <c r="I152" t="s">
+        <v>36</v>
+      </c>
+      <c r="J152" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B153" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C153" s="4">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="D153" t="s">
         <v>30</v>
@@ -5541,24 +5455,24 @@
         <v>31</v>
       </c>
       <c r="H153">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="I153">
-        <v>61.125</v>
+        <v>36.5</v>
       </c>
       <c r="J153">
-        <v>65</v>
+        <v>44</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B154" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C154" s="4">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="D154" t="s">
         <v>30</v>
@@ -5570,27 +5484,27 @@
         <v>2026</v>
       </c>
       <c r="G154" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H154">
-        <v>65</v>
-      </c>
-      <c r="I154">
-        <v>46</v>
-      </c>
-      <c r="J154">
-        <v>55</v>
+        <v>10</v>
+      </c>
+      <c r="I154" t="s">
+        <v>36</v>
+      </c>
+      <c r="J154" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B155" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C155" s="4">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="D155" t="s">
         <v>30</v>
@@ -5602,27 +5516,27 @@
         <v>2026</v>
       </c>
       <c r="G155" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H155">
-        <v>80</v>
-      </c>
-      <c r="I155">
-        <v>58.75</v>
-      </c>
-      <c r="J155">
-        <v>69</v>
+        <v>5</v>
+      </c>
+      <c r="I155" t="s">
+        <v>36</v>
+      </c>
+      <c r="J155" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B156" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C156" s="4">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="D156" t="s">
         <v>30</v>
@@ -5637,24 +5551,24 @@
         <v>31</v>
       </c>
       <c r="H156">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="I156">
-        <v>55.5</v>
+        <v>35.25</v>
       </c>
       <c r="J156">
-        <v>58.5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B157" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C157" s="4">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="D157" t="s">
         <v>30</v>
@@ -5666,27 +5580,27 @@
         <v>2026</v>
       </c>
       <c r="G157" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H157">
-        <v>95</v>
-      </c>
-      <c r="I157">
-        <v>49.125</v>
-      </c>
-      <c r="J157">
-        <v>60</v>
+        <v>10</v>
+      </c>
+      <c r="I157" t="s">
+        <v>36</v>
+      </c>
+      <c r="J157" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B158" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C158" s="4">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="D158" t="s">
         <v>30</v>
@@ -5698,27 +5612,27 @@
         <v>2026</v>
       </c>
       <c r="G158" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H158">
-        <v>40</v>
-      </c>
-      <c r="I158">
-        <v>77.75</v>
-      </c>
-      <c r="J158">
-        <v>85</v>
+        <v>5</v>
+      </c>
+      <c r="I158" t="s">
+        <v>36</v>
+      </c>
+      <c r="J158" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B159" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C159" s="4">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="D159" t="s">
         <v>30</v>
@@ -5730,27 +5644,27 @@
         <v>2026</v>
       </c>
       <c r="G159" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H159">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="I159">
-        <v>53.75</v>
+        <v>21.5</v>
       </c>
       <c r="J159">
-        <v>56</v>
+        <v>27</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B160" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C160" s="4">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="D160" t="s">
         <v>30</v>
@@ -5762,27 +5676,27 @@
         <v>2026</v>
       </c>
       <c r="G160" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H160">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I160">
-        <v>87.25</v>
+        <v>30</v>
       </c>
       <c r="J160">
-        <v>93</v>
+        <v>45</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B161" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C161" s="4">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="D161" t="s">
         <v>30</v>
@@ -5794,27 +5708,27 @@
         <v>2026</v>
       </c>
       <c r="G161" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H161">
-        <v>30</v>
-      </c>
-      <c r="I161">
-        <v>54.5</v>
-      </c>
-      <c r="J161">
-        <v>68</v>
+        <v>65</v>
+      </c>
+      <c r="I161" t="s">
+        <v>36</v>
+      </c>
+      <c r="J161" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B162" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C162" s="4">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="D162" t="s">
         <v>30</v>
@@ -5826,27 +5740,27 @@
         <v>2026</v>
       </c>
       <c r="G162" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H162">
-        <v>80</v>
-      </c>
-      <c r="I162">
-        <v>50</v>
-      </c>
-      <c r="J162">
-        <v>55</v>
+        <v>20</v>
+      </c>
+      <c r="I162" t="s">
+        <v>36</v>
+      </c>
+      <c r="J162" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B163" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C163" s="4">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="D163" t="s">
         <v>30</v>
@@ -5861,24 +5775,24 @@
         <v>31</v>
       </c>
       <c r="H163">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I163">
-        <v>52.125</v>
+        <v>42.125</v>
       </c>
       <c r="J163">
-        <v>56</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B164" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C164" s="4">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="D164" t="s">
         <v>30</v>
@@ -5890,27 +5804,27 @@
         <v>2026</v>
       </c>
       <c r="G164" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H164">
-        <v>85</v>
-      </c>
-      <c r="I164">
-        <v>61.75</v>
-      </c>
-      <c r="J164">
-        <v>65</v>
+        <v>15</v>
+      </c>
+      <c r="I164" t="s">
+        <v>36</v>
+      </c>
+      <c r="J164" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B165" t="s">
         <v>21</v>
       </c>
       <c r="C165" s="4">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="D165" t="s">
         <v>30</v>
@@ -5922,47 +5836,2639 @@
         <v>2026</v>
       </c>
       <c r="G165" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H165">
-        <v>95</v>
-      </c>
-      <c r="I165">
-        <v>56</v>
-      </c>
-      <c r="J165">
-        <v>59.5</v>
+        <v>10</v>
+      </c>
+      <c r="I165" t="s">
+        <v>36</v>
+      </c>
+      <c r="J165" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B166" t="s">
         <v>22</v>
       </c>
       <c r="C166" s="4">
+        <v>46184</v>
+      </c>
+      <c r="D166" t="s">
+        <v>30</v>
+      </c>
+      <c r="E166" t="s">
+        <v>28</v>
+      </c>
+      <c r="F166">
+        <v>2026</v>
+      </c>
+      <c r="G166" t="s">
+        <v>31</v>
+      </c>
+      <c r="H166">
+        <v>55</v>
+      </c>
+      <c r="I166">
+        <v>40.5</v>
+      </c>
+      <c r="J166">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>9</v>
+      </c>
+      <c r="B167" t="s">
+        <v>22</v>
+      </c>
+      <c r="C167" s="4">
+        <v>46184</v>
+      </c>
+      <c r="D167" t="s">
+        <v>30</v>
+      </c>
+      <c r="E167" t="s">
+        <v>28</v>
+      </c>
+      <c r="F167">
+        <v>2026</v>
+      </c>
+      <c r="G167" t="s">
+        <v>34</v>
+      </c>
+      <c r="H167">
+        <v>10</v>
+      </c>
+      <c r="I167" t="s">
+        <v>36</v>
+      </c>
+      <c r="J167" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>9</v>
+      </c>
+      <c r="B168" t="s">
+        <v>22</v>
+      </c>
+      <c r="C168" s="4">
+        <v>46184</v>
+      </c>
+      <c r="D168" t="s">
+        <v>30</v>
+      </c>
+      <c r="E168" t="s">
+        <v>28</v>
+      </c>
+      <c r="F168">
+        <v>2026</v>
+      </c>
+      <c r="G168" t="s">
+        <v>33</v>
+      </c>
+      <c r="H168">
+        <v>15</v>
+      </c>
+      <c r="I168" t="s">
+        <v>36</v>
+      </c>
+      <c r="J168" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>24</v>
+      </c>
+      <c r="B169" t="s">
+        <v>10</v>
+      </c>
+      <c r="C169" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D169" t="s">
+        <v>30</v>
+      </c>
+      <c r="E169" t="s">
+        <v>28</v>
+      </c>
+      <c r="F169">
+        <v>2026</v>
+      </c>
+      <c r="G169" t="s">
+        <v>34</v>
+      </c>
+      <c r="H169">
+        <v>30</v>
+      </c>
+      <c r="I169" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J169" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>24</v>
+      </c>
+      <c r="B170" t="s">
+        <v>10</v>
+      </c>
+      <c r="C170" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D170" t="s">
+        <v>30</v>
+      </c>
+      <c r="E170" t="s">
+        <v>28</v>
+      </c>
+      <c r="F170">
+        <v>2026</v>
+      </c>
+      <c r="G170" t="s">
+        <v>31</v>
+      </c>
+      <c r="H170">
+        <v>15</v>
+      </c>
+      <c r="I170">
+        <v>25</v>
+      </c>
+      <c r="J170">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>24</v>
+      </c>
+      <c r="B171" t="s">
+        <v>11</v>
+      </c>
+      <c r="C171" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D171" t="s">
+        <v>30</v>
+      </c>
+      <c r="E171" t="s">
+        <v>28</v>
+      </c>
+      <c r="F171">
+        <v>2026</v>
+      </c>
+      <c r="G171" t="s">
+        <v>34</v>
+      </c>
+      <c r="H171">
+        <v>40</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J171" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>24</v>
+      </c>
+      <c r="B172" t="s">
+        <v>11</v>
+      </c>
+      <c r="C172" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D172" t="s">
+        <v>30</v>
+      </c>
+      <c r="E172" t="s">
+        <v>28</v>
+      </c>
+      <c r="F172">
+        <v>2026</v>
+      </c>
+      <c r="G172" t="s">
+        <v>31</v>
+      </c>
+      <c r="H172">
+        <v>50</v>
+      </c>
+      <c r="I172">
+        <v>34</v>
+      </c>
+      <c r="J172">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>24</v>
+      </c>
+      <c r="B173" t="s">
+        <v>12</v>
+      </c>
+      <c r="C173" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D173" t="s">
+        <v>30</v>
+      </c>
+      <c r="E173" t="s">
+        <v>28</v>
+      </c>
+      <c r="F173">
+        <v>2026</v>
+      </c>
+      <c r="G173" t="s">
+        <v>31</v>
+      </c>
+      <c r="H173">
+        <v>85</v>
+      </c>
+      <c r="I173">
+        <v>40</v>
+      </c>
+      <c r="J173">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>24</v>
+      </c>
+      <c r="B174" t="s">
+        <v>23</v>
+      </c>
+      <c r="C174" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D174" t="s">
+        <v>30</v>
+      </c>
+      <c r="E174" t="s">
+        <v>28</v>
+      </c>
+      <c r="F174">
+        <v>2026</v>
+      </c>
+      <c r="G174" t="s">
+        <v>31</v>
+      </c>
+      <c r="H174">
+        <v>80</v>
+      </c>
+      <c r="I174">
+        <v>46</v>
+      </c>
+      <c r="J174">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>24</v>
+      </c>
+      <c r="B175" t="s">
+        <v>13</v>
+      </c>
+      <c r="C175" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D175" t="s">
+        <v>30</v>
+      </c>
+      <c r="E175" t="s">
+        <v>28</v>
+      </c>
+      <c r="F175">
+        <v>2026</v>
+      </c>
+      <c r="G175" t="s">
+        <v>31</v>
+      </c>
+      <c r="H175">
+        <v>90</v>
+      </c>
+      <c r="I175">
+        <v>37</v>
+      </c>
+      <c r="J175">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>24</v>
+      </c>
+      <c r="B176" t="s">
+        <v>14</v>
+      </c>
+      <c r="C176" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D176" t="s">
+        <v>30</v>
+      </c>
+      <c r="E176" t="s">
+        <v>28</v>
+      </c>
+      <c r="F176">
+        <v>2026</v>
+      </c>
+      <c r="G176" t="s">
+        <v>31</v>
+      </c>
+      <c r="H176">
+        <v>50</v>
+      </c>
+      <c r="I176">
+        <v>35</v>
+      </c>
+      <c r="J176">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>24</v>
+      </c>
+      <c r="B177" t="s">
+        <v>14</v>
+      </c>
+      <c r="C177" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D177" t="s">
+        <v>30</v>
+      </c>
+      <c r="E177" t="s">
+        <v>28</v>
+      </c>
+      <c r="F177">
+        <v>2026</v>
+      </c>
+      <c r="G177" t="s">
+        <v>33</v>
+      </c>
+      <c r="H177">
+        <v>55</v>
+      </c>
+      <c r="I177">
+        <v>20</v>
+      </c>
+      <c r="J177">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>24</v>
+      </c>
+      <c r="B178" t="s">
+        <v>15</v>
+      </c>
+      <c r="C178" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D178" t="s">
+        <v>30</v>
+      </c>
+      <c r="E178" t="s">
+        <v>28</v>
+      </c>
+      <c r="F178">
+        <v>2026</v>
+      </c>
+      <c r="G178" t="s">
+        <v>33</v>
+      </c>
+      <c r="H178">
+        <v>75</v>
+      </c>
+      <c r="I178">
+        <v>19</v>
+      </c>
+      <c r="J178">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>24</v>
+      </c>
+      <c r="B179" t="s">
+        <v>15</v>
+      </c>
+      <c r="C179" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D179" t="s">
+        <v>30</v>
+      </c>
+      <c r="E179" t="s">
+        <v>28</v>
+      </c>
+      <c r="F179">
+        <v>2026</v>
+      </c>
+      <c r="G179" t="s">
+        <v>38</v>
+      </c>
+      <c r="H179">
+        <v>35</v>
+      </c>
+      <c r="I179" t="s">
+        <v>36</v>
+      </c>
+      <c r="J179" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>24</v>
+      </c>
+      <c r="B180" t="s">
+        <v>15</v>
+      </c>
+      <c r="C180" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D180" t="s">
+        <v>30</v>
+      </c>
+      <c r="E180" t="s">
+        <v>28</v>
+      </c>
+      <c r="F180">
+        <v>2026</v>
+      </c>
+      <c r="G180" t="s">
+        <v>39</v>
+      </c>
+      <c r="H180">
+        <v>10</v>
+      </c>
+      <c r="I180" t="s">
+        <v>36</v>
+      </c>
+      <c r="J180" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>24</v>
+      </c>
+      <c r="B181" t="s">
+        <v>15</v>
+      </c>
+      <c r="C181" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D181" t="s">
+        <v>30</v>
+      </c>
+      <c r="E181" t="s">
+        <v>28</v>
+      </c>
+      <c r="F181">
+        <v>2026</v>
+      </c>
+      <c r="G181" t="s">
+        <v>31</v>
+      </c>
+      <c r="H181">
+        <v>30</v>
+      </c>
+      <c r="I181">
+        <v>27</v>
+      </c>
+      <c r="J181">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>24</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D182" t="s">
+        <v>30</v>
+      </c>
+      <c r="E182" t="s">
+        <v>28</v>
+      </c>
+      <c r="F182">
+        <v>2026</v>
+      </c>
+      <c r="G182" t="s">
+        <v>36</v>
+      </c>
+      <c r="H182">
+        <v>0</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>24</v>
+      </c>
+      <c r="B183" t="s">
+        <v>17</v>
+      </c>
+      <c r="C183" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D183" t="s">
+        <v>30</v>
+      </c>
+      <c r="E183" t="s">
+        <v>28</v>
+      </c>
+      <c r="F183">
+        <v>2026</v>
+      </c>
+      <c r="G183" t="s">
+        <v>31</v>
+      </c>
+      <c r="H183">
+        <v>20</v>
+      </c>
+      <c r="I183">
+        <v>20</v>
+      </c>
+      <c r="J183">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>24</v>
+      </c>
+      <c r="B184" t="s">
+        <v>18</v>
+      </c>
+      <c r="C184" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D184" t="s">
+        <v>30</v>
+      </c>
+      <c r="E184" t="s">
+        <v>28</v>
+      </c>
+      <c r="F184">
+        <v>2026</v>
+      </c>
+      <c r="G184" t="s">
+        <v>31</v>
+      </c>
+      <c r="H184">
+        <v>85</v>
+      </c>
+      <c r="I184">
+        <v>33</v>
+      </c>
+      <c r="J184">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>24</v>
+      </c>
+      <c r="B185" t="s">
+        <v>20</v>
+      </c>
+      <c r="C185" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D185" t="s">
+        <v>30</v>
+      </c>
+      <c r="E185" t="s">
+        <v>28</v>
+      </c>
+      <c r="F185">
+        <v>2026</v>
+      </c>
+      <c r="G185" t="s">
+        <v>31</v>
+      </c>
+      <c r="H185">
+        <v>95</v>
+      </c>
+      <c r="I185">
+        <v>36</v>
+      </c>
+      <c r="J185">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>24</v>
+      </c>
+      <c r="B186" t="s">
+        <v>20</v>
+      </c>
+      <c r="C186" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D186" t="s">
+        <v>30</v>
+      </c>
+      <c r="E186" t="s">
+        <v>28</v>
+      </c>
+      <c r="F186">
+        <v>2026</v>
+      </c>
+      <c r="G186" t="s">
+        <v>33</v>
+      </c>
+      <c r="H186">
+        <v>35</v>
+      </c>
+      <c r="I186" t="s">
+        <v>36</v>
+      </c>
+      <c r="J186" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>24</v>
+      </c>
+      <c r="B187" t="s">
+        <v>19</v>
+      </c>
+      <c r="C187" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D187" t="s">
+        <v>30</v>
+      </c>
+      <c r="E187" t="s">
+        <v>28</v>
+      </c>
+      <c r="F187">
+        <v>2026</v>
+      </c>
+      <c r="G187" t="s">
+        <v>31</v>
+      </c>
+      <c r="H187">
+        <v>90</v>
+      </c>
+      <c r="I187">
+        <v>43</v>
+      </c>
+      <c r="J187">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>24</v>
+      </c>
+      <c r="B188" t="s">
+        <v>21</v>
+      </c>
+      <c r="C188" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D188" t="s">
+        <v>30</v>
+      </c>
+      <c r="E188" t="s">
+        <v>28</v>
+      </c>
+      <c r="F188">
+        <v>2026</v>
+      </c>
+      <c r="G188" t="s">
+        <v>31</v>
+      </c>
+      <c r="H188">
+        <v>95</v>
+      </c>
+      <c r="I188">
+        <v>42</v>
+      </c>
+      <c r="J188">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>24</v>
+      </c>
+      <c r="B189" t="s">
+        <v>22</v>
+      </c>
+      <c r="C189" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D189" t="s">
+        <v>30</v>
+      </c>
+      <c r="E189" t="s">
+        <v>28</v>
+      </c>
+      <c r="F189">
+        <v>2026</v>
+      </c>
+      <c r="G189" t="s">
+        <v>31</v>
+      </c>
+      <c r="H189">
+        <v>95</v>
+      </c>
+      <c r="I189">
+        <v>38</v>
+      </c>
+      <c r="J189">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>25</v>
+      </c>
+      <c r="B190" t="s">
+        <v>10</v>
+      </c>
+      <c r="C190" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D190" t="s">
+        <v>30</v>
+      </c>
+      <c r="E190" t="s">
+        <v>28</v>
+      </c>
+      <c r="F190">
+        <v>2026</v>
+      </c>
+      <c r="G190" t="s">
+        <v>33</v>
+      </c>
+      <c r="H190">
+        <v>80</v>
+      </c>
+      <c r="I190">
+        <v>14.5</v>
+      </c>
+      <c r="J190">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>25</v>
+      </c>
+      <c r="B191" t="s">
+        <v>10</v>
+      </c>
+      <c r="C191" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D191" t="s">
+        <v>30</v>
+      </c>
+      <c r="E191" t="s">
+        <v>28</v>
+      </c>
+      <c r="F191">
+        <v>2026</v>
+      </c>
+      <c r="G191" t="s">
+        <v>31</v>
+      </c>
+      <c r="H191">
+        <v>5</v>
+      </c>
+      <c r="I191">
+        <v>28</v>
+      </c>
+      <c r="J191">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>25</v>
+      </c>
+      <c r="B192" t="s">
+        <v>10</v>
+      </c>
+      <c r="C192" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D192" t="s">
+        <v>30</v>
+      </c>
+      <c r="E192" t="s">
+        <v>28</v>
+      </c>
+      <c r="F192">
+        <v>2026</v>
+      </c>
+      <c r="G192" t="s">
+        <v>34</v>
+      </c>
+      <c r="H192">
+        <v>75</v>
+      </c>
+      <c r="I192" t="s">
+        <v>36</v>
+      </c>
+      <c r="J192" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>25</v>
+      </c>
+      <c r="B193" t="s">
+        <v>11</v>
+      </c>
+      <c r="C193" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D193" t="s">
+        <v>30</v>
+      </c>
+      <c r="E193" t="s">
+        <v>28</v>
+      </c>
+      <c r="F193">
+        <v>2026</v>
+      </c>
+      <c r="G193" t="s">
+        <v>31</v>
+      </c>
+      <c r="H193">
+        <v>10</v>
+      </c>
+      <c r="I193">
+        <v>33</v>
+      </c>
+      <c r="J193">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>25</v>
+      </c>
+      <c r="B194" t="s">
+        <v>11</v>
+      </c>
+      <c r="C194" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D194" t="s">
+        <v>30</v>
+      </c>
+      <c r="E194" t="s">
+        <v>28</v>
+      </c>
+      <c r="F194">
+        <v>2026</v>
+      </c>
+      <c r="G194" t="s">
+        <v>33</v>
+      </c>
+      <c r="H194">
+        <v>75</v>
+      </c>
+      <c r="I194">
+        <v>15</v>
+      </c>
+      <c r="J194">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>25</v>
+      </c>
+      <c r="B195" t="s">
+        <v>11</v>
+      </c>
+      <c r="C195" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D195" t="s">
+        <v>30</v>
+      </c>
+      <c r="E195" t="s">
+        <v>28</v>
+      </c>
+      <c r="F195">
+        <v>2026</v>
+      </c>
+      <c r="G195" t="s">
+        <v>34</v>
+      </c>
+      <c r="H195">
+        <v>50</v>
+      </c>
+      <c r="I195" t="s">
+        <v>36</v>
+      </c>
+      <c r="J195" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>25</v>
+      </c>
+      <c r="B196" t="s">
+        <v>12</v>
+      </c>
+      <c r="C196" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D196" t="s">
+        <v>30</v>
+      </c>
+      <c r="E196" t="s">
+        <v>28</v>
+      </c>
+      <c r="F196">
+        <v>2026</v>
+      </c>
+      <c r="G196" t="s">
+        <v>34</v>
+      </c>
+      <c r="H196">
+        <v>95</v>
+      </c>
+      <c r="I196">
+        <v>36</v>
+      </c>
+      <c r="J196">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>25</v>
+      </c>
+      <c r="B197" t="s">
+        <v>23</v>
+      </c>
+      <c r="C197" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D197" t="s">
+        <v>30</v>
+      </c>
+      <c r="E197" t="s">
+        <v>28</v>
+      </c>
+      <c r="F197">
+        <v>2026</v>
+      </c>
+      <c r="G197" t="s">
+        <v>31</v>
+      </c>
+      <c r="H197">
+        <v>60</v>
+      </c>
+      <c r="I197">
+        <v>54</v>
+      </c>
+      <c r="J197">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>25</v>
+      </c>
+      <c r="B198" t="s">
+        <v>23</v>
+      </c>
+      <c r="C198" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D198" t="s">
+        <v>30</v>
+      </c>
+      <c r="E198" t="s">
+        <v>28</v>
+      </c>
+      <c r="F198">
+        <v>2026</v>
+      </c>
+      <c r="G198" t="s">
+        <v>35</v>
+      </c>
+      <c r="H198">
+        <v>20</v>
+      </c>
+      <c r="I198">
+        <v>77</v>
+      </c>
+      <c r="J198">
+        <v>56.5</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>25</v>
+      </c>
+      <c r="B199" t="s">
+        <v>13</v>
+      </c>
+      <c r="C199" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D199" t="s">
+        <v>30</v>
+      </c>
+      <c r="E199" t="s">
+        <v>28</v>
+      </c>
+      <c r="F199">
+        <v>2026</v>
+      </c>
+      <c r="G199" t="s">
+        <v>31</v>
+      </c>
+      <c r="H199">
+        <v>35</v>
+      </c>
+      <c r="I199">
+        <v>44</v>
+      </c>
+      <c r="J199">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>25</v>
+      </c>
+      <c r="B200" t="s">
+        <v>13</v>
+      </c>
+      <c r="C200" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D200" t="s">
+        <v>30</v>
+      </c>
+      <c r="E200" t="s">
+        <v>28</v>
+      </c>
+      <c r="F200">
+        <v>2026</v>
+      </c>
+      <c r="G200" t="s">
+        <v>34</v>
+      </c>
+      <c r="H200">
+        <v>10</v>
+      </c>
+      <c r="I200" t="s">
+        <v>36</v>
+      </c>
+      <c r="J200" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>25</v>
+      </c>
+      <c r="B201" t="s">
+        <v>13</v>
+      </c>
+      <c r="C201" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D201" t="s">
+        <v>30</v>
+      </c>
+      <c r="E201" t="s">
+        <v>28</v>
+      </c>
+      <c r="F201">
+        <v>2026</v>
+      </c>
+      <c r="G201" t="s">
+        <v>35</v>
+      </c>
+      <c r="H201">
+        <v>45</v>
+      </c>
+      <c r="I201">
+        <v>68</v>
+      </c>
+      <c r="J201">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>25</v>
+      </c>
+      <c r="B202" t="s">
+        <v>14</v>
+      </c>
+      <c r="C202" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D202" t="s">
+        <v>30</v>
+      </c>
+      <c r="E202" t="s">
+        <v>28</v>
+      </c>
+      <c r="F202">
+        <v>2026</v>
+      </c>
+      <c r="G202" t="s">
+        <v>31</v>
+      </c>
+      <c r="H202">
+        <v>15</v>
+      </c>
+      <c r="I202">
+        <v>46</v>
+      </c>
+      <c r="J202">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>25</v>
+      </c>
+      <c r="B203" t="s">
+        <v>14</v>
+      </c>
+      <c r="C203" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D203" t="s">
+        <v>30</v>
+      </c>
+      <c r="E203" t="s">
+        <v>28</v>
+      </c>
+      <c r="F203">
+        <v>2026</v>
+      </c>
+      <c r="G203" t="s">
+        <v>33</v>
+      </c>
+      <c r="H203">
+        <v>80</v>
+      </c>
+      <c r="I203">
+        <v>25</v>
+      </c>
+      <c r="J203">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>25</v>
+      </c>
+      <c r="B204" t="s">
+        <v>14</v>
+      </c>
+      <c r="C204" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D204" t="s">
+        <v>30</v>
+      </c>
+      <c r="E204" t="s">
+        <v>28</v>
+      </c>
+      <c r="F204">
+        <v>2026</v>
+      </c>
+      <c r="G204" t="s">
+        <v>35</v>
+      </c>
+      <c r="H204">
+        <v>20</v>
+      </c>
+      <c r="I204">
+        <v>64</v>
+      </c>
+      <c r="J204">
+        <v>71.5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>25</v>
+      </c>
+      <c r="B205" t="s">
+        <v>15</v>
+      </c>
+      <c r="C205" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D205" t="s">
+        <v>30</v>
+      </c>
+      <c r="E205" t="s">
+        <v>28</v>
+      </c>
+      <c r="F205">
+        <v>2026</v>
+      </c>
+      <c r="G205" t="s">
+        <v>34</v>
+      </c>
+      <c r="H205">
+        <v>90</v>
+      </c>
+      <c r="I205">
+        <v>30</v>
+      </c>
+      <c r="J205">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>25</v>
+      </c>
+      <c r="B206" t="s">
+        <v>15</v>
+      </c>
+      <c r="C206" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D206" t="s">
+        <v>30</v>
+      </c>
+      <c r="E206" t="s">
+        <v>28</v>
+      </c>
+      <c r="F206">
+        <v>2026</v>
+      </c>
+      <c r="G206" t="s">
+        <v>31</v>
+      </c>
+      <c r="H206">
+        <v>5</v>
+      </c>
+      <c r="I206">
+        <v>27</v>
+      </c>
+      <c r="J206">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>25</v>
+      </c>
+      <c r="B207" t="s">
+        <v>16</v>
+      </c>
+      <c r="C207" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D207" t="s">
+        <v>30</v>
+      </c>
+      <c r="E207" t="s">
+        <v>28</v>
+      </c>
+      <c r="F207">
+        <v>2026</v>
+      </c>
+      <c r="G207" t="s">
+        <v>31</v>
+      </c>
+      <c r="H207">
+        <v>20</v>
+      </c>
+      <c r="I207" s="3">
+        <v>34.875</v>
+      </c>
+      <c r="J207">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>25</v>
+      </c>
+      <c r="B208" t="s">
+        <v>16</v>
+      </c>
+      <c r="C208" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D208" t="s">
+        <v>30</v>
+      </c>
+      <c r="E208" t="s">
+        <v>28</v>
+      </c>
+      <c r="F208">
+        <v>2026</v>
+      </c>
+      <c r="G208" t="s">
+        <v>33</v>
+      </c>
+      <c r="H208">
+        <v>75</v>
+      </c>
+      <c r="I208">
+        <v>16</v>
+      </c>
+      <c r="J208">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>25</v>
+      </c>
+      <c r="B209" t="s">
+        <v>16</v>
+      </c>
+      <c r="C209" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D209" t="s">
+        <v>30</v>
+      </c>
+      <c r="E209" t="s">
+        <v>28</v>
+      </c>
+      <c r="F209">
+        <v>2026</v>
+      </c>
+      <c r="G209" t="s">
+        <v>34</v>
+      </c>
+      <c r="H209">
+        <v>15</v>
+      </c>
+      <c r="I209" t="s">
+        <v>36</v>
+      </c>
+      <c r="J209" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>25</v>
+      </c>
+      <c r="B210" t="s">
+        <v>17</v>
+      </c>
+      <c r="C210" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D210" t="s">
+        <v>30</v>
+      </c>
+      <c r="E210" t="s">
+        <v>28</v>
+      </c>
+      <c r="F210">
+        <v>2026</v>
+      </c>
+      <c r="G210" t="s">
+        <v>31</v>
+      </c>
+      <c r="H210">
+        <v>20</v>
+      </c>
+      <c r="I210">
+        <v>25</v>
+      </c>
+      <c r="J210">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>25</v>
+      </c>
+      <c r="B211" t="s">
+        <v>17</v>
+      </c>
+      <c r="C211" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D211" t="s">
+        <v>30</v>
+      </c>
+      <c r="E211" t="s">
+        <v>28</v>
+      </c>
+      <c r="F211">
+        <v>2026</v>
+      </c>
+      <c r="G211" t="s">
+        <v>33</v>
+      </c>
+      <c r="H211">
+        <v>75</v>
+      </c>
+      <c r="I211">
+        <v>16</v>
+      </c>
+      <c r="J211">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>25</v>
+      </c>
+      <c r="B212" t="s">
+        <v>17</v>
+      </c>
+      <c r="C212" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D212" t="s">
+        <v>30</v>
+      </c>
+      <c r="E212" t="s">
+        <v>28</v>
+      </c>
+      <c r="F212">
+        <v>2026</v>
+      </c>
+      <c r="G212" t="s">
+        <v>34</v>
+      </c>
+      <c r="H212">
+        <v>65</v>
+      </c>
+      <c r="I212" t="s">
+        <v>36</v>
+      </c>
+      <c r="J212" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>25</v>
+      </c>
+      <c r="B213" t="s">
+        <v>18</v>
+      </c>
+      <c r="C213" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D213" t="s">
+        <v>30</v>
+      </c>
+      <c r="E213" t="s">
+        <v>28</v>
+      </c>
+      <c r="F213">
+        <v>2026</v>
+      </c>
+      <c r="G213" t="s">
+        <v>31</v>
+      </c>
+      <c r="H213">
+        <v>40</v>
+      </c>
+      <c r="I213">
+        <v>43</v>
+      </c>
+      <c r="J213">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>25</v>
+      </c>
+      <c r="B214" t="s">
+        <v>18</v>
+      </c>
+      <c r="C214" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D214" t="s">
+        <v>30</v>
+      </c>
+      <c r="E214" t="s">
+        <v>28</v>
+      </c>
+      <c r="F214">
+        <v>2026</v>
+      </c>
+      <c r="G214" t="s">
+        <v>33</v>
+      </c>
+      <c r="H214">
+        <v>50</v>
+      </c>
+      <c r="I214">
+        <v>22</v>
+      </c>
+      <c r="J214">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>25</v>
+      </c>
+      <c r="B215" t="s">
+        <v>18</v>
+      </c>
+      <c r="C215" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D215" t="s">
+        <v>30</v>
+      </c>
+      <c r="E215" t="s">
+        <v>28</v>
+      </c>
+      <c r="F215">
+        <v>2026</v>
+      </c>
+      <c r="G215" t="s">
+        <v>34</v>
+      </c>
+      <c r="H215">
+        <v>30</v>
+      </c>
+      <c r="I215" t="s">
+        <v>36</v>
+      </c>
+      <c r="J215" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>25</v>
+      </c>
+      <c r="B216" t="s">
+        <v>18</v>
+      </c>
+      <c r="C216" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D216" t="s">
+        <v>30</v>
+      </c>
+      <c r="E216" t="s">
+        <v>28</v>
+      </c>
+      <c r="F216">
+        <v>2026</v>
+      </c>
+      <c r="G216" t="s">
+        <v>35</v>
+      </c>
+      <c r="H216">
+        <v>10</v>
+      </c>
+      <c r="I216">
+        <v>53</v>
+      </c>
+      <c r="J216">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>25</v>
+      </c>
+      <c r="B217" t="s">
+        <v>20</v>
+      </c>
+      <c r="C217" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D217" t="s">
+        <v>30</v>
+      </c>
+      <c r="E217" t="s">
+        <v>28</v>
+      </c>
+      <c r="F217">
+        <v>2026</v>
+      </c>
+      <c r="G217" t="s">
+        <v>31</v>
+      </c>
+      <c r="H217">
+        <v>35</v>
+      </c>
+      <c r="I217">
+        <v>48</v>
+      </c>
+      <c r="J217">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>25</v>
+      </c>
+      <c r="B218" t="s">
+        <v>20</v>
+      </c>
+      <c r="C218" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D218" t="s">
+        <v>30</v>
+      </c>
+      <c r="E218" t="s">
+        <v>28</v>
+      </c>
+      <c r="F218">
+        <v>2026</v>
+      </c>
+      <c r="G218" t="s">
+        <v>33</v>
+      </c>
+      <c r="H218">
+        <v>55</v>
+      </c>
+      <c r="I218">
+        <v>21</v>
+      </c>
+      <c r="J218">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>25</v>
+      </c>
+      <c r="B219" t="s">
+        <v>20</v>
+      </c>
+      <c r="C219" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D219" t="s">
+        <v>30</v>
+      </c>
+      <c r="E219" t="s">
+        <v>28</v>
+      </c>
+      <c r="F219">
+        <v>2026</v>
+      </c>
+      <c r="G219" t="s">
+        <v>34</v>
+      </c>
+      <c r="H219">
+        <v>10</v>
+      </c>
+      <c r="I219" t="s">
+        <v>36</v>
+      </c>
+      <c r="J219" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>25</v>
+      </c>
+      <c r="B220" t="s">
+        <v>20</v>
+      </c>
+      <c r="C220" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D220" t="s">
+        <v>30</v>
+      </c>
+      <c r="E220" t="s">
+        <v>28</v>
+      </c>
+      <c r="F220">
+        <v>2026</v>
+      </c>
+      <c r="G220" t="s">
+        <v>35</v>
+      </c>
+      <c r="H220">
+        <v>15</v>
+      </c>
+      <c r="I220">
+        <v>49</v>
+      </c>
+      <c r="J220">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>25</v>
+      </c>
+      <c r="B221" t="s">
+        <v>19</v>
+      </c>
+      <c r="C221" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D221" t="s">
+        <v>30</v>
+      </c>
+      <c r="E221" t="s">
+        <v>28</v>
+      </c>
+      <c r="F221">
+        <v>2026</v>
+      </c>
+      <c r="G221" t="s">
+        <v>31</v>
+      </c>
+      <c r="H221">
+        <v>25</v>
+      </c>
+      <c r="I221">
+        <v>49</v>
+      </c>
+      <c r="J221">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>25</v>
+      </c>
+      <c r="B222" t="s">
+        <v>19</v>
+      </c>
+      <c r="C222" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D222" t="s">
+        <v>30</v>
+      </c>
+      <c r="E222" t="s">
+        <v>28</v>
+      </c>
+      <c r="F222">
+        <v>2026</v>
+      </c>
+      <c r="G222" t="s">
+        <v>35</v>
+      </c>
+      <c r="H222">
+        <v>35</v>
+      </c>
+      <c r="I222">
+        <v>55</v>
+      </c>
+      <c r="J222">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>25</v>
+      </c>
+      <c r="B223" t="s">
+        <v>19</v>
+      </c>
+      <c r="C223" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D223" t="s">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>28</v>
+      </c>
+      <c r="F223">
+        <v>2026</v>
+      </c>
+      <c r="G223" t="s">
+        <v>33</v>
+      </c>
+      <c r="H223">
+        <v>45</v>
+      </c>
+      <c r="I223">
+        <v>25.5</v>
+      </c>
+      <c r="J223">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>25</v>
+      </c>
+      <c r="B224" t="s">
+        <v>21</v>
+      </c>
+      <c r="C224" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D224" t="s">
+        <v>30</v>
+      </c>
+      <c r="E224" t="s">
+        <v>28</v>
+      </c>
+      <c r="F224">
+        <v>2026</v>
+      </c>
+      <c r="G224" t="s">
+        <v>35</v>
+      </c>
+      <c r="H224">
+        <v>20</v>
+      </c>
+      <c r="I224">
+        <v>54</v>
+      </c>
+      <c r="J224">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>25</v>
+      </c>
+      <c r="B225" t="s">
+        <v>21</v>
+      </c>
+      <c r="C225" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D225" t="s">
+        <v>30</v>
+      </c>
+      <c r="E225" t="s">
+        <v>28</v>
+      </c>
+      <c r="F225">
+        <v>2026</v>
+      </c>
+      <c r="G225" t="s">
+        <v>31</v>
+      </c>
+      <c r="H225">
+        <v>25</v>
+      </c>
+      <c r="I225">
+        <v>34</v>
+      </c>
+      <c r="J225">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>25</v>
+      </c>
+      <c r="B226" t="s">
+        <v>21</v>
+      </c>
+      <c r="C226" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D226" t="s">
+        <v>30</v>
+      </c>
+      <c r="E226" t="s">
+        <v>28</v>
+      </c>
+      <c r="F226">
+        <v>2026</v>
+      </c>
+      <c r="G226" t="s">
+        <v>34</v>
+      </c>
+      <c r="H226">
+        <v>10</v>
+      </c>
+      <c r="I226" t="s">
+        <v>36</v>
+      </c>
+      <c r="J226" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>25</v>
+      </c>
+      <c r="B227" t="s">
+        <v>21</v>
+      </c>
+      <c r="C227" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D227" t="s">
+        <v>30</v>
+      </c>
+      <c r="E227" t="s">
+        <v>28</v>
+      </c>
+      <c r="F227">
+        <v>2026</v>
+      </c>
+      <c r="G227" t="s">
+        <v>33</v>
+      </c>
+      <c r="H227">
+        <v>65</v>
+      </c>
+      <c r="I227">
+        <v>23</v>
+      </c>
+      <c r="J227">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>25</v>
+      </c>
+      <c r="B228" t="s">
+        <v>22</v>
+      </c>
+      <c r="C228" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D228" t="s">
+        <v>30</v>
+      </c>
+      <c r="E228" t="s">
+        <v>28</v>
+      </c>
+      <c r="F228">
+        <v>2026</v>
+      </c>
+      <c r="G228" t="s">
+        <v>33</v>
+      </c>
+      <c r="H228">
+        <v>35</v>
+      </c>
+      <c r="I228" t="s">
+        <v>36</v>
+      </c>
+      <c r="J228" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>25</v>
+      </c>
+      <c r="B229" t="s">
+        <v>22</v>
+      </c>
+      <c r="C229" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D229" t="s">
+        <v>30</v>
+      </c>
+      <c r="E229" t="s">
+        <v>28</v>
+      </c>
+      <c r="F229">
+        <v>2026</v>
+      </c>
+      <c r="G229" t="s">
+        <v>34</v>
+      </c>
+      <c r="H229">
+        <v>90</v>
+      </c>
+      <c r="I229">
+        <v>31</v>
+      </c>
+      <c r="J229">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>25</v>
+      </c>
+      <c r="B230" t="s">
+        <v>22</v>
+      </c>
+      <c r="C230" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D230" t="s">
+        <v>30</v>
+      </c>
+      <c r="E230" t="s">
+        <v>28</v>
+      </c>
+      <c r="F230">
+        <v>2026</v>
+      </c>
+      <c r="G230" t="s">
+        <v>35</v>
+      </c>
+      <c r="H230">
+        <v>5</v>
+      </c>
+      <c r="I230">
+        <v>56</v>
+      </c>
+      <c r="J230">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>26</v>
+      </c>
+      <c r="B231" t="s">
+        <v>10</v>
+      </c>
+      <c r="C231" s="4">
         <v>46185</v>
       </c>
-      <c r="D166" t="s">
-        <v>30</v>
-      </c>
-      <c r="E166" t="s">
-        <v>28</v>
-      </c>
-      <c r="F166">
-        <v>2026</v>
-      </c>
-      <c r="G166" t="s">
-        <v>31</v>
-      </c>
-      <c r="H166">
+      <c r="D231" t="s">
+        <v>30</v>
+      </c>
+      <c r="E231" t="s">
+        <v>28</v>
+      </c>
+      <c r="F231">
+        <v>2026</v>
+      </c>
+      <c r="G231" t="s">
+        <v>31</v>
+      </c>
+      <c r="H231">
+        <v>35</v>
+      </c>
+      <c r="I231">
+        <v>57</v>
+      </c>
+      <c r="J231">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>26</v>
+      </c>
+      <c r="B232" t="s">
+        <v>10</v>
+      </c>
+      <c r="C232" s="4">
+        <v>46185</v>
+      </c>
+      <c r="D232" t="s">
+        <v>30</v>
+      </c>
+      <c r="E232" t="s">
+        <v>28</v>
+      </c>
+      <c r="F232">
+        <v>2026</v>
+      </c>
+      <c r="G232" t="s">
+        <v>35</v>
+      </c>
+      <c r="H232">
+        <v>35</v>
+      </c>
+      <c r="I232">
+        <v>67</v>
+      </c>
+      <c r="J232">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>26</v>
+      </c>
+      <c r="B233" t="s">
+        <v>11</v>
+      </c>
+      <c r="C233" s="4">
+        <v>46185</v>
+      </c>
+      <c r="D233" t="s">
+        <v>30</v>
+      </c>
+      <c r="E233" t="s">
+        <v>28</v>
+      </c>
+      <c r="F233">
+        <v>2026</v>
+      </c>
+      <c r="G233" t="s">
+        <v>31</v>
+      </c>
+      <c r="H233">
+        <v>75</v>
+      </c>
+      <c r="I233">
+        <v>52</v>
+      </c>
+      <c r="J233">
+        <v>69.5</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>26</v>
+      </c>
+      <c r="B234" t="s">
+        <v>12</v>
+      </c>
+      <c r="C234" s="4">
+        <v>46185</v>
+      </c>
+      <c r="D234" t="s">
+        <v>30</v>
+      </c>
+      <c r="E234" t="s">
+        <v>28</v>
+      </c>
+      <c r="F234">
+        <v>2026</v>
+      </c>
+      <c r="G234" t="s">
+        <v>31</v>
+      </c>
+      <c r="H234">
+        <v>60</v>
+      </c>
+      <c r="I234">
+        <v>61</v>
+      </c>
+      <c r="J234">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>26</v>
+      </c>
+      <c r="B235" t="s">
+        <v>23</v>
+      </c>
+      <c r="C235" s="4">
+        <v>46185</v>
+      </c>
+      <c r="D235" t="s">
+        <v>30</v>
+      </c>
+      <c r="E235" t="s">
+        <v>28</v>
+      </c>
+      <c r="F235">
+        <v>2026</v>
+      </c>
+      <c r="G235" t="s">
+        <v>31</v>
+      </c>
+      <c r="H235">
+        <v>65</v>
+      </c>
+      <c r="I235">
+        <v>46</v>
+      </c>
+      <c r="J235">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>26</v>
+      </c>
+      <c r="B236" t="s">
+        <v>13</v>
+      </c>
+      <c r="C236" s="4">
+        <v>46185</v>
+      </c>
+      <c r="D236" t="s">
+        <v>30</v>
+      </c>
+      <c r="E236" t="s">
+        <v>28</v>
+      </c>
+      <c r="F236">
+        <v>2026</v>
+      </c>
+      <c r="G236" t="s">
+        <v>31</v>
+      </c>
+      <c r="H236">
+        <v>80</v>
+      </c>
+      <c r="I236">
+        <v>59</v>
+      </c>
+      <c r="J236">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>26</v>
+      </c>
+      <c r="B237" t="s">
+        <v>14</v>
+      </c>
+      <c r="C237" s="4">
+        <v>46185</v>
+      </c>
+      <c r="D237" t="s">
+        <v>30</v>
+      </c>
+      <c r="E237" t="s">
+        <v>28</v>
+      </c>
+      <c r="F237">
+        <v>2026</v>
+      </c>
+      <c r="G237" t="s">
+        <v>31</v>
+      </c>
+      <c r="H237">
         <v>95</v>
       </c>
-      <c r="I166">
-        <v>50.25</v>
-      </c>
-      <c r="J166">
+      <c r="I237">
+        <v>55.5</v>
+      </c>
+      <c r="J237">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>26</v>
+      </c>
+      <c r="B238" t="s">
+        <v>15</v>
+      </c>
+      <c r="C238" s="4">
+        <v>46185</v>
+      </c>
+      <c r="D238" t="s">
+        <v>30</v>
+      </c>
+      <c r="E238" t="s">
+        <v>28</v>
+      </c>
+      <c r="F238">
+        <v>2026</v>
+      </c>
+      <c r="G238" t="s">
+        <v>31</v>
+      </c>
+      <c r="H238">
+        <v>95</v>
+      </c>
+      <c r="I238">
+        <v>49</v>
+      </c>
+      <c r="J238">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>26</v>
+      </c>
+      <c r="B239" t="s">
+        <v>16</v>
+      </c>
+      <c r="C239" s="4">
+        <v>46185</v>
+      </c>
+      <c r="D239" t="s">
+        <v>30</v>
+      </c>
+      <c r="E239" t="s">
+        <v>28</v>
+      </c>
+      <c r="F239">
+        <v>2026</v>
+      </c>
+      <c r="G239" t="s">
+        <v>35</v>
+      </c>
+      <c r="H239">
+        <v>40</v>
+      </c>
+      <c r="I239">
+        <v>78</v>
+      </c>
+      <c r="J239">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>26</v>
+      </c>
+      <c r="B240" t="s">
+        <v>16</v>
+      </c>
+      <c r="C240" s="4">
+        <v>46185</v>
+      </c>
+      <c r="D240" t="s">
+        <v>30</v>
+      </c>
+      <c r="E240" t="s">
+        <v>28</v>
+      </c>
+      <c r="F240">
+        <v>2026</v>
+      </c>
+      <c r="G240" t="s">
+        <v>31</v>
+      </c>
+      <c r="H240">
+        <v>30</v>
+      </c>
+      <c r="I240">
+        <v>54</v>
+      </c>
+      <c r="J240">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>26</v>
+      </c>
+      <c r="B241" t="s">
+        <v>17</v>
+      </c>
+      <c r="C241" s="4">
+        <v>46185</v>
+      </c>
+      <c r="D241" t="s">
+        <v>30</v>
+      </c>
+      <c r="E241" t="s">
+        <v>28</v>
+      </c>
+      <c r="F241">
+        <v>2026</v>
+      </c>
+      <c r="G241" t="s">
+        <v>35</v>
+      </c>
+      <c r="H241">
+        <v>35</v>
+      </c>
+      <c r="I241">
+        <v>87</v>
+      </c>
+      <c r="J241">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>26</v>
+      </c>
+      <c r="B242" t="s">
+        <v>17</v>
+      </c>
+      <c r="C242" s="4">
+        <v>46185</v>
+      </c>
+      <c r="D242" t="s">
+        <v>30</v>
+      </c>
+      <c r="E242" t="s">
+        <v>28</v>
+      </c>
+      <c r="F242">
+        <v>2026</v>
+      </c>
+      <c r="G242" t="s">
+        <v>31</v>
+      </c>
+      <c r="H242">
+        <v>30</v>
+      </c>
+      <c r="I242">
+        <v>54.5</v>
+      </c>
+      <c r="J242">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>26</v>
+      </c>
+      <c r="B243" t="s">
+        <v>18</v>
+      </c>
+      <c r="C243" s="4">
+        <v>46185</v>
+      </c>
+      <c r="D243" t="s">
+        <v>30</v>
+      </c>
+      <c r="E243" t="s">
+        <v>28</v>
+      </c>
+      <c r="F243">
+        <v>2026</v>
+      </c>
+      <c r="G243" t="s">
+        <v>31</v>
+      </c>
+      <c r="H243">
+        <v>80</v>
+      </c>
+      <c r="I243">
+        <v>50</v>
+      </c>
+      <c r="J243">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>26</v>
+      </c>
+      <c r="B244" t="s">
+        <v>20</v>
+      </c>
+      <c r="C244" s="4">
+        <v>46185</v>
+      </c>
+      <c r="D244" t="s">
+        <v>30</v>
+      </c>
+      <c r="E244" t="s">
+        <v>28</v>
+      </c>
+      <c r="F244">
+        <v>2026</v>
+      </c>
+      <c r="G244" t="s">
+        <v>31</v>
+      </c>
+      <c r="H244">
+        <v>90</v>
+      </c>
+      <c r="I244">
+        <v>52</v>
+      </c>
+      <c r="J244">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>26</v>
+      </c>
+      <c r="B245" t="s">
+        <v>19</v>
+      </c>
+      <c r="C245" s="4">
+        <v>46185</v>
+      </c>
+      <c r="D245" t="s">
+        <v>30</v>
+      </c>
+      <c r="E245" t="s">
+        <v>28</v>
+      </c>
+      <c r="F245">
+        <v>2026</v>
+      </c>
+      <c r="G245" t="s">
+        <v>31</v>
+      </c>
+      <c r="H245">
+        <v>85</v>
+      </c>
+      <c r="I245">
+        <v>62</v>
+      </c>
+      <c r="J245">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>26</v>
+      </c>
+      <c r="B246" t="s">
+        <v>21</v>
+      </c>
+      <c r="C246" s="4">
+        <v>46185</v>
+      </c>
+      <c r="D246" t="s">
+        <v>30</v>
+      </c>
+      <c r="E246" t="s">
+        <v>28</v>
+      </c>
+      <c r="F246">
+        <v>2026</v>
+      </c>
+      <c r="G246" t="s">
+        <v>31</v>
+      </c>
+      <c r="H246">
+        <v>95</v>
+      </c>
+      <c r="I246">
+        <v>56</v>
+      </c>
+      <c r="J246">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>26</v>
+      </c>
+      <c r="B247" t="s">
+        <v>22</v>
+      </c>
+      <c r="C247" s="4">
+        <v>46185</v>
+      </c>
+      <c r="D247" t="s">
+        <v>30</v>
+      </c>
+      <c r="E247" t="s">
+        <v>28</v>
+      </c>
+      <c r="F247">
+        <v>2026</v>
+      </c>
+      <c r="G247" t="s">
+        <v>31</v>
+      </c>
+      <c r="H247">
+        <v>95</v>
+      </c>
+      <c r="I247">
+        <v>50</v>
+      </c>
+      <c r="J247">
         <v>58</v>
       </c>
     </row>
